--- a/news_daily/2026-08-27.xlsx
+++ b/news_daily/2026-08-27.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BH$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BH$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BH$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH33"/>
+  <dimension ref="A1:BL33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -534,6 +534,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -835,6 +839,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -1007,176 +1031,208 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>SYY</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Sysco Corporation Common Stock</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>2026-08-27T22:43:56+08:00</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Nadler, Frost Demand Antitrust Investigation Into Sysco’s $29.1 Billion Acquisition of Restaurant Depot Over Threats of Higher Costs for Restaurants</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>反壟斷調查</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>'-0.526</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr"/>
+      <c r="R3" s="2" t="inlineStr"/>
+      <c r="S3" s="2" t="inlineStr"/>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE9SZ1ZMdmFkeE5GbVRSRVREUUlDX1VzMzVxcW9CWHlVN25OeENlbkRYRTNoejBHRTdHUk0tbFhZUHdXMnZxQnAyS2VyUGZqcUVEWldWQU1jVTRCaFduOHRBMDI4WmJ0ZDNCUkljbHZLaTFwenVkLXc?oc=5</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Congressman Jerrold Nadler (.gov)</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr"/>
+      <c r="X3" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y3" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z3" s="2" t="inlineStr">
+        <is>
+          <t>antitrust</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>aea8c7425bc54e06878752ff75641eb2</t>
+        </is>
+      </c>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>42980a4642e9e5a68ce2a1d4</t>
+        </is>
+      </c>
+      <c r="AD3" s="2" t="inlineStr">
+        <is>
+          <t>644247059e602af11f7e4e44</t>
+        </is>
+      </c>
+      <c r="AE3" s="2" t="inlineStr"/>
+      <c r="AF3" s="2" t="inlineStr"/>
+      <c r="AG3" s="2" t="inlineStr"/>
+      <c r="AH3" s="2" t="inlineStr"/>
+      <c r="AI3" s="2" t="inlineStr"/>
+      <c r="AJ3" s="2" t="inlineStr"/>
+      <c r="AK3" s="2" t="inlineStr"/>
+      <c r="AL3" s="2" t="inlineStr"/>
+      <c r="AM3" s="2" t="inlineStr"/>
+      <c r="AN3" s="2" t="inlineStr"/>
+      <c r="AO3" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>'-0.526</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
-      <c r="T3" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE9SZ1ZMdmFkeE5GbVRSRVREUUlDX1VzMzVxcW9CWHlVN25OeENlbkRYRTNoejBHRTdHUk0tbFhZUHdXMnZxQnAyS2VyUGZqcUVEWldWQU1jVTRCaFduOHRBMDI4WmJ0ZDNCUkljbHZLaTFwenVkLXc?oc=5</t>
-        </is>
-      </c>
-      <c r="V3" s="3" t="inlineStr">
-        <is>
-          <t>Congressman Jerrold Nadler (.gov)</t>
-        </is>
-      </c>
-      <c r="W3" s="3" t="inlineStr"/>
-      <c r="X3" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>ANTITRUST_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z3" s="3" t="inlineStr">
-        <is>
-          <t>antitrust</t>
-        </is>
-      </c>
-      <c r="AA3" s="3" t="inlineStr"/>
-      <c r="AB3" s="3" t="inlineStr"/>
-      <c r="AC3" s="3" t="inlineStr">
-        <is>
-          <t>42980a4642e9e5a68ce2a1d4</t>
-        </is>
-      </c>
-      <c r="AD3" s="3" t="inlineStr">
-        <is>
-          <t>644247059e602af11f7e4e44</t>
-        </is>
-      </c>
-      <c r="AE3" s="3" t="inlineStr"/>
-      <c r="AF3" s="3" t="inlineStr"/>
-      <c r="AG3" s="3" t="inlineStr"/>
-      <c r="AH3" s="3" t="inlineStr"/>
-      <c r="AI3" s="3" t="inlineStr"/>
-      <c r="AJ3" s="3" t="inlineStr"/>
-      <c r="AK3" s="3" t="inlineStr"/>
-      <c r="AL3" s="3" t="inlineStr"/>
-      <c r="AM3" s="3" t="inlineStr"/>
-      <c r="AN3" s="3" t="inlineStr"/>
-      <c r="AO3" s="3" t="inlineStr"/>
-      <c r="AP3" s="3" t="inlineStr"/>
-      <c r="AQ3" s="3" t="inlineStr"/>
-      <c r="AR3" s="3" t="inlineStr"/>
-      <c r="AS3" s="3" t="inlineStr"/>
-      <c r="AT3" s="3" t="inlineStr"/>
-      <c r="AU3" s="3" t="inlineStr"/>
-      <c r="AV3" s="3" t="inlineStr"/>
-      <c r="AW3" s="3" t="inlineStr">
+      <c r="AP3" s="2" t="inlineStr"/>
+      <c r="AQ3" s="2" t="inlineStr"/>
+      <c r="AR3" s="2" t="inlineStr"/>
+      <c r="AS3" s="2" t="inlineStr"/>
+      <c r="AT3" s="2" t="inlineStr"/>
+      <c r="AU3" s="2" t="inlineStr"/>
+      <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX3" s="3" t="inlineStr"/>
-      <c r="AY3" s="3" t="inlineStr"/>
-      <c r="AZ3" s="3" t="inlineStr"/>
-      <c r="BA3" s="3" t="inlineStr"/>
-      <c r="BB3" s="3" t="inlineStr">
+      <c r="AX3" s="2" t="inlineStr"/>
+      <c r="AY3" s="2" t="inlineStr"/>
+      <c r="AZ3" s="2" t="inlineStr"/>
+      <c r="BA3" s="2" t="inlineStr"/>
+      <c r="BB3" s="2" t="inlineStr">
         <is>
           <t>SYY</t>
         </is>
       </c>
-      <c r="BC3" s="3" t="inlineStr">
+      <c r="BC3" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD3" s="3" t="inlineStr"/>
-      <c r="BE3" s="3" t="inlineStr">
+      <c r="BD3" s="2" t="inlineStr"/>
+      <c r="BE3" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF3" s="3" t="inlineStr">
+      <c r="BF3" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG3" s="3" t="inlineStr">
+      <c r="BG3" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BH3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -1227,13 +1283,17 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -1282,7 +1342,11 @@
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr"/>
-      <c r="AB4" s="3" t="inlineStr"/>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>71bbeed4c98a4006b760ff9d82520e6a</t>
+        </is>
+      </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
           <t>5a447f249bf76399fdba70b1</t>
@@ -1303,7 +1367,11 @@
       <c r="AL4" s="3" t="inlineStr"/>
       <c r="AM4" s="3" t="inlineStr"/>
       <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP4" s="3" t="inlineStr"/>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr"/>
@@ -1347,6 +1415,18 @@
         </is>
       </c>
       <c r="BH4" s="3" t="inlineStr"/>
+      <c r="BI4" s="3" t="inlineStr"/>
+      <c r="BJ4" s="3" t="inlineStr"/>
+      <c r="BK4" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1517,6 +1597,10 @@
         </is>
       </c>
       <c r="BH5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr"/>
+      <c r="BJ5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr"/>
+      <c r="BL5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -1567,13 +1651,17 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -1622,7 +1710,11 @@
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr"/>
-      <c r="AB6" s="3" t="inlineStr"/>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>927e4f522a8d494e9d820e47e3917463</t>
+        </is>
+      </c>
       <c r="AC6" s="3" t="inlineStr">
         <is>
           <t>eee07bff2712b30b39193fc7</t>
@@ -1643,7 +1735,11 @@
       <c r="AL6" s="3" t="inlineStr"/>
       <c r="AM6" s="3" t="inlineStr"/>
       <c r="AN6" s="3" t="inlineStr"/>
-      <c r="AO6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP6" s="3" t="inlineStr"/>
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr"/>
@@ -1687,6 +1783,18 @@
         </is>
       </c>
       <c r="BH6" s="3" t="inlineStr"/>
+      <c r="BI6" s="3" t="inlineStr"/>
+      <c r="BJ6" s="3" t="inlineStr"/>
+      <c r="BK6" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -1737,13 +1845,17 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1792,7 +1904,11 @@
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr"/>
-      <c r="AB7" s="3" t="inlineStr"/>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>ccc45cae2e224e1aa92a581a94fd663c</t>
+        </is>
+      </c>
       <c r="AC7" s="3" t="inlineStr">
         <is>
           <t>1fef20b4a17d0bcf775adb21</t>
@@ -1813,7 +1929,11 @@
       <c r="AL7" s="3" t="inlineStr"/>
       <c r="AM7" s="3" t="inlineStr"/>
       <c r="AN7" s="3" t="inlineStr"/>
-      <c r="AO7" s="3" t="inlineStr"/>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP7" s="3" t="inlineStr"/>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr"/>
@@ -1857,176 +1977,216 @@
         </is>
       </c>
       <c r="BH7" s="3" t="inlineStr"/>
+      <c r="BI7" s="3" t="inlineStr"/>
+      <c r="BJ7" s="3" t="inlineStr"/>
+      <c r="BK7" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>NVIDIA Corporation</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>2026-08-27T19:01:00+08:00</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Fortune Tech: Meta’s record settlement, Nvidia Q2 earnings, DraftKings’ co-founder contract</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr"/>
-      <c r="M8" s="3" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5PQUNnVm02ZFdsdVVWdUo1UHhGdEhYNDVuWmVpX1JsV3ZaTFJ0TWpvQVgtM0RYVUpkRWhQMWdqMkZVaHpYXzlXSFc4VHR0VHF1MGZuY0Ywb3NIdTVvOEgxRlRWUkhjM1BnYUxiLQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Fortune</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr"/>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>81e2c99a618d4762ad3035f2a583431d</t>
+        </is>
+      </c>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>39729ed676e9017c7054c269</t>
+        </is>
+      </c>
+      <c r="AD8" s="2" t="inlineStr">
+        <is>
+          <t>34b25b146fddf80abb566360</t>
+        </is>
+      </c>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr"/>
+      <c r="AG8" s="2" t="inlineStr"/>
+      <c r="AH8" s="2" t="inlineStr"/>
+      <c r="AI8" s="2" t="inlineStr"/>
+      <c r="AJ8" s="2" t="inlineStr"/>
+      <c r="AK8" s="2" t="inlineStr"/>
+      <c r="AL8" s="2" t="inlineStr"/>
+      <c r="AM8" s="2" t="inlineStr"/>
+      <c r="AN8" s="2" t="inlineStr"/>
+      <c r="AO8" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>0.08</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="3" t="inlineStr"/>
-      <c r="R8" s="3" t="inlineStr"/>
-      <c r="S8" s="3" t="inlineStr"/>
-      <c r="T8" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U8" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5PQUNnVm02ZFdsdVVWdUo1UHhGdEhYNDVuWmVpX1JsV3ZaTFJ0TWpvQVgtM0RYVUpkRWhQMWdqMkZVaHpYXzlXSFc4VHR0VHF1MGZuY0Ywb3NIdTVvOEgxRlRWUkhjM1BnYUxiLQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V8" s="3" t="inlineStr">
-        <is>
-          <t>Fortune</t>
-        </is>
-      </c>
-      <c r="W8" s="3" t="inlineStr"/>
-      <c r="X8" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z8" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA8" s="3" t="inlineStr"/>
-      <c r="AB8" s="3" t="inlineStr"/>
-      <c r="AC8" s="3" t="inlineStr">
-        <is>
-          <t>39729ed676e9017c7054c269</t>
-        </is>
-      </c>
-      <c r="AD8" s="3" t="inlineStr">
-        <is>
-          <t>34b25b146fddf80abb566360</t>
-        </is>
-      </c>
-      <c r="AE8" s="3" t="inlineStr"/>
-      <c r="AF8" s="3" t="inlineStr"/>
-      <c r="AG8" s="3" t="inlineStr"/>
-      <c r="AH8" s="3" t="inlineStr"/>
-      <c r="AI8" s="3" t="inlineStr"/>
-      <c r="AJ8" s="3" t="inlineStr"/>
-      <c r="AK8" s="3" t="inlineStr"/>
-      <c r="AL8" s="3" t="inlineStr"/>
-      <c r="AM8" s="3" t="inlineStr"/>
-      <c r="AN8" s="3" t="inlineStr"/>
-      <c r="AO8" s="3" t="inlineStr"/>
-      <c r="AP8" s="3" t="inlineStr"/>
-      <c r="AQ8" s="3" t="inlineStr"/>
-      <c r="AR8" s="3" t="inlineStr"/>
-      <c r="AS8" s="3" t="inlineStr"/>
-      <c r="AT8" s="3" t="inlineStr"/>
-      <c r="AU8" s="3" t="inlineStr"/>
-      <c r="AV8" s="3" t="inlineStr"/>
-      <c r="AW8" s="3" t="inlineStr">
+      <c r="AP8" s="2" t="inlineStr"/>
+      <c r="AQ8" s="2" t="inlineStr"/>
+      <c r="AR8" s="2" t="inlineStr"/>
+      <c r="AS8" s="2" t="inlineStr"/>
+      <c r="AT8" s="2" t="inlineStr"/>
+      <c r="AU8" s="2" t="inlineStr"/>
+      <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" s="2" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX8" s="3" t="inlineStr"/>
-      <c r="AY8" s="3" t="inlineStr"/>
-      <c r="AZ8" s="3" t="inlineStr"/>
-      <c r="BA8" s="3" t="inlineStr"/>
-      <c r="BB8" s="3" t="inlineStr">
+      <c r="AX8" s="2" t="inlineStr"/>
+      <c r="AY8" s="2" t="inlineStr"/>
+      <c r="AZ8" s="2" t="inlineStr"/>
+      <c r="BA8" s="2" t="inlineStr"/>
+      <c r="BB8" s="2" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="BC8" s="3" t="inlineStr">
+      <c r="BC8" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD8" s="3" t="inlineStr"/>
-      <c r="BE8" s="3" t="inlineStr">
+      <c r="BD8" s="2" t="inlineStr"/>
+      <c r="BE8" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF8" s="3" t="inlineStr">
+      <c r="BF8" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG8" s="3" t="inlineStr">
+      <c r="BG8" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH8" s="3" t="inlineStr"/>
+      <c r="BH8" s="2" t="inlineStr"/>
+      <c r="BI8" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ8" s="2" t="inlineStr"/>
+      <c r="BK8" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -2077,13 +2237,17 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -2132,7 +2296,11 @@
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr"/>
-      <c r="AB9" s="3" t="inlineStr"/>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>2baab93a6bac485187c06f88d73b5f22</t>
+        </is>
+      </c>
       <c r="AC9" s="3" t="inlineStr">
         <is>
           <t>39729ed676e9017c7054c269</t>
@@ -2153,7 +2321,11 @@
       <c r="AL9" s="3" t="inlineStr"/>
       <c r="AM9" s="3" t="inlineStr"/>
       <c r="AN9" s="3" t="inlineStr"/>
-      <c r="AO9" s="3" t="inlineStr"/>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP9" s="3" t="inlineStr"/>
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr"/>
@@ -2197,6 +2369,18 @@
         </is>
       </c>
       <c r="BH9" s="3" t="inlineStr"/>
+      <c r="BI9" s="3" t="inlineStr"/>
+      <c r="BJ9" s="3" t="inlineStr"/>
+      <c r="BK9" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2367,6 +2551,10 @@
         </is>
       </c>
       <c r="BH10" s="2" t="inlineStr"/>
+      <c r="BI10" s="2" t="inlineStr"/>
+      <c r="BJ10" s="2" t="inlineStr"/>
+      <c r="BK10" s="2" t="inlineStr"/>
+      <c r="BL10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2537,6 +2725,10 @@
         </is>
       </c>
       <c r="BH11" s="2" t="inlineStr"/>
+      <c r="BI11" s="2" t="inlineStr"/>
+      <c r="BJ11" s="2" t="inlineStr"/>
+      <c r="BK11" s="2" t="inlineStr"/>
+      <c r="BL11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -2577,7 +2769,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>重大訴訟</t>
+          <t>監管裁罰</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -2587,13 +2779,17 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -2629,7 +2825,7 @@
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>MAJOR_LITIGATION</t>
+          <t>REGULATORY_PENALTY</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
@@ -2638,7 +2834,11 @@
         </is>
       </c>
       <c r="AA12" s="3" t="inlineStr"/>
-      <c r="AB12" s="3" t="inlineStr"/>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>2baade4ea47a4753ba1ef3e03e10ed9f</t>
+        </is>
+      </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
           <t>c9e9a09ed7123d18d6688519</t>
@@ -2659,7 +2859,11 @@
       <c r="AL12" s="3" t="inlineStr"/>
       <c r="AM12" s="3" t="inlineStr"/>
       <c r="AN12" s="3" t="inlineStr"/>
-      <c r="AO12" s="3" t="inlineStr"/>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP12" s="3" t="inlineStr"/>
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr"/>
@@ -2703,6 +2907,22 @@
         </is>
       </c>
       <c r="BH12" s="3" t="inlineStr"/>
+      <c r="BI12" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ12" s="3" t="inlineStr"/>
+      <c r="BK12" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL12" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -2753,13 +2973,17 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L13" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
@@ -2808,7 +3032,11 @@
         </is>
       </c>
       <c r="AA13" s="4" t="inlineStr"/>
-      <c r="AB13" s="4" t="inlineStr"/>
+      <c r="AB13" s="4" t="inlineStr">
+        <is>
+          <t>2ea21fbcaaea4d0aba0ac5cc1b57e64c</t>
+        </is>
+      </c>
       <c r="AC13" s="4" t="inlineStr">
         <is>
           <t>89f3b56b12cbc82210c453bf</t>
@@ -2829,7 +3057,11 @@
       <c r="AL13" s="4" t="inlineStr"/>
       <c r="AM13" s="4" t="inlineStr"/>
       <c r="AN13" s="4" t="inlineStr"/>
-      <c r="AO13" s="4" t="inlineStr"/>
+      <c r="AO13" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP13" s="4" t="inlineStr"/>
       <c r="AQ13" s="4" t="inlineStr"/>
       <c r="AR13" s="4" t="inlineStr"/>
@@ -2873,6 +3105,18 @@
         </is>
       </c>
       <c r="BH13" s="4" t="inlineStr"/>
+      <c r="BI13" s="4" t="inlineStr"/>
+      <c r="BJ13" s="4" t="inlineStr"/>
+      <c r="BK13" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL13" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -2923,13 +3167,17 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -2978,7 +3226,11 @@
         </is>
       </c>
       <c r="AA14" s="3" t="inlineStr"/>
-      <c r="AB14" s="3" t="inlineStr"/>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>064a2faa2d27491ab78785104fdc78c6</t>
+        </is>
+      </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
           <t>7a7e4ce476373c6d0080ea74</t>
@@ -2999,7 +3251,11 @@
       <c r="AL14" s="3" t="inlineStr"/>
       <c r="AM14" s="3" t="inlineStr"/>
       <c r="AN14" s="3" t="inlineStr"/>
-      <c r="AO14" s="3" t="inlineStr"/>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP14" s="3" t="inlineStr"/>
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr"/>
@@ -3043,6 +3299,18 @@
         </is>
       </c>
       <c r="BH14" s="3" t="inlineStr"/>
+      <c r="BI14" s="3" t="inlineStr"/>
+      <c r="BJ14" s="3" t="inlineStr"/>
+      <c r="BK14" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL14" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3213,6 +3481,10 @@
         </is>
       </c>
       <c r="BH15" s="2" t="inlineStr"/>
+      <c r="BI15" s="2" t="inlineStr"/>
+      <c r="BJ15" s="2" t="inlineStr"/>
+      <c r="BK15" s="2" t="inlineStr"/>
+      <c r="BL15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -3263,13 +3535,17 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -3318,7 +3594,11 @@
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr"/>
-      <c r="AB16" s="3" t="inlineStr"/>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>0bbbe195d80d465c997c16efbb786911</t>
+        </is>
+      </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
           <t>55872d6a6b59c80d0aeec51f</t>
@@ -3339,7 +3619,11 @@
       <c r="AL16" s="3" t="inlineStr"/>
       <c r="AM16" s="3" t="inlineStr"/>
       <c r="AN16" s="3" t="inlineStr"/>
-      <c r="AO16" s="3" t="inlineStr"/>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP16" s="3" t="inlineStr"/>
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr"/>
@@ -3383,6 +3667,18 @@
         </is>
       </c>
       <c r="BH16" s="3" t="inlineStr"/>
+      <c r="BI16" s="3" t="inlineStr"/>
+      <c r="BJ16" s="3" t="inlineStr"/>
+      <c r="BK16" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL16" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -3433,13 +3729,17 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
@@ -3488,7 +3788,11 @@
         </is>
       </c>
       <c r="AA17" s="3" t="inlineStr"/>
-      <c r="AB17" s="3" t="inlineStr"/>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>810e5ee5c5ba4c5dbd815f16e28d14ee</t>
+        </is>
+      </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
           <t>e429d01b73955f7a13eeeb96</t>
@@ -3509,7 +3813,11 @@
       <c r="AL17" s="3" t="inlineStr"/>
       <c r="AM17" s="3" t="inlineStr"/>
       <c r="AN17" s="3" t="inlineStr"/>
-      <c r="AO17" s="3" t="inlineStr"/>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP17" s="3" t="inlineStr"/>
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr"/>
@@ -3553,6 +3861,18 @@
         </is>
       </c>
       <c r="BH17" s="3" t="inlineStr"/>
+      <c r="BI17" s="3" t="inlineStr"/>
+      <c r="BJ17" s="3" t="inlineStr"/>
+      <c r="BK17" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL17" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -3723,6 +4043,10 @@
         </is>
       </c>
       <c r="BH18" s="5" t="inlineStr"/>
+      <c r="BI18" s="5" t="inlineStr"/>
+      <c r="BJ18" s="5" t="inlineStr"/>
+      <c r="BK18" s="5" t="inlineStr"/>
+      <c r="BL18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -3877,6 +4201,10 @@
       <c r="BF19" s="5" t="inlineStr"/>
       <c r="BG19" s="5" t="inlineStr"/>
       <c r="BH19" s="5" t="inlineStr"/>
+      <c r="BI19" s="5" t="inlineStr"/>
+      <c r="BJ19" s="5" t="inlineStr"/>
+      <c r="BK19" s="5" t="inlineStr"/>
+      <c r="BL19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -3927,13 +4255,17 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -3982,7 +4314,11 @@
         </is>
       </c>
       <c r="AA20" s="3" t="inlineStr"/>
-      <c r="AB20" s="3" t="inlineStr"/>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>832797d648cf412aadc3fea1aca57fb8</t>
+        </is>
+      </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
           <t>39e351ac93b9ef965a0173b9</t>
@@ -4003,7 +4339,11 @@
       <c r="AL20" s="3" t="inlineStr"/>
       <c r="AM20" s="3" t="inlineStr"/>
       <c r="AN20" s="3" t="inlineStr"/>
-      <c r="AO20" s="3" t="inlineStr"/>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP20" s="3" t="inlineStr"/>
       <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr"/>
@@ -4047,6 +4387,18 @@
         </is>
       </c>
       <c r="BH20" s="3" t="inlineStr"/>
+      <c r="BI20" s="3" t="inlineStr"/>
+      <c r="BJ20" s="3" t="inlineStr"/>
+      <c r="BK20" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL20" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -4097,13 +4449,17 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
@@ -4152,7 +4508,11 @@
         </is>
       </c>
       <c r="AA21" s="3" t="inlineStr"/>
-      <c r="AB21" s="3" t="inlineStr"/>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>844e78ec07bb4e12a544fa2235bc541e</t>
+        </is>
+      </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
           <t>227a7f932a6bb9d768ff6fd1</t>
@@ -4173,7 +4533,11 @@
       <c r="AL21" s="3" t="inlineStr"/>
       <c r="AM21" s="3" t="inlineStr"/>
       <c r="AN21" s="3" t="inlineStr"/>
-      <c r="AO21" s="3" t="inlineStr"/>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP21" s="3" t="inlineStr"/>
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr"/>
@@ -4209,6 +4573,18 @@
         </is>
       </c>
       <c r="BH21" s="3" t="inlineStr"/>
+      <c r="BI21" s="3" t="inlineStr"/>
+      <c r="BJ21" s="3" t="inlineStr"/>
+      <c r="BK21" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL21" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -4249,7 +4625,7 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>重大訴訟</t>
+          <t>監管裁罰</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -4259,13 +4635,17 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -4301,7 +4681,7 @@
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t>MAJOR_LITIGATION</t>
+          <t>REGULATORY_PENALTY</t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
@@ -4310,7 +4690,11 @@
         </is>
       </c>
       <c r="AA22" s="3" t="inlineStr"/>
-      <c r="AB22" s="3" t="inlineStr"/>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>1aa3debf05bb46d1b5430dfa9909b986</t>
+        </is>
+      </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
           <t>41638baa3e96be115a8cb4a0</t>
@@ -4331,7 +4715,11 @@
       <c r="AL22" s="3" t="inlineStr"/>
       <c r="AM22" s="3" t="inlineStr"/>
       <c r="AN22" s="3" t="inlineStr"/>
-      <c r="AO22" s="3" t="inlineStr"/>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP22" s="3" t="inlineStr"/>
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr"/>
@@ -4375,6 +4763,22 @@
         </is>
       </c>
       <c r="BH22" s="3" t="inlineStr"/>
+      <c r="BI22" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ22" s="3" t="inlineStr"/>
+      <c r="BK22" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL22" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4545,6 +4949,10 @@
         </is>
       </c>
       <c r="BH23" s="2" t="inlineStr"/>
+      <c r="BI23" s="2" t="inlineStr"/>
+      <c r="BJ23" s="2" t="inlineStr"/>
+      <c r="BK23" s="2" t="inlineStr"/>
+      <c r="BL23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -4595,13 +5003,17 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
@@ -4650,7 +5062,11 @@
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr"/>
-      <c r="AB24" s="3" t="inlineStr"/>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>c15c1b53295b47a7aa47af0c95dcdceb</t>
+        </is>
+      </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
           <t>4441b880142ef32d3285eafd</t>
@@ -4671,7 +5087,11 @@
       <c r="AL24" s="3" t="inlineStr"/>
       <c r="AM24" s="3" t="inlineStr"/>
       <c r="AN24" s="3" t="inlineStr"/>
-      <c r="AO24" s="3" t="inlineStr"/>
+      <c r="AO24" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP24" s="3" t="inlineStr"/>
       <c r="AQ24" s="3" t="inlineStr"/>
       <c r="AR24" s="3" t="inlineStr"/>
@@ -4715,6 +5135,18 @@
         </is>
       </c>
       <c r="BH24" s="3" t="inlineStr"/>
+      <c r="BI24" s="3" t="inlineStr"/>
+      <c r="BJ24" s="3" t="inlineStr"/>
+      <c r="BK24" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL24" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -4885,6 +5317,10 @@
         </is>
       </c>
       <c r="BH25" s="2" t="inlineStr"/>
+      <c r="BI25" s="2" t="inlineStr"/>
+      <c r="BJ25" s="2" t="inlineStr"/>
+      <c r="BK25" s="2" t="inlineStr"/>
+      <c r="BL25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5039,6 +5475,10 @@
       <c r="BF26" s="2" t="inlineStr"/>
       <c r="BG26" s="2" t="inlineStr"/>
       <c r="BH26" s="2" t="inlineStr"/>
+      <c r="BI26" s="2" t="inlineStr"/>
+      <c r="BJ26" s="2" t="inlineStr"/>
+      <c r="BK26" s="2" t="inlineStr"/>
+      <c r="BL26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -5209,6 +5649,10 @@
         </is>
       </c>
       <c r="BH27" s="5" t="inlineStr"/>
+      <c r="BI27" s="5" t="inlineStr"/>
+      <c r="BJ27" s="5" t="inlineStr"/>
+      <c r="BK27" s="5" t="inlineStr"/>
+      <c r="BL27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5379,6 +5823,10 @@
         </is>
       </c>
       <c r="BH28" s="2" t="inlineStr"/>
+      <c r="BI28" s="2" t="inlineStr"/>
+      <c r="BJ28" s="2" t="inlineStr"/>
+      <c r="BK28" s="2" t="inlineStr"/>
+      <c r="BL28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -5429,13 +5877,17 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
@@ -5484,7 +5936,11 @@
         </is>
       </c>
       <c r="AA29" s="3" t="inlineStr"/>
-      <c r="AB29" s="3" t="inlineStr"/>
+      <c r="AB29" s="3" t="inlineStr">
+        <is>
+          <t>cd5b2ac52af1476a96a9c3d822dd467e</t>
+        </is>
+      </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
           <t>fc678d417cfd75c3ec6d960b</t>
@@ -5505,7 +5961,11 @@
       <c r="AL29" s="3" t="inlineStr"/>
       <c r="AM29" s="3" t="inlineStr"/>
       <c r="AN29" s="3" t="inlineStr"/>
-      <c r="AO29" s="3" t="inlineStr"/>
+      <c r="AO29" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP29" s="3" t="inlineStr"/>
       <c r="AQ29" s="3" t="inlineStr"/>
       <c r="AR29" s="3" t="inlineStr"/>
@@ -5541,6 +6001,18 @@
         </is>
       </c>
       <c r="BH29" s="3" t="inlineStr"/>
+      <c r="BI29" s="3" t="inlineStr"/>
+      <c r="BJ29" s="3" t="inlineStr"/>
+      <c r="BK29" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL29" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5711,168 +6183,200 @@
         </is>
       </c>
       <c r="BH30" s="2" t="inlineStr"/>
+      <c r="BI30" s="2" t="inlineStr"/>
+      <c r="BJ30" s="2" t="inlineStr"/>
+      <c r="BK30" s="2" t="inlineStr"/>
+      <c r="BL30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Kroger</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>2026-08-27T02:41:48+08:00</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Here’s how to qualify for the new Kroger $17M settlement over prescription drug pricing</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr"/>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L31" s="3" t="inlineStr"/>
-      <c r="M31" s="3" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>0.119</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr"/>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPdXBLX0NLOE9SdXBLMGFSZ0pWNk4tZDZZdUNxNm9Nd2VSal9sUzBjUHpQLWtJUVVDOEVLLXlXSDVYMnJSM1lFQjFKV0pTNl9MRFVWcG5vbmxFd1QtLWlnV3IxRWJsbHZuTG9BR0JYNWJ5VlJhWkVFUzY0ZTNHX0JJeEVtV3lNTFpPSzAySzhfT01zSURBSHlrRV9rMA?oc=5</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr"/>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr"/>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>de16916eaf144396ab7d11d2d421df37</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>615d9c04531dc7f90a7e53ff</t>
+        </is>
+      </c>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>21ffcb676aeadfb494b962a3</t>
+        </is>
+      </c>
+      <c r="AE31" s="2" t="inlineStr"/>
+      <c r="AF31" s="2" t="inlineStr"/>
+      <c r="AG31" s="2" t="inlineStr"/>
+      <c r="AH31" s="2" t="inlineStr"/>
+      <c r="AI31" s="2" t="inlineStr"/>
+      <c r="AJ31" s="2" t="inlineStr"/>
+      <c r="AK31" s="2" t="inlineStr"/>
+      <c r="AL31" s="2" t="inlineStr"/>
+      <c r="AM31" s="2" t="inlineStr"/>
+      <c r="AN31" s="2" t="inlineStr"/>
+      <c r="AO31" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N31" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>0.119</t>
-        </is>
-      </c>
-      <c r="P31" s="3" t="inlineStr"/>
-      <c r="Q31" s="3" t="inlineStr"/>
-      <c r="R31" s="3" t="inlineStr"/>
-      <c r="S31" s="3" t="inlineStr"/>
-      <c r="T31" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U31" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPdXBLX0NLOE9SdXBLMGFSZ0pWNk4tZDZZdUNxNm9Nd2VSal9sUzBjUHpQLWtJUVVDOEVLLXlXSDVYMnJSM1lFQjFKV0pTNl9MRFVWcG5vbmxFd1QtLWlnV3IxRWJsbHZuTG9BR0JYNWJ5VlJhWkVFUzY0ZTNHX0JJeEVtV3lNTFpPSzAySzhfT01zSURBSHlrRV9rMA?oc=5</t>
-        </is>
-      </c>
-      <c r="V31" s="3" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W31" s="3" t="inlineStr"/>
-      <c r="X31" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y31" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z31" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA31" s="3" t="inlineStr"/>
-      <c r="AB31" s="3" t="inlineStr"/>
-      <c r="AC31" s="3" t="inlineStr">
-        <is>
-          <t>615d9c04531dc7f90a7e53ff</t>
-        </is>
-      </c>
-      <c r="AD31" s="3" t="inlineStr">
-        <is>
-          <t>21ffcb676aeadfb494b962a3</t>
-        </is>
-      </c>
-      <c r="AE31" s="3" t="inlineStr"/>
-      <c r="AF31" s="3" t="inlineStr"/>
-      <c r="AG31" s="3" t="inlineStr"/>
-      <c r="AH31" s="3" t="inlineStr"/>
-      <c r="AI31" s="3" t="inlineStr"/>
-      <c r="AJ31" s="3" t="inlineStr"/>
-      <c r="AK31" s="3" t="inlineStr"/>
-      <c r="AL31" s="3" t="inlineStr"/>
-      <c r="AM31" s="3" t="inlineStr"/>
-      <c r="AN31" s="3" t="inlineStr"/>
-      <c r="AO31" s="3" t="inlineStr"/>
-      <c r="AP31" s="3" t="inlineStr"/>
-      <c r="AQ31" s="3" t="inlineStr"/>
-      <c r="AR31" s="3" t="inlineStr"/>
-      <c r="AS31" s="3" t="inlineStr"/>
-      <c r="AT31" s="3" t="inlineStr"/>
-      <c r="AU31" s="3" t="inlineStr"/>
-      <c r="AV31" s="3" t="inlineStr"/>
-      <c r="AW31" s="3" t="inlineStr"/>
-      <c r="AX31" s="3" t="inlineStr"/>
-      <c r="AY31" s="3" t="inlineStr"/>
-      <c r="AZ31" s="3" t="inlineStr"/>
-      <c r="BA31" s="3" t="inlineStr"/>
-      <c r="BB31" s="3" t="inlineStr">
+      <c r="AP31" s="2" t="inlineStr"/>
+      <c r="AQ31" s="2" t="inlineStr"/>
+      <c r="AR31" s="2" t="inlineStr"/>
+      <c r="AS31" s="2" t="inlineStr"/>
+      <c r="AT31" s="2" t="inlineStr"/>
+      <c r="AU31" s="2" t="inlineStr"/>
+      <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" s="2" t="inlineStr"/>
+      <c r="AX31" s="2" t="inlineStr"/>
+      <c r="AY31" s="2" t="inlineStr"/>
+      <c r="AZ31" s="2" t="inlineStr"/>
+      <c r="BA31" s="2" t="inlineStr"/>
+      <c r="BB31" s="2" t="inlineStr">
         <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="BC31" s="3" t="inlineStr">
+      <c r="BC31" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD31" s="3" t="inlineStr"/>
-      <c r="BE31" s="3" t="inlineStr">
+      <c r="BD31" s="2" t="inlineStr"/>
+      <c r="BE31" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF31" s="3" t="inlineStr"/>
-      <c r="BG31" s="3" t="inlineStr">
+      <c r="BF31" s="2" t="inlineStr"/>
+      <c r="BG31" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH31" s="3" t="inlineStr"/>
+      <c r="BH31" s="2" t="inlineStr"/>
+      <c r="BI31" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ31" s="2" t="inlineStr"/>
+      <c r="BK31" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL31" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6043,171 +6547,203 @@
         </is>
       </c>
       <c r="BH32" s="2" t="inlineStr"/>
+      <c r="BI32" s="2" t="inlineStr"/>
+      <c r="BJ32" s="2" t="inlineStr"/>
+      <c r="BK32" s="2" t="inlineStr"/>
+      <c r="BL32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Kroger</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>2026-08-27T00:13:00+08:00</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Here’s how to find out if you qualify for part of Kroger’s $17 million settlement</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr"/>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L33" s="3" t="inlineStr"/>
-      <c r="M33" s="3" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>0.027</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr"/>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOQVVLZHdGeWMxbmlpb3JoMHpBTkRRWnFReFpwZU9YZ2dkVlRrTUJqY1AtbG1OOTQtbnpaV1AxTGxDY1RvNnhHN0ZyM0dLQzczWXJoMWRjdFNxM3ZneVJmSk1SSkp5dnRvRFpGZmtsVUdBdDB0ZmgtSHhqUkgxdHh2QmwtV2kxNjFZOXREWGtWdF9QUUdRTElaOGNtM0lYM2U1ZXhSNndGZE5fcHBL?oc=5</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>Action News 5</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr"/>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr"/>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>c26ca8c7b5f54901b399ff9bbda2f50a</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>ae73f6f537d1a1594921ce64</t>
+        </is>
+      </c>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>eadf751f796e32d981e1a538</t>
+        </is>
+      </c>
+      <c r="AE33" s="2" t="inlineStr"/>
+      <c r="AF33" s="2" t="inlineStr"/>
+      <c r="AG33" s="2" t="inlineStr"/>
+      <c r="AH33" s="2" t="inlineStr"/>
+      <c r="AI33" s="2" t="inlineStr"/>
+      <c r="AJ33" s="2" t="inlineStr"/>
+      <c r="AK33" s="2" t="inlineStr"/>
+      <c r="AL33" s="2" t="inlineStr"/>
+      <c r="AM33" s="2" t="inlineStr"/>
+      <c r="AN33" s="2" t="inlineStr"/>
+      <c r="AO33" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N33" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>0.027</t>
-        </is>
-      </c>
-      <c r="P33" s="3" t="inlineStr"/>
-      <c r="Q33" s="3" t="inlineStr"/>
-      <c r="R33" s="3" t="inlineStr"/>
-      <c r="S33" s="3" t="inlineStr"/>
-      <c r="T33" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U33" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOQVVLZHdGeWMxbmlpb3JoMHpBTkRRWnFReFpwZU9YZ2dkVlRrTUJqY1AtbG1OOTQtbnpaV1AxTGxDY1RvNnhHN0ZyM0dLQzczWXJoMWRjdFNxM3ZneVJmSk1SSkp5dnRvRFpGZmtsVUdBdDB0ZmgtSHhqUkgxdHh2QmwtV2kxNjFZOXREWGtWdF9QUUdRTElaOGNtM0lYM2U1ZXhSNndGZE5fcHBL?oc=5</t>
-        </is>
-      </c>
-      <c r="V33" s="3" t="inlineStr">
-        <is>
-          <t>Action News 5</t>
-        </is>
-      </c>
-      <c r="W33" s="3" t="inlineStr"/>
-      <c r="X33" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y33" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z33" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA33" s="3" t="inlineStr"/>
-      <c r="AB33" s="3" t="inlineStr"/>
-      <c r="AC33" s="3" t="inlineStr">
-        <is>
-          <t>ae73f6f537d1a1594921ce64</t>
-        </is>
-      </c>
-      <c r="AD33" s="3" t="inlineStr">
-        <is>
-          <t>eadf751f796e32d981e1a538</t>
-        </is>
-      </c>
-      <c r="AE33" s="3" t="inlineStr"/>
-      <c r="AF33" s="3" t="inlineStr"/>
-      <c r="AG33" s="3" t="inlineStr"/>
-      <c r="AH33" s="3" t="inlineStr"/>
-      <c r="AI33" s="3" t="inlineStr"/>
-      <c r="AJ33" s="3" t="inlineStr"/>
-      <c r="AK33" s="3" t="inlineStr"/>
-      <c r="AL33" s="3" t="inlineStr"/>
-      <c r="AM33" s="3" t="inlineStr"/>
-      <c r="AN33" s="3" t="inlineStr"/>
-      <c r="AO33" s="3" t="inlineStr"/>
-      <c r="AP33" s="3" t="inlineStr"/>
-      <c r="AQ33" s="3" t="inlineStr"/>
-      <c r="AR33" s="3" t="inlineStr"/>
-      <c r="AS33" s="3" t="inlineStr"/>
-      <c r="AT33" s="3" t="inlineStr"/>
-      <c r="AU33" s="3" t="inlineStr"/>
-      <c r="AV33" s="3" t="inlineStr"/>
-      <c r="AW33" s="3" t="inlineStr"/>
-      <c r="AX33" s="3" t="inlineStr"/>
-      <c r="AY33" s="3" t="inlineStr"/>
-      <c r="AZ33" s="3" t="inlineStr"/>
-      <c r="BA33" s="3" t="inlineStr"/>
-      <c r="BB33" s="3" t="inlineStr">
+      <c r="AP33" s="2" t="inlineStr"/>
+      <c r="AQ33" s="2" t="inlineStr"/>
+      <c r="AR33" s="2" t="inlineStr"/>
+      <c r="AS33" s="2" t="inlineStr"/>
+      <c r="AT33" s="2" t="inlineStr"/>
+      <c r="AU33" s="2" t="inlineStr"/>
+      <c r="AV33" s="2" t="inlineStr"/>
+      <c r="AW33" s="2" t="inlineStr"/>
+      <c r="AX33" s="2" t="inlineStr"/>
+      <c r="AY33" s="2" t="inlineStr"/>
+      <c r="AZ33" s="2" t="inlineStr"/>
+      <c r="BA33" s="2" t="inlineStr"/>
+      <c r="BB33" s="2" t="inlineStr">
         <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="BC33" s="3" t="inlineStr">
+      <c r="BC33" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD33" s="3" t="inlineStr"/>
-      <c r="BE33" s="3" t="inlineStr">
+      <c r="BD33" s="2" t="inlineStr"/>
+      <c r="BE33" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF33" s="3" t="inlineStr"/>
-      <c r="BG33" s="3" t="inlineStr">
+      <c r="BF33" s="2" t="inlineStr"/>
+      <c r="BG33" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH33" s="3" t="inlineStr"/>
+      <c r="BH33" s="2" t="inlineStr"/>
+      <c r="BI33" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ33" s="2" t="inlineStr"/>
+      <c r="BK33" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL33" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH33"/>
+  <autoFilter ref="A1:BL33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6218,7 +6754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH22"/>
+  <dimension ref="A1:BL18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6281,6 +6817,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6584,6 +7124,26 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -6598,22 +7158,22 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>SYY</t>
+          <t>HUM</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Sysco Corporation Common Stock</t>
+          <t>Humana Inc. Common Stock</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27T22:43:56+08:00</t>
+          <t>2026-08-27T22:34:03+08:00</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Nadler, Frost Demand Antitrust Investigation Into Sysco’s $29.1 Billion Acquisition of Restaurant Depot Over Threats of Higher Costs for Restaurants</t>
+          <t>Humana-owned Villages Health agrees to $542M settlement for overbilling Medicare</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr"/>
@@ -6624,7 +7184,7 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>反壟斷調查</t>
+          <t>監管裁罰</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -6634,13 +7194,17 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
@@ -6650,7 +7214,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>'-0.526</t>
+          <t>'-0.035</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr"/>
@@ -6664,12 +7228,12 @@
       </c>
       <c r="U2" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE9SZ1ZMdmFkeE5GbVRSRVREUUlDX1VzMzVxcW9CWHlVN25OeENlbkRYRTNoejBHRTdHUk0tbFhZUHdXMnZxQnAyS2VyUGZqcUVEWldWQU1jVTRCaFduOHRBMDI4WmJ0ZDNCUkljbHZLaTFwenVkLXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQUGpmNG14eUdmbklCZFF0TWVGUHRWQ3Nidkt5NDdtZ0wyZVZRNC1NZnZhcXFrVG1lakZNRldIaWQweHJkN0tRbGVuR0hKTlZwY2Q0RUN4M0NHa2F0blBQSFNMVkR6amdEdWZkYzFfTC1idHBJSUI3YjFTUDdQU3pyc0FpdmxDMXVZQU9JTFJ5elh6ejl1QVNJZi1PXzVvUHNpTURXVlFZSi1fQQ?oc=5</t>
         </is>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
-          <t>Congressman Jerrold Nadler (.gov)</t>
+          <t>Healthcare Dive</t>
         </is>
       </c>
       <c r="W2" s="3" t="inlineStr"/>
@@ -6680,24 +7244,28 @@
       </c>
       <c r="Y2" s="3" t="inlineStr">
         <is>
-          <t>ANTITRUST_INVESTIGATION</t>
+          <t>REGULATORY_PENALTY</t>
         </is>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
-          <t>antitrust</t>
+          <t>settlement</t>
         </is>
       </c>
       <c r="AA2" s="3" t="inlineStr"/>
-      <c r="AB2" s="3" t="inlineStr"/>
+      <c r="AB2" s="3" t="inlineStr">
+        <is>
+          <t>71bbeed4c98a4006b760ff9d82520e6a</t>
+        </is>
+      </c>
       <c r="AC2" s="3" t="inlineStr">
         <is>
-          <t>42980a4642e9e5a68ce2a1d4</t>
+          <t>5a447f249bf76399fdba70b1</t>
         </is>
       </c>
       <c r="AD2" s="3" t="inlineStr">
         <is>
-          <t>644247059e602af11f7e4e44</t>
+          <t>3eccdedff5b423dd25d11b0b</t>
         </is>
       </c>
       <c r="AE2" s="3" t="inlineStr"/>
@@ -6710,7 +7278,11 @@
       <c r="AL2" s="3" t="inlineStr"/>
       <c r="AM2" s="3" t="inlineStr"/>
       <c r="AN2" s="3" t="inlineStr"/>
-      <c r="AO2" s="3" t="inlineStr"/>
+      <c r="AO2" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="3" t="inlineStr"/>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr"/>
@@ -6729,7 +7301,7 @@
       <c r="BA2" s="3" t="inlineStr"/>
       <c r="BB2" s="3" t="inlineStr">
         <is>
-          <t>SYY</t>
+          <t>HUM</t>
         </is>
       </c>
       <c r="BC2" s="3" t="inlineStr">
@@ -6754,6 +7326,18 @@
         </is>
       </c>
       <c r="BH2" s="3" t="inlineStr"/>
+      <c r="BI2" s="3" t="inlineStr"/>
+      <c r="BJ2" s="3" t="inlineStr"/>
+      <c r="BK2" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -6768,22 +7352,22 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>HUM</t>
+          <t>META</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Humana Inc. Common Stock</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27T22:34:03+08:00</t>
+          <t>2026-08-27T21:43:15+08:00</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Humana-owned Villages Health agrees to $542M settlement for overbilling Medicare</t>
+          <t>Here’s what Meta’s $18 billion multistate settlement could mean for kids — and for its bottom line</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
@@ -6804,13 +7388,17 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -6820,7 +7408,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>'-0.035</t>
+          <t>0.049</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr"/>
@@ -6834,12 +7422,12 @@
       </c>
       <c r="U3" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQUGpmNG14eUdmbklCZFF0TWVGUHRWQ3Nidkt5NDdtZ0wyZVZRNC1NZnZhcXFrVG1lakZNRldIaWQweHJkN0tRbGVuR0hKTlZwY2Q0RUN4M0NHa2F0blBQSFNMVkR6amdEdWZkYzFfTC1idHBJSUI3YjFTUDdQU3pyc0FpdmxDMXVZQU9JTFJ5elh6ejl1QVNJZi1PXzVvUHNpTURXVlFZSi1fQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNanFWV2Z0cGJ1emJuUVZ1MzFKWGdpUWdXYnE5b1dneXdFMVE1blFGdUtrZHFIUy1MRnRwRDAtbGVmR1BpNnYwbnV5UndHNTNmWTRCaFJSV1ZFSDJlUGhJSUZ6Z3BWWG9yWUd6YldEWF9lRmNRMUsxR01HUkozTFVDbXhlMzhYd1E?oc=5</t>
         </is>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
-          <t>Healthcare Dive</t>
+          <t>CNN</t>
         </is>
       </c>
       <c r="W3" s="3" t="inlineStr"/>
@@ -6859,15 +7447,19 @@
         </is>
       </c>
       <c r="AA3" s="3" t="inlineStr"/>
-      <c r="AB3" s="3" t="inlineStr"/>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>927e4f522a8d494e9d820e47e3917463</t>
+        </is>
+      </c>
       <c r="AC3" s="3" t="inlineStr">
         <is>
-          <t>5a447f249bf76399fdba70b1</t>
+          <t>eee07bff2712b30b39193fc7</t>
         </is>
       </c>
       <c r="AD3" s="3" t="inlineStr">
         <is>
-          <t>3eccdedff5b423dd25d11b0b</t>
+          <t>835c529353eebc961229ccdb</t>
         </is>
       </c>
       <c r="AE3" s="3" t="inlineStr"/>
@@ -6880,7 +7472,11 @@
       <c r="AL3" s="3" t="inlineStr"/>
       <c r="AM3" s="3" t="inlineStr"/>
       <c r="AN3" s="3" t="inlineStr"/>
-      <c r="AO3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="3" t="inlineStr"/>
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr"/>
@@ -6890,7 +7486,7 @@
       <c r="AV3" s="3" t="inlineStr"/>
       <c r="AW3" s="3" t="inlineStr">
         <is>
-          <t>NYSE</t>
+          <t>NASDAQ</t>
         </is>
       </c>
       <c r="AX3" s="3" t="inlineStr"/>
@@ -6899,7 +7495,7 @@
       <c r="BA3" s="3" t="inlineStr"/>
       <c r="BB3" s="3" t="inlineStr">
         <is>
-          <t>HUM</t>
+          <t>META</t>
         </is>
       </c>
       <c r="BC3" s="3" t="inlineStr">
@@ -6910,20 +7506,32 @@
       <c r="BD3" s="3" t="inlineStr"/>
       <c r="BE3" s="3" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+          <t>https://investor.atmeta.com/stock-info/default.aspx</t>
         </is>
       </c>
       <c r="BF3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="BG3" s="3" t="inlineStr">
         <is>
-          <t>交易所目前名單</t>
+          <t>上市公司</t>
         </is>
       </c>
       <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BI3" s="3" t="inlineStr"/>
+      <c r="BJ3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -6948,12 +7556,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27T21:43:15+08:00</t>
+          <t>2026-08-27T19:02:00+08:00</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Here’s what Meta’s $18 billion multistate settlement could mean for kids — and for its bottom line</t>
+          <t>Meta reaches $17B settlement. And, nuclear regulator to abandon radiation safety rule</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
@@ -6974,13 +7582,17 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -6990,7 +7602,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>'-0.124</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr"/>
@@ -7004,12 +7616,12 @@
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNanFWV2Z0cGJ1emJuUVZ1MzFKWGdpUWdXYnE5b1dneXdFMVE1blFGdUtrZHFIUy1MRnRwRDAtbGVmR1BpNnYwbnV5UndHNTNmWTRCaFJSV1ZFSDJlUGhJSUZ6Z3BWWG9yWUd6YldEWF9lRmNRMUsxR01HUkozTFVDbXhlMzhYd1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQMjUyT1JjTmkzVG5tOC1GQUZMUk0takZ2U2FubWN6em5OMmE3ZzdXdEI0X2ZwVXdLazBERFhSbmxNZWVIYkdpMWxlN1ZNS245eVhsaFM3Q0w2cnkzOVVkcTJDSjdaVTI0NDBqMVVtbDhOd2pkOGRRVXBCM2M4VjZVU0lxMDJET3llcHJYbzlUWEVMTGFzQ3lJc0xtcGZ0Y1NCbENDQTJjTDIzNHNMUXVHNGFwR002dERjYUtCNjRoUDdjbXlaREMzWkZsakswUzV4R1RqTXJR?oc=5</t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>CNN</t>
+          <t>Iowa Public Radio</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr"/>
@@ -7029,15 +7641,19 @@
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr"/>
-      <c r="AB4" s="3" t="inlineStr"/>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>ccc45cae2e224e1aa92a581a94fd663c</t>
+        </is>
+      </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>eee07bff2712b30b39193fc7</t>
+          <t>1fef20b4a17d0bcf775adb21</t>
         </is>
       </c>
       <c r="AD4" s="3" t="inlineStr">
         <is>
-          <t>835c529353eebc961229ccdb</t>
+          <t>29fd57e2ecbfab934da3d346</t>
         </is>
       </c>
       <c r="AE4" s="3" t="inlineStr"/>
@@ -7050,7 +7666,11 @@
       <c r="AL4" s="3" t="inlineStr"/>
       <c r="AM4" s="3" t="inlineStr"/>
       <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP4" s="3" t="inlineStr"/>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr"/>
@@ -7094,6 +7714,18 @@
         </is>
       </c>
       <c r="BH4" s="3" t="inlineStr"/>
+      <c r="BI4" s="3" t="inlineStr"/>
+      <c r="BJ4" s="3" t="inlineStr"/>
+      <c r="BK4" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -7118,12 +7750,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27T19:02:00+08:00</t>
+          <t>2026-08-27T19:01:00+08:00</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Meta reaches $17B settlement. And, nuclear regulator to abandon radiation safety rule</t>
+          <t>Fortune Tech: Meta’s record settlement, Nvidia Q2 earnings, DraftKings’ co-founder contract</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
@@ -7144,13 +7776,17 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -7160,7 +7796,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>'-0.124</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr"/>
@@ -7174,12 +7810,12 @@
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQMjUyT1JjTmkzVG5tOC1GQUZMUk0takZ2U2FubWN6em5OMmE3ZzdXdEI0X2ZwVXdLazBERFhSbmxNZWVIYkdpMWxlN1ZNS245eVhsaFM3Q0w2cnkzOVVkcTJDSjdaVTI0NDBqMVVtbDhOd2pkOGRRVXBCM2M4VjZVU0lxMDJET3llcHJYbzlUWEVMTGFzQ3lJc0xtcGZ0Y1NCbENDQTJjTDIzNHNMUXVHNGFwR002dERjYUtCNjRoUDdjbXlaREMzWkZsakswUzV4R1RqTXJR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5PQUNnVm02ZFdsdVVWdUo1UHhGdEhYNDVuWmVpX1JsV3ZaTFJ0TWpvQVgtM0RYVUpkRWhQMWdqMkZVaHpYXzlXSFc4VHR0VHF1MGZuY0Ywb3NIdTVvOEgxRlRWUkhjM1BnYUxiLQ?oc=5</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t>Iowa Public Radio</t>
+          <t>Fortune</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr"/>
@@ -7199,15 +7835,19 @@
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr"/>
-      <c r="AB5" s="3" t="inlineStr"/>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>2baab93a6bac485187c06f88d73b5f22</t>
+        </is>
+      </c>
       <c r="AC5" s="3" t="inlineStr">
         <is>
-          <t>1fef20b4a17d0bcf775adb21</t>
+          <t>39729ed676e9017c7054c269</t>
         </is>
       </c>
       <c r="AD5" s="3" t="inlineStr">
         <is>
-          <t>29fd57e2ecbfab934da3d346</t>
+          <t>1a44deb64fa0fabf7d78b62b</t>
         </is>
       </c>
       <c r="AE5" s="3" t="inlineStr"/>
@@ -7220,7 +7860,11 @@
       <c r="AL5" s="3" t="inlineStr"/>
       <c r="AM5" s="3" t="inlineStr"/>
       <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP5" s="3" t="inlineStr"/>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr"/>
@@ -7264,6 +7908,18 @@
         </is>
       </c>
       <c r="BH5" s="3" t="inlineStr"/>
+      <c r="BI5" s="3" t="inlineStr"/>
+      <c r="BJ5" s="3" t="inlineStr"/>
+      <c r="BK5" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -7278,22 +7934,22 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>KKR</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>KKR &amp; Co. Inc. Common Stock</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27T19:01:00+08:00</t>
+          <t>2026-08-27T16:35:55+08:00</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Fortune Tech: Meta’s record settlement, Nvidia Q2 earnings, DraftKings’ co-founder contract</t>
+          <t>美股異動丨KKR盤前升2.36% 支付2.5億美元就美司法部併購申報訴訟達成和解</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr"/>
@@ -7314,13 +7970,17 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -7328,11 +7988,7 @@
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>0.08</t>
-        </is>
-      </c>
+      <c r="O6" s="3" t="inlineStr"/>
       <c r="P6" s="3" t="inlineStr"/>
       <c r="Q6" s="3" t="inlineStr"/>
       <c r="R6" s="3" t="inlineStr"/>
@@ -7344,12 +8000,12 @@
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5PQUNnVm02ZFdsdVVWdUo1UHhGdEhYNDVuWmVpX1JsV3ZaTFJ0TWpvQVgtM0RYVUpkRWhQMWdqMkZVaHpYXzlXSFc4VHR0VHF1MGZuY0Ywb3NIdTVvOEgxRlRWUkhjM1BnYUxiLQ?oc=5</t>
+          <t>https://www.gelonghui.com/live/2636223</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t>Fortune</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr"/>
@@ -7365,19 +8021,23 @@
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t>settlement</t>
+          <t>訴訟</t>
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr"/>
-      <c r="AB6" s="3" t="inlineStr"/>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>2baade4ea47a4753ba1ef3e03e10ed9f</t>
+        </is>
+      </c>
       <c r="AC6" s="3" t="inlineStr">
         <is>
-          <t>39729ed676e9017c7054c269</t>
+          <t>c9e9a09ed7123d18d6688519</t>
         </is>
       </c>
       <c r="AD6" s="3" t="inlineStr">
         <is>
-          <t>34b25b146fddf80abb566360</t>
+          <t>00b3eb0a13584fb6e7e61053</t>
         </is>
       </c>
       <c r="AE6" s="3" t="inlineStr"/>
@@ -7390,7 +8050,11 @@
       <c r="AL6" s="3" t="inlineStr"/>
       <c r="AM6" s="3" t="inlineStr"/>
       <c r="AN6" s="3" t="inlineStr"/>
-      <c r="AO6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP6" s="3" t="inlineStr"/>
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr"/>
@@ -7400,7 +8064,7 @@
       <c r="AV6" s="3" t="inlineStr"/>
       <c r="AW6" s="3" t="inlineStr">
         <is>
-          <t>NASDAQ</t>
+          <t>NYSE</t>
         </is>
       </c>
       <c r="AX6" s="3" t="inlineStr"/>
@@ -7409,7 +8073,7 @@
       <c r="BA6" s="3" t="inlineStr"/>
       <c r="BB6" s="3" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>KKR</t>
         </is>
       </c>
       <c r="BC6" s="3" t="inlineStr">
@@ -7420,12 +8084,12 @@
       <c r="BD6" s="3" t="inlineStr"/>
       <c r="BE6" s="3" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
       <c r="BF6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
       <c r="BG6" s="3" t="inlineStr">
@@ -7434,176 +8098,216 @@
         </is>
       </c>
       <c r="BH6" s="3" t="inlineStr"/>
+      <c r="BI6" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ6" s="3" t="inlineStr"/>
+      <c r="BK6" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Meta Platforms, Inc.</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27T19:01:00+08:00</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Fortune Tech: Meta’s record settlement, Nvidia Q2 earnings, DraftKings’ co-founder contract</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>ECHO</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>EchoStar Corporation</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-27T15:00:00+08:00</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Judge Pérez orders examiner in Hughes Satellite Systems bankruptcy to probe $1.5bn of EchoStar transfers</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>破產</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>'-0.563</t>
+        </is>
+      </c>
+      <c r="P7" s="4" t="inlineStr"/>
+      <c r="Q7" s="4" t="inlineStr"/>
+      <c r="R7" s="4" t="inlineStr"/>
+      <c r="S7" s="4" t="inlineStr"/>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U7" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQcTB2RU9XTlJtWF94V3U5d0JjVnE2RUF0WU1QMVFwRWJuSm9qX01MdWFONXJzS25pUmd3ZF8yT1pOblNPMzNTSGZ5Z0JYbzh4YnNqR1FTcm1YMjloczBxajl2R3VScDZMYl9TN1U5YnZMQzlwYnlieDlDTExpeS14UlV0WTk2SHRrYklkTUh3dVQ3bUNicU9FdFVpM25xUXlIdXNPRjNDaEU?oc=5</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>9fin</t>
+        </is>
+      </c>
+      <c r="W7" s="4" t="inlineStr"/>
+      <c r="X7" s="4" t="inlineStr">
+        <is>
+          <t>FINANCIAL</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>BANKRUPTCY</t>
+        </is>
+      </c>
+      <c r="Z7" s="4" t="inlineStr">
+        <is>
+          <t>bankruptcy</t>
+        </is>
+      </c>
+      <c r="AA7" s="4" t="inlineStr"/>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>2ea21fbcaaea4d0aba0ac5cc1b57e64c</t>
+        </is>
+      </c>
+      <c r="AC7" s="4" t="inlineStr">
+        <is>
+          <t>89f3b56b12cbc82210c453bf</t>
+        </is>
+      </c>
+      <c r="AD7" s="4" t="inlineStr">
+        <is>
+          <t>598c2ffe45c5df02be123819</t>
+        </is>
+      </c>
+      <c r="AE7" s="4" t="inlineStr"/>
+      <c r="AF7" s="4" t="inlineStr"/>
+      <c r="AG7" s="4" t="inlineStr"/>
+      <c r="AH7" s="4" t="inlineStr"/>
+      <c r="AI7" s="4" t="inlineStr"/>
+      <c r="AJ7" s="4" t="inlineStr"/>
+      <c r="AK7" s="4" t="inlineStr"/>
+      <c r="AL7" s="4" t="inlineStr"/>
+      <c r="AM7" s="4" t="inlineStr"/>
+      <c r="AN7" s="4" t="inlineStr"/>
+      <c r="AO7" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>0.08</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
-      <c r="S7" s="3" t="inlineStr"/>
-      <c r="T7" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5PQUNnVm02ZFdsdVVWdUo1UHhGdEhYNDVuWmVpX1JsV3ZaTFJ0TWpvQVgtM0RYVUpkRWhQMWdqMkZVaHpYXzlXSFc4VHR0VHF1MGZuY0Ywb3NIdTVvOEgxRlRWUkhjM1BnYUxiLQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V7" s="3" t="inlineStr">
-        <is>
-          <t>Fortune</t>
-        </is>
-      </c>
-      <c r="W7" s="3" t="inlineStr"/>
-      <c r="X7" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z7" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA7" s="3" t="inlineStr"/>
-      <c r="AB7" s="3" t="inlineStr"/>
-      <c r="AC7" s="3" t="inlineStr">
-        <is>
-          <t>39729ed676e9017c7054c269</t>
-        </is>
-      </c>
-      <c r="AD7" s="3" t="inlineStr">
-        <is>
-          <t>1a44deb64fa0fabf7d78b62b</t>
-        </is>
-      </c>
-      <c r="AE7" s="3" t="inlineStr"/>
-      <c r="AF7" s="3" t="inlineStr"/>
-      <c r="AG7" s="3" t="inlineStr"/>
-      <c r="AH7" s="3" t="inlineStr"/>
-      <c r="AI7" s="3" t="inlineStr"/>
-      <c r="AJ7" s="3" t="inlineStr"/>
-      <c r="AK7" s="3" t="inlineStr"/>
-      <c r="AL7" s="3" t="inlineStr"/>
-      <c r="AM7" s="3" t="inlineStr"/>
-      <c r="AN7" s="3" t="inlineStr"/>
-      <c r="AO7" s="3" t="inlineStr"/>
-      <c r="AP7" s="3" t="inlineStr"/>
-      <c r="AQ7" s="3" t="inlineStr"/>
-      <c r="AR7" s="3" t="inlineStr"/>
-      <c r="AS7" s="3" t="inlineStr"/>
-      <c r="AT7" s="3" t="inlineStr"/>
-      <c r="AU7" s="3" t="inlineStr"/>
-      <c r="AV7" s="3" t="inlineStr"/>
-      <c r="AW7" s="3" t="inlineStr">
+      <c r="AP7" s="4" t="inlineStr"/>
+      <c r="AQ7" s="4" t="inlineStr"/>
+      <c r="AR7" s="4" t="inlineStr"/>
+      <c r="AS7" s="4" t="inlineStr"/>
+      <c r="AT7" s="4" t="inlineStr"/>
+      <c r="AU7" s="4" t="inlineStr"/>
+      <c r="AV7" s="4" t="inlineStr"/>
+      <c r="AW7" s="4" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX7" s="3" t="inlineStr"/>
-      <c r="AY7" s="3" t="inlineStr"/>
-      <c r="AZ7" s="3" t="inlineStr"/>
-      <c r="BA7" s="3" t="inlineStr"/>
-      <c r="BB7" s="3" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="BC7" s="3" t="inlineStr">
+      <c r="AX7" s="4" t="inlineStr"/>
+      <c r="AY7" s="4" t="inlineStr"/>
+      <c r="AZ7" s="4" t="inlineStr"/>
+      <c r="BA7" s="4" t="inlineStr"/>
+      <c r="BB7" s="4" t="inlineStr">
+        <is>
+          <t>ECHO</t>
+        </is>
+      </c>
+      <c r="BC7" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD7" s="3" t="inlineStr"/>
-      <c r="BE7" s="3" t="inlineStr">
-        <is>
-          <t>https://investor.atmeta.com/stock-info/default.aspx</t>
-        </is>
-      </c>
-      <c r="BF7" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="BG7" s="3" t="inlineStr">
-        <is>
-          <t>上市公司</t>
-        </is>
-      </c>
-      <c r="BH7" s="3" t="inlineStr"/>
+      <c r="BD7" s="4" t="inlineStr"/>
+      <c r="BE7" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
+        </is>
+      </c>
+      <c r="BG7" s="4" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH7" s="4" t="inlineStr"/>
+      <c r="BI7" s="4" t="inlineStr"/>
+      <c r="BJ7" s="4" t="inlineStr"/>
+      <c r="BK7" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -7618,22 +8322,22 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>KKR</t>
+          <t>META</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>KKR &amp; Co. Inc. Common Stock</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27T16:35:55+08:00</t>
+          <t>2026-08-27T15:00:00+08:00</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>美股異動丨KKR盤前升2.36% 支付2.5億美元就美司法部併購申報訴訟達成和解</t>
+          <t>Why Meta's settlement could be an 'inflection point' for reining in Big Tech</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr"/>
@@ -7644,7 +8348,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>重大訴訟</t>
+          <t>監管裁罰</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -7654,13 +8358,17 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -7668,7 +8376,11 @@
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr"/>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>0.113</t>
+        </is>
+      </c>
       <c r="P8" s="3" t="inlineStr"/>
       <c r="Q8" s="3" t="inlineStr"/>
       <c r="R8" s="3" t="inlineStr"/>
@@ -7680,12 +8392,12 @@
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t>https://www.gelonghui.com/live/2636223</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNc1pIcnlnRDdhcmNEVDBZMTc0RDJoS1VWSkRfWEk2X3JLSFQ2aDlJb09WeTVKNldkLU9nZllPV2ZqWFByb25pOHB2UENkd1BjcUZHYlVxOHRNYm83eGRFQ3prV1FpNGx1bnJua3JaVkZlMXpKMTY3QWZEMDljbjJKSjF5T0dhaHQtRWFTZ0JyMXNZUWNLODhrb25aX2ZYeC1aXzFZdEdKU2VPdVI4c1JJ?oc=5</t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>KOSU</t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr"/>
@@ -7696,24 +8408,28 @@
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>MAJOR_LITIGATION</t>
+          <t>REGULATORY_PENALTY</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t>訴訟</t>
+          <t>settlement</t>
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr"/>
-      <c r="AB8" s="3" t="inlineStr"/>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>064a2faa2d27491ab78785104fdc78c6</t>
+        </is>
+      </c>
       <c r="AC8" s="3" t="inlineStr">
         <is>
-          <t>c9e9a09ed7123d18d6688519</t>
+          <t>7a7e4ce476373c6d0080ea74</t>
         </is>
       </c>
       <c r="AD8" s="3" t="inlineStr">
         <is>
-          <t>00b3eb0a13584fb6e7e61053</t>
+          <t>4671cc3f133d696f839a80fe</t>
         </is>
       </c>
       <c r="AE8" s="3" t="inlineStr"/>
@@ -7726,7 +8442,11 @@
       <c r="AL8" s="3" t="inlineStr"/>
       <c r="AM8" s="3" t="inlineStr"/>
       <c r="AN8" s="3" t="inlineStr"/>
-      <c r="AO8" s="3" t="inlineStr"/>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP8" s="3" t="inlineStr"/>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr"/>
@@ -7736,7 +8456,7 @@
       <c r="AV8" s="3" t="inlineStr"/>
       <c r="AW8" s="3" t="inlineStr">
         <is>
-          <t>NYSE</t>
+          <t>NASDAQ</t>
         </is>
       </c>
       <c r="AX8" s="3" t="inlineStr"/>
@@ -7745,7 +8465,7 @@
       <c r="BA8" s="3" t="inlineStr"/>
       <c r="BB8" s="3" t="inlineStr">
         <is>
-          <t>KKR</t>
+          <t>META</t>
         </is>
       </c>
       <c r="BC8" s="3" t="inlineStr">
@@ -7756,190 +8476,226 @@
       <c r="BD8" s="3" t="inlineStr"/>
       <c r="BE8" s="3" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+          <t>https://investor.atmeta.com/stock-info/default.aspx</t>
         </is>
       </c>
       <c r="BF8" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="BG8" s="3" t="inlineStr">
         <is>
-          <t>交易所目前名單</t>
+          <t>上市公司</t>
         </is>
       </c>
       <c r="BH8" s="3" t="inlineStr"/>
+      <c r="BI8" s="3" t="inlineStr"/>
+      <c r="BJ8" s="3" t="inlineStr"/>
+      <c r="BK8" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>ECHO</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>EchoStar Corporation</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-27T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>Judge Pérez orders examiner in Hughes Satellite Systems bankruptcy to probe $1.5bn of EchoStar transfers</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>破產</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27T13:14:05+08:00</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Illinois officials, experts react to Meta's social media addiction trial settlement of up to $18B, promised child safety reforms</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>監管裁罰</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="4" t="inlineStr"/>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>0.378</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr"/>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiSEFVX3lxTE1WSDVzVnhJa1NRaWdfOHF3VjRqeEUtYVFQU3JjREFaUVRSMHFqNTFncDFRVGo4Tk1FTWJIc0txbW5jRnNIeXp6WtIB6wFBVV95cUxQNDhrUW9kemFlbnUwMm15UlpnbEI4dzhucjlmakkwbEs0NFFEaWlyRTZMcWxlTmdwZkk3MHN6VXZoZGRXQ1VnUjdISXoxSVFyX01EQ3NpSk8yNXF1YVpBbHdvRDVvX1VNalotSWVEU3hrUjcyTjJwbEtYNFJIV242SmlCVVBobEs5empsNFhHRGdNUjNKRUhsOE5UUERJX3VZbWVTLWJlRi1EcjF0eHFTV3VOVVVRaTdHSW9jLWhCb3JrRGpZUTNUQjZBa0NDTm1mSFI4bDR6QUxGS25SSEZBZGJqUkRsakgtdFln?oc=5</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>ABC7 Chicago</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr"/>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr"/>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>0bbbe195d80d465c997c16efbb786911</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>55872d6a6b59c80d0aeec51f</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr">
+        <is>
+          <t>380f7859ee84a5bc2092c129</t>
+        </is>
+      </c>
+      <c r="AE9" s="3" t="inlineStr"/>
+      <c r="AF9" s="3" t="inlineStr"/>
+      <c r="AG9" s="3" t="inlineStr"/>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr"/>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr"/>
+      <c r="AM9" s="3" t="inlineStr"/>
+      <c r="AN9" s="3" t="inlineStr"/>
+      <c r="AO9" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O9" s="4" t="inlineStr">
-        <is>
-          <t>'-0.563</t>
-        </is>
-      </c>
-      <c r="P9" s="4" t="inlineStr"/>
-      <c r="Q9" s="4" t="inlineStr"/>
-      <c r="R9" s="4" t="inlineStr"/>
-      <c r="S9" s="4" t="inlineStr"/>
-      <c r="T9" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U9" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQcTB2RU9XTlJtWF94V3U5d0JjVnE2RUF0WU1QMVFwRWJuSm9qX01MdWFONXJzS25pUmd3ZF8yT1pOblNPMzNTSGZ5Z0JYbzh4YnNqR1FTcm1YMjloczBxajl2R3VScDZMYl9TN1U5YnZMQzlwYnlieDlDTExpeS14UlV0WTk2SHRrYklkTUh3dVQ3bUNicU9FdFVpM25xUXlIdXNPRjNDaEU?oc=5</t>
-        </is>
-      </c>
-      <c r="V9" s="4" t="inlineStr">
-        <is>
-          <t>9fin</t>
-        </is>
-      </c>
-      <c r="W9" s="4" t="inlineStr"/>
-      <c r="X9" s="4" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y9" s="4" t="inlineStr">
-        <is>
-          <t>BANKRUPTCY</t>
-        </is>
-      </c>
-      <c r="Z9" s="4" t="inlineStr">
-        <is>
-          <t>bankruptcy</t>
-        </is>
-      </c>
-      <c r="AA9" s="4" t="inlineStr"/>
-      <c r="AB9" s="4" t="inlineStr"/>
-      <c r="AC9" s="4" t="inlineStr">
-        <is>
-          <t>89f3b56b12cbc82210c453bf</t>
-        </is>
-      </c>
-      <c r="AD9" s="4" t="inlineStr">
-        <is>
-          <t>598c2ffe45c5df02be123819</t>
-        </is>
-      </c>
-      <c r="AE9" s="4" t="inlineStr"/>
-      <c r="AF9" s="4" t="inlineStr"/>
-      <c r="AG9" s="4" t="inlineStr"/>
-      <c r="AH9" s="4" t="inlineStr"/>
-      <c r="AI9" s="4" t="inlineStr"/>
-      <c r="AJ9" s="4" t="inlineStr"/>
-      <c r="AK9" s="4" t="inlineStr"/>
-      <c r="AL9" s="4" t="inlineStr"/>
-      <c r="AM9" s="4" t="inlineStr"/>
-      <c r="AN9" s="4" t="inlineStr"/>
-      <c r="AO9" s="4" t="inlineStr"/>
-      <c r="AP9" s="4" t="inlineStr"/>
-      <c r="AQ9" s="4" t="inlineStr"/>
-      <c r="AR9" s="4" t="inlineStr"/>
-      <c r="AS9" s="4" t="inlineStr"/>
-      <c r="AT9" s="4" t="inlineStr"/>
-      <c r="AU9" s="4" t="inlineStr"/>
-      <c r="AV9" s="4" t="inlineStr"/>
-      <c r="AW9" s="4" t="inlineStr">
+      <c r="AP9" s="3" t="inlineStr"/>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr"/>
+      <c r="AS9" s="3" t="inlineStr"/>
+      <c r="AT9" s="3" t="inlineStr"/>
+      <c r="AU9" s="3" t="inlineStr"/>
+      <c r="AV9" s="3" t="inlineStr"/>
+      <c r="AW9" s="3" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX9" s="4" t="inlineStr"/>
-      <c r="AY9" s="4" t="inlineStr"/>
-      <c r="AZ9" s="4" t="inlineStr"/>
-      <c r="BA9" s="4" t="inlineStr"/>
-      <c r="BB9" s="4" t="inlineStr">
-        <is>
-          <t>ECHO</t>
-        </is>
-      </c>
-      <c r="BC9" s="4" t="inlineStr">
+      <c r="AX9" s="3" t="inlineStr"/>
+      <c r="AY9" s="3" t="inlineStr"/>
+      <c r="AZ9" s="3" t="inlineStr"/>
+      <c r="BA9" s="3" t="inlineStr"/>
+      <c r="BB9" s="3" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="BC9" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD9" s="4" t="inlineStr"/>
-      <c r="BE9" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF9" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG9" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH9" s="4" t="inlineStr"/>
+      <c r="BD9" s="3" t="inlineStr"/>
+      <c r="BE9" s="3" t="inlineStr">
+        <is>
+          <t>https://investor.atmeta.com/stock-info/default.aspx</t>
+        </is>
+      </c>
+      <c r="BF9" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="BG9" s="3" t="inlineStr">
+        <is>
+          <t>上市公司</t>
+        </is>
+      </c>
+      <c r="BH9" s="3" t="inlineStr"/>
+      <c r="BI9" s="3" t="inlineStr"/>
+      <c r="BJ9" s="3" t="inlineStr"/>
+      <c r="BK9" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -7964,12 +8720,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27T15:00:00+08:00</t>
+          <t>2026-08-27T11:56:26+08:00</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Why Meta's settlement could be an 'inflection point' for reining in Big Tech</t>
+          <t>Father speaks out on Meta’s $18B child safety settlement</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -7990,13 +8746,17 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -8006,7 +8766,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>0.079</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr"/>
@@ -8020,12 +8780,12 @@
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNc1pIcnlnRDdhcmNEVDBZMTc0RDJoS1VWSkRfWEk2X3JLSFQ2aDlJb09WeTVKNldkLU9nZllPV2ZqWFByb25pOHB2UENkd1BjcUZHYlVxOHRNYm83eGRFQ3prV1FpNGx1bnJua3JaVkZlMXpKMTY3QWZEMDljbjJKSjF5T0dhaHQtRWFTZ0JyMXNZUWNLODhrb25aX2ZYeC1aXzFZdEdKU2VPdVI4c1JJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPN1VCOTFyTC0xU0RhYlVadlhjRW42c3hqeTV1NTU5ZWdzbEl4MW9nREhPUXE3MzlESUQ2NzBYVGZ6Y3N3M3YyUFJWVEZKTUhvaVJhVVZpbVYzczcxLWluOUNLRFdHbTlfNTJieF82bi1NS2EtZFo2d1VmVnE5Q3BVcWJENmZWSXdvSkJLall0a3kwdjF1b0U0RG5JdE1oRzZjd29IZHgxYW4?oc=5</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t>KOSU</t>
+          <t>NBC News</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr"/>
@@ -8045,15 +8805,19 @@
         </is>
       </c>
       <c r="AA10" s="3" t="inlineStr"/>
-      <c r="AB10" s="3" t="inlineStr"/>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>810e5ee5c5ba4c5dbd815f16e28d14ee</t>
+        </is>
+      </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
-          <t>7a7e4ce476373c6d0080ea74</t>
+          <t>e429d01b73955f7a13eeeb96</t>
         </is>
       </c>
       <c r="AD10" s="3" t="inlineStr">
         <is>
-          <t>4671cc3f133d696f839a80fe</t>
+          <t>137eb3e610b2f8439aff8007</t>
         </is>
       </c>
       <c r="AE10" s="3" t="inlineStr"/>
@@ -8066,7 +8830,11 @@
       <c r="AL10" s="3" t="inlineStr"/>
       <c r="AM10" s="3" t="inlineStr"/>
       <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP10" s="3" t="inlineStr"/>
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr"/>
@@ -8110,670 +8878,730 @@
         </is>
       </c>
       <c r="BH10" s="3" t="inlineStr"/>
+      <c r="BI10" s="3" t="inlineStr"/>
+      <c r="BJ10" s="3" t="inlineStr"/>
+      <c r="BK10" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Meta Platforms, Inc.</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27T13:14:05+08:00</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>Illinois officials, experts react to Meta's social media addiction trial settlement of up to $18B, promised child safety reforms</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-27T11:08:04+08:00</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Nvidia blowout earnings spur mixed reaction in its Asian supply chain, here’s why:</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>供應鏈中斷</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L11" s="3" t="inlineStr"/>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr">
+      <c r="N11" s="5" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>0.378</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="inlineStr"/>
-      <c r="Q11" s="3" t="inlineStr"/>
-      <c r="R11" s="3" t="inlineStr"/>
-      <c r="S11" s="3" t="inlineStr"/>
-      <c r="T11" s="3" t="inlineStr">
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>'-0.769</t>
+        </is>
+      </c>
+      <c r="P11" s="5" t="inlineStr"/>
+      <c r="Q11" s="5" t="inlineStr"/>
+      <c r="R11" s="5" t="inlineStr"/>
+      <c r="S11" s="5" t="inlineStr"/>
+      <c r="T11" s="5" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U11" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiSEFVX3lxTE1WSDVzVnhJa1NRaWdfOHF3VjRqeEUtYVFQU3JjREFaUVRSMHFqNTFncDFRVGo4Tk1FTWJIc0txbW5jRnNIeXp6WtIB6wFBVV95cUxQNDhrUW9kemFlbnUwMm15UlpnbEI4dzhucjlmakkwbEs0NFFEaWlyRTZMcWxlTmdwZkk3MHN6VXZoZGRXQ1VnUjdISXoxSVFyX01EQ3NpSk8yNXF1YVpBbHdvRDVvX1VNalotSWVEU3hrUjcyTjJwbEtYNFJIV242SmlCVVBobEs5empsNFhHRGdNUjNKRUhsOE5UUERJX3VZbWVTLWJlRi1EcjF0eHFTV3VOVVVRaTdHSW9jLWhCb3JrRGpZUTNUQjZBa0NDTm1mSFI4bDR6QUxGS25SSEZBZGJqUkRsakgtdFln?oc=5</t>
-        </is>
-      </c>
-      <c r="V11" s="3" t="inlineStr">
-        <is>
-          <t>ABC7 Chicago</t>
-        </is>
-      </c>
-      <c r="W11" s="3" t="inlineStr"/>
-      <c r="X11" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z11" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA11" s="3" t="inlineStr"/>
-      <c r="AB11" s="3" t="inlineStr"/>
-      <c r="AC11" s="3" t="inlineStr">
-        <is>
-          <t>55872d6a6b59c80d0aeec51f</t>
-        </is>
-      </c>
-      <c r="AD11" s="3" t="inlineStr">
-        <is>
-          <t>380f7859ee84a5bc2092c129</t>
-        </is>
-      </c>
-      <c r="AE11" s="3" t="inlineStr"/>
-      <c r="AF11" s="3" t="inlineStr"/>
-      <c r="AG11" s="3" t="inlineStr"/>
-      <c r="AH11" s="3" t="inlineStr"/>
-      <c r="AI11" s="3" t="inlineStr"/>
-      <c r="AJ11" s="3" t="inlineStr"/>
-      <c r="AK11" s="3" t="inlineStr"/>
-      <c r="AL11" s="3" t="inlineStr"/>
-      <c r="AM11" s="3" t="inlineStr"/>
-      <c r="AN11" s="3" t="inlineStr"/>
-      <c r="AO11" s="3" t="inlineStr"/>
-      <c r="AP11" s="3" t="inlineStr"/>
-      <c r="AQ11" s="3" t="inlineStr"/>
-      <c r="AR11" s="3" t="inlineStr"/>
-      <c r="AS11" s="3" t="inlineStr"/>
-      <c r="AT11" s="3" t="inlineStr"/>
-      <c r="AU11" s="3" t="inlineStr"/>
-      <c r="AV11" s="3" t="inlineStr"/>
-      <c r="AW11" s="3" t="inlineStr">
+      <c r="U11" s="5" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPaXBDb0R1SWRKampnWV9NTUx3Y0lYZUlDUmpfbmx1TWtIeGUyeWVXelpaZ1hoZHRTT0xUSGhfbUpncmR3dEppakZPUVdJeGZhZ2pCa1NGTk9DNDc1emlzN3ZiemVLZVB3U3BJWUtrSWdXVWxTZVJQdVV1cXNjM19oSHNCMlMxaUY5dU1COWg1VFhoeWhMbmlLRnl3RjJnTzRSWEdUb0pTbVFwRklXaTZSb1N3dGJodWNhdXEzeU1TTmZMYlRFUTlMbFY1c3N2alF2dzQ5U3ZuZmw?oc=5</t>
+        </is>
+      </c>
+      <c r="V11" s="5" t="inlineStr">
+        <is>
+          <t>Investing.com</t>
+        </is>
+      </c>
+      <c r="W11" s="5" t="inlineStr"/>
+      <c r="X11" s="5" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y11" s="5" t="inlineStr">
+        <is>
+          <t>SUPPLY_CHAIN_DISRUPTION</t>
+        </is>
+      </c>
+      <c r="Z11" s="5" t="inlineStr">
+        <is>
+          <t>supply chain</t>
+        </is>
+      </c>
+      <c r="AA11" s="5" t="inlineStr"/>
+      <c r="AB11" s="5" t="inlineStr"/>
+      <c r="AC11" s="5" t="inlineStr">
+        <is>
+          <t>1a7bf279996dd39eba2e70c7</t>
+        </is>
+      </c>
+      <c r="AD11" s="5" t="inlineStr">
+        <is>
+          <t>40915b7abd936cc448ca631c</t>
+        </is>
+      </c>
+      <c r="AE11" s="5" t="inlineStr"/>
+      <c r="AF11" s="5" t="inlineStr"/>
+      <c r="AG11" s="5" t="inlineStr"/>
+      <c r="AH11" s="5" t="inlineStr"/>
+      <c r="AI11" s="5" t="inlineStr"/>
+      <c r="AJ11" s="5" t="inlineStr"/>
+      <c r="AK11" s="5" t="inlineStr"/>
+      <c r="AL11" s="5" t="inlineStr"/>
+      <c r="AM11" s="5" t="inlineStr"/>
+      <c r="AN11" s="5" t="inlineStr"/>
+      <c r="AO11" s="5" t="inlineStr"/>
+      <c r="AP11" s="5" t="inlineStr"/>
+      <c r="AQ11" s="5" t="inlineStr"/>
+      <c r="AR11" s="5" t="inlineStr"/>
+      <c r="AS11" s="5" t="inlineStr"/>
+      <c r="AT11" s="5" t="inlineStr"/>
+      <c r="AU11" s="5" t="inlineStr"/>
+      <c r="AV11" s="5" t="inlineStr"/>
+      <c r="AW11" s="5" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX11" s="3" t="inlineStr"/>
-      <c r="AY11" s="3" t="inlineStr"/>
-      <c r="AZ11" s="3" t="inlineStr"/>
-      <c r="BA11" s="3" t="inlineStr"/>
-      <c r="BB11" s="3" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="BC11" s="3" t="inlineStr">
+      <c r="AX11" s="5" t="inlineStr"/>
+      <c r="AY11" s="5" t="inlineStr"/>
+      <c r="AZ11" s="5" t="inlineStr"/>
+      <c r="BA11" s="5" t="inlineStr"/>
+      <c r="BB11" s="5" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="BC11" s="5" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD11" s="3" t="inlineStr"/>
-      <c r="BE11" s="3" t="inlineStr">
-        <is>
-          <t>https://investor.atmeta.com/stock-info/default.aspx</t>
-        </is>
-      </c>
-      <c r="BF11" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="BG11" s="3" t="inlineStr">
-        <is>
-          <t>上市公司</t>
-        </is>
-      </c>
-      <c r="BH11" s="3" t="inlineStr"/>
+      <c r="BD11" s="5" t="inlineStr"/>
+      <c r="BE11" s="5" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF11" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
+        </is>
+      </c>
+      <c r="BG11" s="5" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH11" s="5" t="inlineStr"/>
+      <c r="BI11" s="5" t="inlineStr"/>
+      <c r="BJ11" s="5" t="inlineStr"/>
+      <c r="BK11" s="5" t="inlineStr"/>
+      <c r="BL11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Meta Platforms, Inc.</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27T11:56:26+08:00</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Father speaks out on Meta’s $18B child safety settlement</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr"/>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>T-Mobile US</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-27T10:36:59+08:00</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>T-Mobile計劃在華盛頓州裁員並關閉多個網點</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>裁員或人力縮減</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L12" s="3" t="inlineStr"/>
-      <c r="M12" s="3" t="inlineStr">
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>待人工覆核</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N12" s="3" t="inlineStr">
+      <c r="N12" s="5" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>0.079</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="inlineStr"/>
-      <c r="Q12" s="3" t="inlineStr"/>
-      <c r="R12" s="3" t="inlineStr"/>
-      <c r="S12" s="3" t="inlineStr"/>
-      <c r="T12" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U12" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPN1VCOTFyTC0xU0RhYlVadlhjRW42c3hqeTV1NTU5ZWdzbEl4MW9nREhPUXE3MzlESUQ2NzBYVGZ6Y3N3M3YyUFJWVEZKTUhvaVJhVVZpbVYzczcxLWluOUNLRFdHbTlfNTJieF82bi1NS2EtZFo2d1VmVnE5Q3BVcWJENmZWSXdvSkJLall0a3kwdjF1b0U0RG5JdE1oRzZjd29IZHgxYW4?oc=5</t>
-        </is>
-      </c>
-      <c r="V12" s="3" t="inlineStr">
-        <is>
-          <t>NBC News</t>
-        </is>
-      </c>
-      <c r="W12" s="3" t="inlineStr"/>
-      <c r="X12" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z12" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA12" s="3" t="inlineStr"/>
-      <c r="AB12" s="3" t="inlineStr"/>
-      <c r="AC12" s="3" t="inlineStr">
-        <is>
-          <t>e429d01b73955f7a13eeeb96</t>
-        </is>
-      </c>
-      <c r="AD12" s="3" t="inlineStr">
-        <is>
-          <t>137eb3e610b2f8439aff8007</t>
-        </is>
-      </c>
-      <c r="AE12" s="3" t="inlineStr"/>
-      <c r="AF12" s="3" t="inlineStr"/>
-      <c r="AG12" s="3" t="inlineStr"/>
-      <c r="AH12" s="3" t="inlineStr"/>
-      <c r="AI12" s="3" t="inlineStr"/>
-      <c r="AJ12" s="3" t="inlineStr"/>
-      <c r="AK12" s="3" t="inlineStr"/>
-      <c r="AL12" s="3" t="inlineStr"/>
-      <c r="AM12" s="3" t="inlineStr"/>
-      <c r="AN12" s="3" t="inlineStr"/>
-      <c r="AO12" s="3" t="inlineStr"/>
-      <c r="AP12" s="3" t="inlineStr"/>
-      <c r="AQ12" s="3" t="inlineStr"/>
-      <c r="AR12" s="3" t="inlineStr"/>
-      <c r="AS12" s="3" t="inlineStr"/>
-      <c r="AT12" s="3" t="inlineStr"/>
-      <c r="AU12" s="3" t="inlineStr"/>
-      <c r="AV12" s="3" t="inlineStr"/>
-      <c r="AW12" s="3" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX12" s="3" t="inlineStr"/>
-      <c r="AY12" s="3" t="inlineStr"/>
-      <c r="AZ12" s="3" t="inlineStr"/>
-      <c r="BA12" s="3" t="inlineStr"/>
-      <c r="BB12" s="3" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="BC12" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD12" s="3" t="inlineStr"/>
-      <c r="BE12" s="3" t="inlineStr">
-        <is>
-          <t>https://investor.atmeta.com/stock-info/default.aspx</t>
-        </is>
-      </c>
-      <c r="BF12" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="BG12" s="3" t="inlineStr">
-        <is>
-          <t>上市公司</t>
-        </is>
-      </c>
-      <c r="BH12" s="3" t="inlineStr"/>
+      <c r="O12" s="5" t="inlineStr"/>
+      <c r="P12" s="5" t="inlineStr"/>
+      <c r="Q12" s="5" t="inlineStr"/>
+      <c r="R12" s="5" t="inlineStr"/>
+      <c r="S12" s="5" t="inlineStr"/>
+      <c r="T12" s="5" t="inlineStr">
+        <is>
+          <t>公司名稱／股票代號歧義</t>
+        </is>
+      </c>
+      <c r="U12" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gelonghui.com/live/2635509</t>
+        </is>
+      </c>
+      <c r="V12" s="5" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W12" s="5" t="inlineStr"/>
+      <c r="X12" s="5" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y12" s="5" t="inlineStr">
+        <is>
+          <t>WORKFORCE_REDUCTION</t>
+        </is>
+      </c>
+      <c r="Z12" s="5" t="inlineStr">
+        <is>
+          <t>裁員</t>
+        </is>
+      </c>
+      <c r="AA12" s="5" t="inlineStr"/>
+      <c r="AB12" s="5" t="inlineStr"/>
+      <c r="AC12" s="5" t="inlineStr">
+        <is>
+          <t>a66028331c9d1c3dec9371f4</t>
+        </is>
+      </c>
+      <c r="AD12" s="5" t="inlineStr">
+        <is>
+          <t>69306eed6362ccd5aad985fc</t>
+        </is>
+      </c>
+      <c r="AE12" s="5" t="inlineStr"/>
+      <c r="AF12" s="5" t="inlineStr"/>
+      <c r="AG12" s="5" t="inlineStr"/>
+      <c r="AH12" s="5" t="inlineStr"/>
+      <c r="AI12" s="5" t="inlineStr"/>
+      <c r="AJ12" s="5" t="inlineStr"/>
+      <c r="AK12" s="5" t="inlineStr"/>
+      <c r="AL12" s="5" t="inlineStr"/>
+      <c r="AM12" s="5" t="inlineStr"/>
+      <c r="AN12" s="5" t="inlineStr"/>
+      <c r="AO12" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AP12" s="5" t="inlineStr"/>
+      <c r="AQ12" s="5" t="inlineStr"/>
+      <c r="AR12" s="5" t="inlineStr"/>
+      <c r="AS12" s="5" t="inlineStr"/>
+      <c r="AT12" s="5" t="inlineStr"/>
+      <c r="AU12" s="5" t="inlineStr"/>
+      <c r="AV12" s="5" t="inlineStr"/>
+      <c r="AW12" s="5" t="inlineStr"/>
+      <c r="AX12" s="5" t="inlineStr"/>
+      <c r="AY12" s="5" t="inlineStr"/>
+      <c r="AZ12" s="5" t="inlineStr"/>
+      <c r="BA12" s="5" t="inlineStr"/>
+      <c r="BB12" s="5" t="inlineStr">
+        <is>
+          <t>TMUS</t>
+        </is>
+      </c>
+      <c r="BC12" s="5" t="inlineStr">
+        <is>
+          <t>公司名稱／股票代號歧義</t>
+        </is>
+      </c>
+      <c r="BD12" s="5" t="inlineStr"/>
+      <c r="BE12" s="5" t="inlineStr"/>
+      <c r="BF12" s="5" t="inlineStr"/>
+      <c r="BG12" s="5" t="inlineStr"/>
+      <c r="BH12" s="5" t="inlineStr"/>
+      <c r="BI12" s="5" t="inlineStr"/>
+      <c r="BJ12" s="5" t="inlineStr"/>
+      <c r="BK12" s="5" t="inlineStr"/>
+      <c r="BL12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>NVIDIA Corporation</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-27T11:08:04+08:00</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>Nvidia blowout earnings spur mixed reaction in its Asian supply chain, here’s why:</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr"/>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L13" s="5" t="inlineStr"/>
-      <c r="M13" s="5" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27T09:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Landmark settlement agreement with META</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>監管裁罰</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>0.694</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr"/>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQVE5XWkRKckFwRk1HWmc0WlhxbzRZVlNCc3docC0tVF9EbGNnUVpmRk40RXBWUmt5YVZ1NjN1Qk1nTUlrSFFMYXdqYmwyeUN4RWZVektWMlJkSDFwa19OOHVDaEtvTzZrcHRpMDRQVUlrVU1pcHpsb21mejVXSU5RUlVyZTBYbEZ2bFFjNmR0YkNCUWlqbDFvT1V4aDNUMGpmSWJKUkJYNkozbnNyWUhtN0ZBOWI?oc=5</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>KXLY.com</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr"/>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr"/>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>832797d648cf412aadc3fea1aca57fb8</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>39e351ac93b9ef965a0173b9</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr">
+        <is>
+          <t>60fc635434635081cf5136dd</t>
+        </is>
+      </c>
+      <c r="AE13" s="3" t="inlineStr"/>
+      <c r="AF13" s="3" t="inlineStr"/>
+      <c r="AG13" s="3" t="inlineStr"/>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr"/>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr"/>
+      <c r="AM13" s="3" t="inlineStr"/>
+      <c r="AN13" s="3" t="inlineStr"/>
+      <c r="AO13" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N13" s="5" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O13" s="5" t="inlineStr">
-        <is>
-          <t>'-0.769</t>
-        </is>
-      </c>
-      <c r="P13" s="5" t="inlineStr"/>
-      <c r="Q13" s="5" t="inlineStr"/>
-      <c r="R13" s="5" t="inlineStr"/>
-      <c r="S13" s="5" t="inlineStr"/>
-      <c r="T13" s="5" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U13" s="5" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPaXBDb0R1SWRKampnWV9NTUx3Y0lYZUlDUmpfbmx1TWtIeGUyeWVXelpaZ1hoZHRTT0xUSGhfbUpncmR3dEppakZPUVdJeGZhZ2pCa1NGTk9DNDc1emlzN3ZiemVLZVB3U3BJWUtrSWdXVWxTZVJQdVV1cXNjM19oSHNCMlMxaUY5dU1COWg1VFhoeWhMbmlLRnl3RjJnTzRSWEdUb0pTbVFwRklXaTZSb1N3dGJodWNhdXEzeU1TTmZMYlRFUTlMbFY1c3N2alF2dzQ5U3ZuZmw?oc=5</t>
-        </is>
-      </c>
-      <c r="V13" s="5" t="inlineStr">
-        <is>
-          <t>Investing.com</t>
-        </is>
-      </c>
-      <c r="W13" s="5" t="inlineStr"/>
-      <c r="X13" s="5" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y13" s="5" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z13" s="5" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA13" s="5" t="inlineStr"/>
-      <c r="AB13" s="5" t="inlineStr"/>
-      <c r="AC13" s="5" t="inlineStr">
-        <is>
-          <t>1a7bf279996dd39eba2e70c7</t>
-        </is>
-      </c>
-      <c r="AD13" s="5" t="inlineStr">
-        <is>
-          <t>40915b7abd936cc448ca631c</t>
-        </is>
-      </c>
-      <c r="AE13" s="5" t="inlineStr"/>
-      <c r="AF13" s="5" t="inlineStr"/>
-      <c r="AG13" s="5" t="inlineStr"/>
-      <c r="AH13" s="5" t="inlineStr"/>
-      <c r="AI13" s="5" t="inlineStr"/>
-      <c r="AJ13" s="5" t="inlineStr"/>
-      <c r="AK13" s="5" t="inlineStr"/>
-      <c r="AL13" s="5" t="inlineStr"/>
-      <c r="AM13" s="5" t="inlineStr"/>
-      <c r="AN13" s="5" t="inlineStr"/>
-      <c r="AO13" s="5" t="inlineStr"/>
-      <c r="AP13" s="5" t="inlineStr"/>
-      <c r="AQ13" s="5" t="inlineStr"/>
-      <c r="AR13" s="5" t="inlineStr"/>
-      <c r="AS13" s="5" t="inlineStr"/>
-      <c r="AT13" s="5" t="inlineStr"/>
-      <c r="AU13" s="5" t="inlineStr"/>
-      <c r="AV13" s="5" t="inlineStr"/>
-      <c r="AW13" s="5" t="inlineStr">
+      <c r="AP13" s="3" t="inlineStr"/>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr"/>
+      <c r="AS13" s="3" t="inlineStr"/>
+      <c r="AT13" s="3" t="inlineStr"/>
+      <c r="AU13" s="3" t="inlineStr"/>
+      <c r="AV13" s="3" t="inlineStr"/>
+      <c r="AW13" s="3" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX13" s="5" t="inlineStr"/>
-      <c r="AY13" s="5" t="inlineStr"/>
-      <c r="AZ13" s="5" t="inlineStr"/>
-      <c r="BA13" s="5" t="inlineStr"/>
-      <c r="BB13" s="5" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="BC13" s="5" t="inlineStr">
+      <c r="AX13" s="3" t="inlineStr"/>
+      <c r="AY13" s="3" t="inlineStr"/>
+      <c r="AZ13" s="3" t="inlineStr"/>
+      <c r="BA13" s="3" t="inlineStr"/>
+      <c r="BB13" s="3" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="BC13" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD13" s="5" t="inlineStr"/>
-      <c r="BE13" s="5" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF13" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG13" s="5" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH13" s="5" t="inlineStr"/>
+      <c r="BD13" s="3" t="inlineStr"/>
+      <c r="BE13" s="3" t="inlineStr">
+        <is>
+          <t>https://investor.atmeta.com/stock-info/default.aspx</t>
+        </is>
+      </c>
+      <c r="BF13" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="BG13" s="3" t="inlineStr">
+        <is>
+          <t>上市公司</t>
+        </is>
+      </c>
+      <c r="BH13" s="3" t="inlineStr"/>
+      <c r="BI13" s="3" t="inlineStr"/>
+      <c r="BJ13" s="3" t="inlineStr"/>
+      <c r="BK13" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL13" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr"/>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>T-Mobile US</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-27T10:36:59+08:00</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>T-Mobile計劃在華盛頓州裁員並關閉多個網點</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr"/>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L14" s="5" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M14" s="5" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>PNR</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Pentair</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27T07:55:00+08:00</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>PNR INVESTOR DEADLINE: Robbins Geller Rudman &amp; Dowd LLP Files Class Action Lawsuit Against Pentair plc and Announces Opportunity for Investors with Substantial Losses to Lead the Pentair Class Action Lawsuit</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>0.003</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr"/>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi-AJBVV95cUxOdjZZemJ1VDJ0emtGZVd1ZzBOZVlaclFuMHpaNHZwTXIxVDVfZlZUVUZKQzIzX2x0Q3l3RUZaa1g0VDYwcW5EbmQ5czlEenVvdHhNLVVqbkowQjlCQ2s3X18yU0pvczU3eHFuYUZkaVJ3N2FxTlVFaUkxTzJQXzc0NGxSRUtTZkR4MzdDUVNhZlRzdFUtVmUxMm45bWp2WE9vTGRLSWk3Z1JXS2QxZGROaWRCWUpuUmpQRk5tWUhGaE95UWJNZzVvMW1reGhJOWVibGhkZnB3eEljd0ZGaEllNExzNUIxSGtZemVEdFBDZ184M3luMmRWS2theEQyQVVYT0JPNnVvdUVuc2VsUDg5blZwMTFZWGU2VHdTLWFsSm1fRGFBdGpLUFV0Mm5sYTZyMGh2WTRPM2RteHZNR3Y3STJyYUtOdExGUG9sZWlsTEpTaFJ5TXRNTU4yX2xlN2JKM1dVMVNVTlFBS3RDS0FVRDctV3loRzR0?oc=5</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>prnewswire.com</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr"/>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>class action</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr"/>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>844e78ec07bb4e12a544fa2235bc541e</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr">
+        <is>
+          <t>227a7f932a6bb9d768ff6fd1</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr">
+        <is>
+          <t>df17447d9bc471f1391300cd</t>
+        </is>
+      </c>
+      <c r="AE14" s="3" t="inlineStr"/>
+      <c r="AF14" s="3" t="inlineStr"/>
+      <c r="AG14" s="3" t="inlineStr"/>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr"/>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr"/>
+      <c r="AM14" s="3" t="inlineStr"/>
+      <c r="AN14" s="3" t="inlineStr"/>
+      <c r="AO14" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N14" s="5" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O14" s="5" t="inlineStr"/>
-      <c r="P14" s="5" t="inlineStr"/>
-      <c r="Q14" s="5" t="inlineStr"/>
-      <c r="R14" s="5" t="inlineStr"/>
-      <c r="S14" s="5" t="inlineStr"/>
-      <c r="T14" s="5" t="inlineStr">
-        <is>
-          <t>公司名稱／股票代號歧義</t>
-        </is>
-      </c>
-      <c r="U14" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/live/2635509</t>
-        </is>
-      </c>
-      <c r="V14" s="5" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W14" s="5" t="inlineStr"/>
-      <c r="X14" s="5" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y14" s="5" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z14" s="5" t="inlineStr">
-        <is>
-          <t>裁員</t>
-        </is>
-      </c>
-      <c r="AA14" s="5" t="inlineStr"/>
-      <c r="AB14" s="5" t="inlineStr"/>
-      <c r="AC14" s="5" t="inlineStr">
-        <is>
-          <t>a66028331c9d1c3dec9371f4</t>
-        </is>
-      </c>
-      <c r="AD14" s="5" t="inlineStr">
-        <is>
-          <t>69306eed6362ccd5aad985fc</t>
-        </is>
-      </c>
-      <c r="AE14" s="5" t="inlineStr"/>
-      <c r="AF14" s="5" t="inlineStr"/>
-      <c r="AG14" s="5" t="inlineStr"/>
-      <c r="AH14" s="5" t="inlineStr"/>
-      <c r="AI14" s="5" t="inlineStr"/>
-      <c r="AJ14" s="5" t="inlineStr"/>
-      <c r="AK14" s="5" t="inlineStr"/>
-      <c r="AL14" s="5" t="inlineStr"/>
-      <c r="AM14" s="5" t="inlineStr"/>
-      <c r="AN14" s="5" t="inlineStr"/>
-      <c r="AO14" s="5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP14" s="5" t="inlineStr"/>
-      <c r="AQ14" s="5" t="inlineStr"/>
-      <c r="AR14" s="5" t="inlineStr"/>
-      <c r="AS14" s="5" t="inlineStr"/>
-      <c r="AT14" s="5" t="inlineStr"/>
-      <c r="AU14" s="5" t="inlineStr"/>
-      <c r="AV14" s="5" t="inlineStr"/>
-      <c r="AW14" s="5" t="inlineStr"/>
-      <c r="AX14" s="5" t="inlineStr"/>
-      <c r="AY14" s="5" t="inlineStr"/>
-      <c r="AZ14" s="5" t="inlineStr"/>
-      <c r="BA14" s="5" t="inlineStr"/>
-      <c r="BB14" s="5" t="inlineStr">
-        <is>
-          <t>TMUS</t>
-        </is>
-      </c>
-      <c r="BC14" s="5" t="inlineStr">
-        <is>
-          <t>公司名稱／股票代號歧義</t>
-        </is>
-      </c>
-      <c r="BD14" s="5" t="inlineStr"/>
-      <c r="BE14" s="5" t="inlineStr"/>
-      <c r="BF14" s="5" t="inlineStr"/>
-      <c r="BG14" s="5" t="inlineStr"/>
-      <c r="BH14" s="5" t="inlineStr"/>
+      <c r="AP14" s="3" t="inlineStr"/>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr"/>
+      <c r="AS14" s="3" t="inlineStr"/>
+      <c r="AT14" s="3" t="inlineStr"/>
+      <c r="AU14" s="3" t="inlineStr"/>
+      <c r="AV14" s="3" t="inlineStr"/>
+      <c r="AW14" s="3" t="inlineStr"/>
+      <c r="AX14" s="3" t="inlineStr"/>
+      <c r="AY14" s="3" t="inlineStr"/>
+      <c r="AZ14" s="3" t="inlineStr"/>
+      <c r="BA14" s="3" t="inlineStr"/>
+      <c r="BB14" s="3" t="inlineStr">
+        <is>
+          <t>PNR</t>
+        </is>
+      </c>
+      <c r="BC14" s="3" t="inlineStr">
+        <is>
+          <t>已核對</t>
+        </is>
+      </c>
+      <c r="BD14" s="3" t="inlineStr"/>
+      <c r="BE14" s="3" t="inlineStr">
+        <is>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF14" s="3" t="inlineStr"/>
+      <c r="BG14" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／交易所參照</t>
+        </is>
+      </c>
+      <c r="BH14" s="3" t="inlineStr"/>
+      <c r="BI14" s="3" t="inlineStr"/>
+      <c r="BJ14" s="3" t="inlineStr"/>
+      <c r="BK14" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL14" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -8788,22 +9616,22 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>KKR</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>KKR &amp; Co. Inc. Common Stock</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27T09:20:00+08:00</t>
+          <t>2026-08-27T07:25:13+08:00</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Landmark settlement agreement with META</t>
+          <t>KKR將支付2.5億美元了結司法部併購申報訴訟</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr"/>
@@ -8824,13 +9652,17 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
@@ -8838,11 +9670,7 @@
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>0.694</t>
-        </is>
-      </c>
+      <c r="O15" s="3" t="inlineStr"/>
       <c r="P15" s="3" t="inlineStr"/>
       <c r="Q15" s="3" t="inlineStr"/>
       <c r="R15" s="3" t="inlineStr"/>
@@ -8854,12 +9682,12 @@
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQVE5XWkRKckFwRk1HWmc0WlhxbzRZVlNCc3docC0tVF9EbGNnUVpmRk40RXBWUmt5YVZ1NjN1Qk1nTUlrSFFMYXdqYmwyeUN4RWZVektWMlJkSDFwa19OOHVDaEtvTzZrcHRpMDRQVUlrVU1pcHpsb21mejVXSU5RUlVyZTBYbEZ2bFFjNmR0YkNCUWlqbDFvT1V4aDNUMGpmSWJKUkJYNkozbnNyWUhtN0ZBOWI?oc=5</t>
+          <t>https://www.gelonghui.com/live/2635016</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t>KXLY.com</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr"/>
@@ -8875,19 +9703,23 @@
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t>settlement</t>
+          <t>訴訟</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr"/>
-      <c r="AB15" s="3" t="inlineStr"/>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>1aa3debf05bb46d1b5430dfa9909b986</t>
+        </is>
+      </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>39e351ac93b9ef965a0173b9</t>
+          <t>41638baa3e96be115a8cb4a0</t>
         </is>
       </c>
       <c r="AD15" s="3" t="inlineStr">
         <is>
-          <t>60fc635434635081cf5136dd</t>
+          <t>da1b0f5d42dae22f74977dfa</t>
         </is>
       </c>
       <c r="AE15" s="3" t="inlineStr"/>
@@ -8900,7 +9732,11 @@
       <c r="AL15" s="3" t="inlineStr"/>
       <c r="AM15" s="3" t="inlineStr"/>
       <c r="AN15" s="3" t="inlineStr"/>
-      <c r="AO15" s="3" t="inlineStr"/>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP15" s="3" t="inlineStr"/>
       <c r="AQ15" s="3" t="inlineStr"/>
       <c r="AR15" s="3" t="inlineStr"/>
@@ -8910,7 +9746,7 @@
       <c r="AV15" s="3" t="inlineStr"/>
       <c r="AW15" s="3" t="inlineStr">
         <is>
-          <t>NASDAQ</t>
+          <t>NYSE</t>
         </is>
       </c>
       <c r="AX15" s="3" t="inlineStr"/>
@@ -8919,7 +9755,7 @@
       <c r="BA15" s="3" t="inlineStr"/>
       <c r="BB15" s="3" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>KKR</t>
         </is>
       </c>
       <c r="BC15" s="3" t="inlineStr">
@@ -8930,20 +9766,36 @@
       <c r="BD15" s="3" t="inlineStr"/>
       <c r="BE15" s="3" t="inlineStr">
         <is>
-          <t>https://investor.atmeta.com/stock-info/default.aspx</t>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
       <c r="BF15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
       <c r="BG15" s="3" t="inlineStr">
         <is>
-          <t>上市公司</t>
+          <t>交易所目前名單</t>
         </is>
       </c>
       <c r="BH15" s="3" t="inlineStr"/>
+      <c r="BI15" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ15" s="3" t="inlineStr"/>
+      <c r="BK15" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL15" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -8958,22 +9810,22 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>PNR</t>
+          <t>META</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Pentair</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27T07:55:00+08:00</t>
+          <t>2026-08-27T05:15:00+08:00</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>PNR INVESTOR DEADLINE: Robbins Geller Rudman &amp; Dowd LLP Files Class Action Lawsuit Against Pentair plc and Announces Opportunity for Investors with Substantial Losses to Lead the Pentair Class Action Lawsuit</t>
+          <t>Meta reaches landmark $18 billion settlement with states in trial over teen social media addiction</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr"/>
@@ -8984,7 +9836,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>重大訴訟</t>
+          <t>監管裁罰</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -8994,13 +9846,17 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -9010,7 +9866,7 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>'-0.184</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr"/>
@@ -9024,12 +9880,12 @@
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AJBVV95cUxOdjZZemJ1VDJ0emtGZVd1ZzBOZVlaclFuMHpaNHZwTXIxVDVfZlZUVUZKQzIzX2x0Q3l3RUZaa1g0VDYwcW5EbmQ5czlEenVvdHhNLVVqbkowQjlCQ2s3X18yU0pvczU3eHFuYUZkaVJ3N2FxTlVFaUkxTzJQXzc0NGxSRUtTZkR4MzdDUVNhZlRzdFUtVmUxMm45bWp2WE9vTGRLSWk3Z1JXS2QxZGROaWRCWUpuUmpQRk5tWUhGaE95UWJNZzVvMW1reGhJOWVibGhkZnB3eEljd0ZGaEllNExzNUIxSGtZemVEdFBDZ184M3luMmRWS2theEQyQVVYT0JPNnVvdUVuc2VsUDg5blZwMTFZWGU2VHdTLWFsSm1fRGFBdGpLUFV0Mm5sYTZyMGh2WTRPM2RteHZNR3Y3STJyYUtOdExGUG9sZWlsTEpTaFJ5TXRNTU4yX2xlN2JKM1dVMVNVTlFBS3RDS0FVRDctV3loRzR0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNMlhBT1Zvb1ZRZFhDYmpQdzhKVlJ3LXFEb1VUby1ZR0xZQnp3LTdwY2E2UWFzVy1sbHRUWTJXM0VaeVRZRnJFdjZUS3c3Q3V4VzdXYW1KeXRIT0JGZmFLeE1iNklXQkdZdmxmVnB3bnpGZ1V0bUpGSGZiZjF1c01FcU5zd3NCblNzSU9RRnR4OGNNdGpSRmc?oc=5</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t>prnewswire.com</t>
+          <t>AP News</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr"/>
@@ -9040,24 +9896,28 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>MAJOR_LITIGATION</t>
+          <t>REGULATORY_PENALTY</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t>class action</t>
+          <t>settlement</t>
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr"/>
-      <c r="AB16" s="3" t="inlineStr"/>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>c15c1b53295b47a7aa47af0c95dcdceb</t>
+        </is>
+      </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>227a7f932a6bb9d768ff6fd1</t>
+          <t>4441b880142ef32d3285eafd</t>
         </is>
       </c>
       <c r="AD16" s="3" t="inlineStr">
         <is>
-          <t>df17447d9bc471f1391300cd</t>
+          <t>2b0eb5bbbe871ecbf264a7df</t>
         </is>
       </c>
       <c r="AE16" s="3" t="inlineStr"/>
@@ -9070,7 +9930,11 @@
       <c r="AL16" s="3" t="inlineStr"/>
       <c r="AM16" s="3" t="inlineStr"/>
       <c r="AN16" s="3" t="inlineStr"/>
-      <c r="AO16" s="3" t="inlineStr"/>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP16" s="3" t="inlineStr"/>
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr"/>
@@ -9078,14 +9942,18 @@
       <c r="AT16" s="3" t="inlineStr"/>
       <c r="AU16" s="3" t="inlineStr"/>
       <c r="AV16" s="3" t="inlineStr"/>
-      <c r="AW16" s="3" t="inlineStr"/>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
       <c r="AX16" s="3" t="inlineStr"/>
       <c r="AY16" s="3" t="inlineStr"/>
       <c r="AZ16" s="3" t="inlineStr"/>
       <c r="BA16" s="3" t="inlineStr"/>
       <c r="BB16" s="3" t="inlineStr">
         <is>
-          <t>PNR</t>
+          <t>META</t>
         </is>
       </c>
       <c r="BC16" s="3" t="inlineStr">
@@ -9096,182 +9964,206 @@
       <c r="BD16" s="3" t="inlineStr"/>
       <c r="BE16" s="3" t="inlineStr">
         <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF16" s="3" t="inlineStr"/>
+          <t>https://investor.atmeta.com/stock-info/default.aspx</t>
+        </is>
+      </c>
+      <c r="BF16" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
       <c r="BG16" s="3" t="inlineStr">
         <is>
-          <t>公司清單／交易所參照</t>
+          <t>上市公司</t>
         </is>
       </c>
       <c r="BH16" s="3" t="inlineStr"/>
+      <c r="BI16" s="3" t="inlineStr"/>
+      <c r="BJ16" s="3" t="inlineStr"/>
+      <c r="BK16" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL16" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>KKR</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>KKR &amp; Co. Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27T07:25:13+08:00</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>KKR將支付2.5億美元了結司法部併購申報訴訟</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>FDX</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>FedEx Corporation Common Stock</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-27T03:48:16+08:00</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>FedEx Cup playoffs: What to watch over the next three weeks, including Ryder Cup spots</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>裁員或人力縮減</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L17" s="3" t="inlineStr"/>
-      <c r="M17" s="3" t="inlineStr">
+      <c r="L17" s="5" t="inlineStr"/>
+      <c r="M17" s="5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N17" s="3" t="inlineStr">
+      <c r="N17" s="5" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr"/>
-      <c r="P17" s="3" t="inlineStr"/>
-      <c r="Q17" s="3" t="inlineStr"/>
-      <c r="R17" s="3" t="inlineStr"/>
-      <c r="S17" s="3" t="inlineStr"/>
-      <c r="T17" s="3" t="inlineStr">
+      <c r="O17" s="5" t="inlineStr">
+        <is>
+          <t>'-0.004</t>
+        </is>
+      </c>
+      <c r="P17" s="5" t="inlineStr"/>
+      <c r="Q17" s="5" t="inlineStr"/>
+      <c r="R17" s="5" t="inlineStr"/>
+      <c r="S17" s="5" t="inlineStr"/>
+      <c r="T17" s="5" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U17" s="3" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/live/2635016</t>
-        </is>
-      </c>
-      <c r="V17" s="3" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W17" s="3" t="inlineStr"/>
-      <c r="X17" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y17" s="3" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z17" s="3" t="inlineStr">
-        <is>
-          <t>訴訟</t>
-        </is>
-      </c>
-      <c r="AA17" s="3" t="inlineStr"/>
-      <c r="AB17" s="3" t="inlineStr"/>
-      <c r="AC17" s="3" t="inlineStr">
-        <is>
-          <t>41638baa3e96be115a8cb4a0</t>
-        </is>
-      </c>
-      <c r="AD17" s="3" t="inlineStr">
-        <is>
-          <t>da1b0f5d42dae22f74977dfa</t>
-        </is>
-      </c>
-      <c r="AE17" s="3" t="inlineStr"/>
-      <c r="AF17" s="3" t="inlineStr"/>
-      <c r="AG17" s="3" t="inlineStr"/>
-      <c r="AH17" s="3" t="inlineStr"/>
-      <c r="AI17" s="3" t="inlineStr"/>
-      <c r="AJ17" s="3" t="inlineStr"/>
-      <c r="AK17" s="3" t="inlineStr"/>
-      <c r="AL17" s="3" t="inlineStr"/>
-      <c r="AM17" s="3" t="inlineStr"/>
-      <c r="AN17" s="3" t="inlineStr"/>
-      <c r="AO17" s="3" t="inlineStr"/>
-      <c r="AP17" s="3" t="inlineStr"/>
-      <c r="AQ17" s="3" t="inlineStr"/>
-      <c r="AR17" s="3" t="inlineStr"/>
-      <c r="AS17" s="3" t="inlineStr"/>
-      <c r="AT17" s="3" t="inlineStr"/>
-      <c r="AU17" s="3" t="inlineStr"/>
-      <c r="AV17" s="3" t="inlineStr"/>
-      <c r="AW17" s="3" t="inlineStr">
+      <c r="U17" s="5" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE03cUtKcjNZX0F4OFBnVVlKbkdXVW5pZ2JJaEtlSVlpTmRzOVl2N3JWSFdXcUFxd2dOSDBBN2gtWHJWUjRVY3pMdVlQUDVSUzdpZEhmOW5TMWkxc0E?oc=5</t>
+        </is>
+      </c>
+      <c r="V17" s="5" t="inlineStr">
+        <is>
+          <t>ESPN</t>
+        </is>
+      </c>
+      <c r="W17" s="5" t="inlineStr"/>
+      <c r="X17" s="5" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y17" s="5" t="inlineStr">
+        <is>
+          <t>WORKFORCE_REDUCTION</t>
+        </is>
+      </c>
+      <c r="Z17" s="5" t="inlineStr">
+        <is>
+          <t>layoff；layoffs</t>
+        </is>
+      </c>
+      <c r="AA17" s="5" t="inlineStr"/>
+      <c r="AB17" s="5" t="inlineStr"/>
+      <c r="AC17" s="5" t="inlineStr">
+        <is>
+          <t>4983f82dd60dacc31d2b65da</t>
+        </is>
+      </c>
+      <c r="AD17" s="5" t="inlineStr">
+        <is>
+          <t>ce7b96e947cb336b8f02e89d</t>
+        </is>
+      </c>
+      <c r="AE17" s="5" t="inlineStr"/>
+      <c r="AF17" s="5" t="inlineStr"/>
+      <c r="AG17" s="5" t="inlineStr"/>
+      <c r="AH17" s="5" t="inlineStr"/>
+      <c r="AI17" s="5" t="inlineStr"/>
+      <c r="AJ17" s="5" t="inlineStr"/>
+      <c r="AK17" s="5" t="inlineStr"/>
+      <c r="AL17" s="5" t="inlineStr"/>
+      <c r="AM17" s="5" t="inlineStr"/>
+      <c r="AN17" s="5" t="inlineStr"/>
+      <c r="AO17" s="5" t="inlineStr"/>
+      <c r="AP17" s="5" t="inlineStr"/>
+      <c r="AQ17" s="5" t="inlineStr"/>
+      <c r="AR17" s="5" t="inlineStr"/>
+      <c r="AS17" s="5" t="inlineStr"/>
+      <c r="AT17" s="5" t="inlineStr"/>
+      <c r="AU17" s="5" t="inlineStr"/>
+      <c r="AV17" s="5" t="inlineStr"/>
+      <c r="AW17" s="5" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX17" s="3" t="inlineStr"/>
-      <c r="AY17" s="3" t="inlineStr"/>
-      <c r="AZ17" s="3" t="inlineStr"/>
-      <c r="BA17" s="3" t="inlineStr"/>
-      <c r="BB17" s="3" t="inlineStr">
-        <is>
-          <t>KKR</t>
-        </is>
-      </c>
-      <c r="BC17" s="3" t="inlineStr">
+      <c r="AX17" s="5" t="inlineStr"/>
+      <c r="AY17" s="5" t="inlineStr"/>
+      <c r="AZ17" s="5" t="inlineStr"/>
+      <c r="BA17" s="5" t="inlineStr"/>
+      <c r="BB17" s="5" t="inlineStr">
+        <is>
+          <t>FDX</t>
+        </is>
+      </c>
+      <c r="BC17" s="5" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD17" s="3" t="inlineStr"/>
-      <c r="BE17" s="3" t="inlineStr">
+      <c r="BD17" s="5" t="inlineStr"/>
+      <c r="BE17" s="5" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF17" s="3" t="inlineStr">
+      <c r="BF17" s="5" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG17" s="3" t="inlineStr">
+      <c r="BG17" s="5" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH17" s="3" t="inlineStr"/>
+      <c r="BH17" s="5" t="inlineStr"/>
+      <c r="BI17" s="5" t="inlineStr"/>
+      <c r="BJ17" s="5" t="inlineStr"/>
+      <c r="BK17" s="5" t="inlineStr"/>
+      <c r="BL17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -9286,22 +10178,22 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>PNR</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>Pentair</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27T05:15:00+08:00</t>
+          <t>2026-08-27T03:11:00+08:00</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Meta reaches landmark $18 billion settlement with states in trial over teen social media addiction</t>
+          <t>Levi &amp; Korsinsky Reminds Pentair plc Investors of the Pending Class Action Lawsuit With a Lead Plaintiff Deadline of October 2, 2026 - PNR</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr"/>
@@ -9312,7 +10204,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>重大訴訟</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -9322,13 +10214,17 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -9338,7 +10234,7 @@
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>'-0.184</t>
+          <t>'-0.206</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr"/>
@@ -9352,12 +10248,12 @@
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNMlhBT1Zvb1ZRZFhDYmpQdzhKVlJ3LXFEb1VUby1ZR0xZQnp3LTdwY2E2UWFzVy1sbHRUWTJXM0VaeVRZRnJFdjZUS3c3Q3V4VzdXYW1KeXRIT0JGZmFLeE1iNklXQkdZdmxmVnB3bnpGZ1V0bUpGSGZiZjF1c01FcU5zd3NCblNzSU9RRnR4OGNNdGpSRmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwJBVV95cUxPX0N5b084TkpHLTByOE0wZUs1RmtmSnNFUkVPbnJGWUhWMkVYVFBZQm1fbkw3bFlkREZSSnRLNWNKMExMcVl0STJsb3pSWXFLRDBRMDBaY1dHYWJYdWxZbzF5ekZZaWR3WmI3ZWtON1ZGTVRBaHlkeFVibjY2R1JITy1sTUhPUlNlV3Nvd2NjVnUzaHpraGhMR1c2NHVFV3l3VllfNmpMeVlKalhCaUpudnMzUUliSVM0N2MxSGw1dzNVZ1MyZlZfVnBVdFJfMDhEWDc4bFFUN2R2TUVrY3JQMk5zNklSOFhDTzZXQzQxdFdqTUpvckRxdjNnRzgtOFdRemd1WS11d1VORFlSeWJGRUV2LUNTOVpBSjhPNGUzOA?oc=5</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t>AP News</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr"/>
@@ -9368,24 +10264,28 @@
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>MAJOR_LITIGATION</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t>settlement</t>
+          <t>class action</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr"/>
-      <c r="AB18" s="3" t="inlineStr"/>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>cd5b2ac52af1476a96a9c3d822dd467e</t>
+        </is>
+      </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>4441b880142ef32d3285eafd</t>
+          <t>fc678d417cfd75c3ec6d960b</t>
         </is>
       </c>
       <c r="AD18" s="3" t="inlineStr">
         <is>
-          <t>2b0eb5bbbe871ecbf264a7df</t>
+          <t>466023413d68985d9685c100</t>
         </is>
       </c>
       <c r="AE18" s="3" t="inlineStr"/>
@@ -9398,7 +10298,11 @@
       <c r="AL18" s="3" t="inlineStr"/>
       <c r="AM18" s="3" t="inlineStr"/>
       <c r="AN18" s="3" t="inlineStr"/>
-      <c r="AO18" s="3" t="inlineStr"/>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP18" s="3" t="inlineStr"/>
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr"/>
@@ -9406,18 +10310,14 @@
       <c r="AT18" s="3" t="inlineStr"/>
       <c r="AU18" s="3" t="inlineStr"/>
       <c r="AV18" s="3" t="inlineStr"/>
-      <c r="AW18" s="3" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
+      <c r="AW18" s="3" t="inlineStr"/>
       <c r="AX18" s="3" t="inlineStr"/>
       <c r="AY18" s="3" t="inlineStr"/>
       <c r="AZ18" s="3" t="inlineStr"/>
       <c r="BA18" s="3" t="inlineStr"/>
       <c r="BB18" s="3" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>PNR</t>
         </is>
       </c>
       <c r="BC18" s="3" t="inlineStr">
@@ -9428,679 +10328,31 @@
       <c r="BD18" s="3" t="inlineStr"/>
       <c r="BE18" s="3" t="inlineStr">
         <is>
-          <t>https://investor.atmeta.com/stock-info/default.aspx</t>
-        </is>
-      </c>
-      <c r="BF18" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF18" s="3" t="inlineStr"/>
       <c r="BG18" s="3" t="inlineStr">
         <is>
-          <t>上市公司</t>
+          <t>公司清單／交易所參照</t>
         </is>
       </c>
       <c r="BH18" s="3" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>FDX</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>FedEx Corporation Common Stock</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-27T03:48:16+08:00</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>FedEx Cup playoffs: What to watch over the next three weeks, including Ryder Cup spots</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr"/>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L19" s="5" t="inlineStr"/>
-      <c r="M19" s="5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N19" s="5" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O19" s="5" t="inlineStr">
-        <is>
-          <t>'-0.004</t>
-        </is>
-      </c>
-      <c r="P19" s="5" t="inlineStr"/>
-      <c r="Q19" s="5" t="inlineStr"/>
-      <c r="R19" s="5" t="inlineStr"/>
-      <c r="S19" s="5" t="inlineStr"/>
-      <c r="T19" s="5" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U19" s="5" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE03cUtKcjNZX0F4OFBnVVlKbkdXVW5pZ2JJaEtlSVlpTmRzOVl2N3JWSFdXcUFxd2dOSDBBN2gtWHJWUjRVY3pMdVlQUDVSUzdpZEhmOW5TMWkxc0E?oc=5</t>
-        </is>
-      </c>
-      <c r="V19" s="5" t="inlineStr">
-        <is>
-          <t>ESPN</t>
-        </is>
-      </c>
-      <c r="W19" s="5" t="inlineStr"/>
-      <c r="X19" s="5" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y19" s="5" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z19" s="5" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA19" s="5" t="inlineStr"/>
-      <c r="AB19" s="5" t="inlineStr"/>
-      <c r="AC19" s="5" t="inlineStr">
-        <is>
-          <t>4983f82dd60dacc31d2b65da</t>
-        </is>
-      </c>
-      <c r="AD19" s="5" t="inlineStr">
-        <is>
-          <t>ce7b96e947cb336b8f02e89d</t>
-        </is>
-      </c>
-      <c r="AE19" s="5" t="inlineStr"/>
-      <c r="AF19" s="5" t="inlineStr"/>
-      <c r="AG19" s="5" t="inlineStr"/>
-      <c r="AH19" s="5" t="inlineStr"/>
-      <c r="AI19" s="5" t="inlineStr"/>
-      <c r="AJ19" s="5" t="inlineStr"/>
-      <c r="AK19" s="5" t="inlineStr"/>
-      <c r="AL19" s="5" t="inlineStr"/>
-      <c r="AM19" s="5" t="inlineStr"/>
-      <c r="AN19" s="5" t="inlineStr"/>
-      <c r="AO19" s="5" t="inlineStr"/>
-      <c r="AP19" s="5" t="inlineStr"/>
-      <c r="AQ19" s="5" t="inlineStr"/>
-      <c r="AR19" s="5" t="inlineStr"/>
-      <c r="AS19" s="5" t="inlineStr"/>
-      <c r="AT19" s="5" t="inlineStr"/>
-      <c r="AU19" s="5" t="inlineStr"/>
-      <c r="AV19" s="5" t="inlineStr"/>
-      <c r="AW19" s="5" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX19" s="5" t="inlineStr"/>
-      <c r="AY19" s="5" t="inlineStr"/>
-      <c r="AZ19" s="5" t="inlineStr"/>
-      <c r="BA19" s="5" t="inlineStr"/>
-      <c r="BB19" s="5" t="inlineStr">
-        <is>
-          <t>FDX</t>
-        </is>
-      </c>
-      <c r="BC19" s="5" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD19" s="5" t="inlineStr"/>
-      <c r="BE19" s="5" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF19" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG19" s="5" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH19" s="5" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>PNR</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>Pentair</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27T03:11:00+08:00</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Levi &amp; Korsinsky Reminds Pentair plc Investors of the Pending Class Action Lawsuit With a Lead Plaintiff Deadline of October 2, 2026 - PNR</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr"/>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>'-0.206</t>
-        </is>
-      </c>
-      <c r="P20" s="3" t="inlineStr"/>
-      <c r="Q20" s="3" t="inlineStr"/>
-      <c r="R20" s="3" t="inlineStr"/>
-      <c r="S20" s="3" t="inlineStr"/>
-      <c r="T20" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U20" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMinwJBVV95cUxPX0N5b084TkpHLTByOE0wZUs1RmtmSnNFUkVPbnJGWUhWMkVYVFBZQm1fbkw3bFlkREZSSnRLNWNKMExMcVl0STJsb3pSWXFLRDBRMDBaY1dHYWJYdWxZbzF5ekZZaWR3WmI3ZWtON1ZGTVRBaHlkeFVibjY2R1JITy1sTUhPUlNlV3Nvd2NjVnUzaHpraGhMR1c2NHVFV3l3VllfNmpMeVlKalhCaUpudnMzUUliSVM0N2MxSGw1dzNVZ1MyZlZfVnBVdFJfMDhEWDc4bFFUN2R2TUVrY3JQMk5zNklSOFhDTzZXQzQxdFdqTUpvckRxdjNnRzgtOFdRemd1WS11d1VORFlSeWJGRUV2LUNTOVpBSjhPNGUzOA?oc=5</t>
-        </is>
-      </c>
-      <c r="V20" s="3" t="inlineStr">
-        <is>
-          <t>Morningstar</t>
-        </is>
-      </c>
-      <c r="W20" s="3" t="inlineStr"/>
-      <c r="X20" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y20" s="3" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z20" s="3" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA20" s="3" t="inlineStr"/>
-      <c r="AB20" s="3" t="inlineStr"/>
-      <c r="AC20" s="3" t="inlineStr">
-        <is>
-          <t>fc678d417cfd75c3ec6d960b</t>
-        </is>
-      </c>
-      <c r="AD20" s="3" t="inlineStr">
-        <is>
-          <t>466023413d68985d9685c100</t>
-        </is>
-      </c>
-      <c r="AE20" s="3" t="inlineStr"/>
-      <c r="AF20" s="3" t="inlineStr"/>
-      <c r="AG20" s="3" t="inlineStr"/>
-      <c r="AH20" s="3" t="inlineStr"/>
-      <c r="AI20" s="3" t="inlineStr"/>
-      <c r="AJ20" s="3" t="inlineStr"/>
-      <c r="AK20" s="3" t="inlineStr"/>
-      <c r="AL20" s="3" t="inlineStr"/>
-      <c r="AM20" s="3" t="inlineStr"/>
-      <c r="AN20" s="3" t="inlineStr"/>
-      <c r="AO20" s="3" t="inlineStr"/>
-      <c r="AP20" s="3" t="inlineStr"/>
-      <c r="AQ20" s="3" t="inlineStr"/>
-      <c r="AR20" s="3" t="inlineStr"/>
-      <c r="AS20" s="3" t="inlineStr"/>
-      <c r="AT20" s="3" t="inlineStr"/>
-      <c r="AU20" s="3" t="inlineStr"/>
-      <c r="AV20" s="3" t="inlineStr"/>
-      <c r="AW20" s="3" t="inlineStr"/>
-      <c r="AX20" s="3" t="inlineStr"/>
-      <c r="AY20" s="3" t="inlineStr"/>
-      <c r="AZ20" s="3" t="inlineStr"/>
-      <c r="BA20" s="3" t="inlineStr"/>
-      <c r="BB20" s="3" t="inlineStr">
-        <is>
-          <t>PNR</t>
-        </is>
-      </c>
-      <c r="BC20" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD20" s="3" t="inlineStr"/>
-      <c r="BE20" s="3" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF20" s="3" t="inlineStr"/>
-      <c r="BG20" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH20" s="3" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>Kroger</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27T02:41:48+08:00</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>Here’s how to qualify for the new Kroger $17M settlement over prescription drug pricing</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr"/>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>0.119</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="inlineStr"/>
-      <c r="Q21" s="3" t="inlineStr"/>
-      <c r="R21" s="3" t="inlineStr"/>
-      <c r="S21" s="3" t="inlineStr"/>
-      <c r="T21" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U21" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPdXBLX0NLOE9SdXBLMGFSZ0pWNk4tZDZZdUNxNm9Nd2VSal9sUzBjUHpQLWtJUVVDOEVLLXlXSDVYMnJSM1lFQjFKV0pTNl9MRFVWcG5vbmxFd1QtLWlnV3IxRWJsbHZuTG9BR0JYNWJ5VlJhWkVFUzY0ZTNHX0JJeEVtV3lNTFpPSzAySzhfT01zSURBSHlrRV9rMA?oc=5</t>
-        </is>
-      </c>
-      <c r="V21" s="3" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W21" s="3" t="inlineStr"/>
-      <c r="X21" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y21" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z21" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA21" s="3" t="inlineStr"/>
-      <c r="AB21" s="3" t="inlineStr"/>
-      <c r="AC21" s="3" t="inlineStr">
-        <is>
-          <t>615d9c04531dc7f90a7e53ff</t>
-        </is>
-      </c>
-      <c r="AD21" s="3" t="inlineStr">
-        <is>
-          <t>21ffcb676aeadfb494b962a3</t>
-        </is>
-      </c>
-      <c r="AE21" s="3" t="inlineStr"/>
-      <c r="AF21" s="3" t="inlineStr"/>
-      <c r="AG21" s="3" t="inlineStr"/>
-      <c r="AH21" s="3" t="inlineStr"/>
-      <c r="AI21" s="3" t="inlineStr"/>
-      <c r="AJ21" s="3" t="inlineStr"/>
-      <c r="AK21" s="3" t="inlineStr"/>
-      <c r="AL21" s="3" t="inlineStr"/>
-      <c r="AM21" s="3" t="inlineStr"/>
-      <c r="AN21" s="3" t="inlineStr"/>
-      <c r="AO21" s="3" t="inlineStr"/>
-      <c r="AP21" s="3" t="inlineStr"/>
-      <c r="AQ21" s="3" t="inlineStr"/>
-      <c r="AR21" s="3" t="inlineStr"/>
-      <c r="AS21" s="3" t="inlineStr"/>
-      <c r="AT21" s="3" t="inlineStr"/>
-      <c r="AU21" s="3" t="inlineStr"/>
-      <c r="AV21" s="3" t="inlineStr"/>
-      <c r="AW21" s="3" t="inlineStr"/>
-      <c r="AX21" s="3" t="inlineStr"/>
-      <c r="AY21" s="3" t="inlineStr"/>
-      <c r="AZ21" s="3" t="inlineStr"/>
-      <c r="BA21" s="3" t="inlineStr"/>
-      <c r="BB21" s="3" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="BC21" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD21" s="3" t="inlineStr"/>
-      <c r="BE21" s="3" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF21" s="3" t="inlineStr"/>
-      <c r="BG21" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH21" s="3" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Kroger</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27T00:13:00+08:00</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Here’s how to find out if you qualify for part of Kroger’s $17 million settlement</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr"/>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>0.027</t>
-        </is>
-      </c>
-      <c r="P22" s="3" t="inlineStr"/>
-      <c r="Q22" s="3" t="inlineStr"/>
-      <c r="R22" s="3" t="inlineStr"/>
-      <c r="S22" s="3" t="inlineStr"/>
-      <c r="T22" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U22" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOQVVLZHdGeWMxbmlpb3JoMHpBTkRRWnFReFpwZU9YZ2dkVlRrTUJqY1AtbG1OOTQtbnpaV1AxTGxDY1RvNnhHN0ZyM0dLQzczWXJoMWRjdFNxM3ZneVJmSk1SSkp5dnRvRFpGZmtsVUdBdDB0ZmgtSHhqUkgxdHh2QmwtV2kxNjFZOXREWGtWdF9QUUdRTElaOGNtM0lYM2U1ZXhSNndGZE5fcHBL?oc=5</t>
-        </is>
-      </c>
-      <c r="V22" s="3" t="inlineStr">
-        <is>
-          <t>Action News 5</t>
-        </is>
-      </c>
-      <c r="W22" s="3" t="inlineStr"/>
-      <c r="X22" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y22" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z22" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA22" s="3" t="inlineStr"/>
-      <c r="AB22" s="3" t="inlineStr"/>
-      <c r="AC22" s="3" t="inlineStr">
-        <is>
-          <t>ae73f6f537d1a1594921ce64</t>
-        </is>
-      </c>
-      <c r="AD22" s="3" t="inlineStr">
-        <is>
-          <t>eadf751f796e32d981e1a538</t>
-        </is>
-      </c>
-      <c r="AE22" s="3" t="inlineStr"/>
-      <c r="AF22" s="3" t="inlineStr"/>
-      <c r="AG22" s="3" t="inlineStr"/>
-      <c r="AH22" s="3" t="inlineStr"/>
-      <c r="AI22" s="3" t="inlineStr"/>
-      <c r="AJ22" s="3" t="inlineStr"/>
-      <c r="AK22" s="3" t="inlineStr"/>
-      <c r="AL22" s="3" t="inlineStr"/>
-      <c r="AM22" s="3" t="inlineStr"/>
-      <c r="AN22" s="3" t="inlineStr"/>
-      <c r="AO22" s="3" t="inlineStr"/>
-      <c r="AP22" s="3" t="inlineStr"/>
-      <c r="AQ22" s="3" t="inlineStr"/>
-      <c r="AR22" s="3" t="inlineStr"/>
-      <c r="AS22" s="3" t="inlineStr"/>
-      <c r="AT22" s="3" t="inlineStr"/>
-      <c r="AU22" s="3" t="inlineStr"/>
-      <c r="AV22" s="3" t="inlineStr"/>
-      <c r="AW22" s="3" t="inlineStr"/>
-      <c r="AX22" s="3" t="inlineStr"/>
-      <c r="AY22" s="3" t="inlineStr"/>
-      <c r="AZ22" s="3" t="inlineStr"/>
-      <c r="BA22" s="3" t="inlineStr"/>
-      <c r="BB22" s="3" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="BC22" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD22" s="3" t="inlineStr"/>
-      <c r="BE22" s="3" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF22" s="3" t="inlineStr"/>
-      <c r="BG22" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH22" s="3" t="inlineStr"/>
+      <c r="BI18" s="3" t="inlineStr"/>
+      <c r="BJ18" s="3" t="inlineStr"/>
+      <c r="BK18" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL18" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH22"/>
+  <autoFilter ref="A1:BL18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10111,7 +10363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH3"/>
+  <dimension ref="A1:BL3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10174,6 +10426,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10475,6 +10731,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -10631,6 +10907,10 @@
       <c r="BF2" s="5" t="inlineStr"/>
       <c r="BG2" s="5" t="inlineStr"/>
       <c r="BH2" s="5" t="inlineStr"/>
+      <c r="BI2" s="5" t="inlineStr"/>
+      <c r="BJ2" s="5" t="inlineStr"/>
+      <c r="BK2" s="5" t="inlineStr"/>
+      <c r="BL2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -10785,9 +11065,13 @@
       <c r="BF3" s="2" t="inlineStr"/>
       <c r="BG3" s="2" t="inlineStr"/>
       <c r="BH3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BJ3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr"/>
+      <c r="BL3" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH3"/>
+  <autoFilter ref="A1:BL3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10798,7 +11082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10861,6 +11145,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11164,9 +11452,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11177,7 +11485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -11227,134 +11535,134 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>methods</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>started_at</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>finished_at</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>llm_calls</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>cache_reused</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>selected_company_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>collected</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>errors</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>stages</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>quota_reserved</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>重複合併</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>sources</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>changed</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>missing_publication_time</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ticker_statuses</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>llm_calls</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>start</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>methods</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>cache_reused</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>major</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>selected_company_count</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>collected</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>errors</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>stages</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>quota_reserved</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>重複合併</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ticker-audit-20261024-081549</t>
+          <t>daily-2026-10-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ticker-audit</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -11364,46 +11672,80 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296780+08:00</t>
+          <t>2026-10-25T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296790+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>1691</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>257</v>
-      </c>
-      <c r="I2" s="2" t="n">
+          <t>2026-10-26T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:23:38.366332+08:00</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:40:53.776257+08:00</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr"/>
-      <c r="U2" s="2" t="inlineStr"/>
-      <c r="V2" s="2" t="inlineStr"/>
-      <c r="W2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="n">
+        <v>1926</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>1976</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 16 筆', '方法二 1958 筆；公司 503 家（非輪替）', '市場事件搜尋 2 筆', 'FinBERT 完成 1976 筆']</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="W2" s="2" t="n">
+        <v>15</v>
+      </c>
       <c r="X2" s="2" t="inlineStr"/>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -11412,12 +11754,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+          <t>daily-2026-10-25</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -11427,90 +11769,94 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:26:34.299718+08:00</t>
+          <t>2026-10-24T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:32:11.776786+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
+          <t>2026-10-25T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:23:17.137147+08:00</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:40:12.120180+08:00</t>
+        </is>
+      </c>
       <c r="K3" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>2032</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>503</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>34</v>
+        <v>2089</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="T3" s="2" t="n">
-        <v>17</v>
+        <v>2067</v>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 26 筆', '方法二 2059 筆；公司 503 家（非輪替）', '市場事件搜尋 6 筆', 'FinBERT 完成 2089 筆']</t>
+        </is>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
-      </c>
-      <c r="Y3" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="Z3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>2067</v>
+      </c>
+      <c r="W3" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="X3" s="2" t="inlineStr"/>
+      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr"/>
+      <c r="AA3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>daily-2026-10-24</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -11520,94 +11866,94 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:20:47.845317+08:00</t>
+          <t>2026-10-23T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:21:20.302846+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
+          <t>2026-10-24T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:44:09.884829+08:00</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T13:04:34.984103+08:00</t>
+        </is>
+      </c>
       <c r="K4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>3760</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>503</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>2</v>
+        <v>3802</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" s="2" t="n">
-        <v>2</v>
+        <v>3825</v>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 158 筆', '方法二 3638 筆；公司 503 家（非輪替）', '市場事件搜尋 8 筆', 'FinBERT 完成 3802 筆']</t>
+        </is>
       </c>
       <c r="U4" s="2" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA4" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>3793</v>
+      </c>
+      <c r="W4" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="X4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>ticker-audit-20261024-081549</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>ticker-audit</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -11615,89 +11961,342 @@
           <t>success</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:11.949238+08:00</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:18.833437+08:00</t>
-        </is>
-      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="n">
-        <v>33</v>
-      </c>
+      <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296780+08:00</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296790+08:00</t>
+        </is>
+      </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="2" t="n">
-        <v>33</v>
-      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
       <c r="R5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="T5" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="U5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X5" s="2" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
+        <v>1691</v>
+      </c>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="n">
+        <v>19</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>1</v>
+        <v>257</v>
       </c>
       <c r="Z5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA5" s="2" t="n">
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:34.299718+08:00</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:32:11.776786+08:00</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="M6" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N6" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="2" t="inlineStr"/>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:20:47.845317+08:00</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:21:20.302846+08:00</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="W7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="2" t="inlineStr"/>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:11.949238+08:00</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:18.833437+08:00</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="2" t="inlineStr"/>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA5"/>
+  <autoFilter ref="A1:AA8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/news_daily/2026-08-27.xlsx
+++ b/news_daily/2026-08-27.xlsx
@@ -15,8 +15,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
@@ -3875,178 +3875,202 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>NVIDIA Corporation</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>2026-08-27T11:08:04+08:00</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Nvidia blowout earnings spur mixed reaction in its Asian supply chain, here’s why:</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L18" s="5" t="inlineStr"/>
-      <c r="M18" s="5" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>'-0.769</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPaXBDb0R1SWRKampnWV9NTUx3Y0lYZUlDUmpfbmx1TWtIeGUyeWVXelpaZ1hoZHRTT0xUSGhfbUpncmR3dEppakZPUVdJeGZhZ2pCa1NGTk9DNDc1emlzN3ZiemVLZVB3U3BJWUtrSWdXVWxTZVJQdVV1cXNjM19oSHNCMlMxaUY5dU1COWg1VFhoeWhMbmlLRnl3RjJnTzRSWEdUb0pTbVFwRklXaTZSb1N3dGJodWNhdXEzeU1TTmZMYlRFUTlMbFY1c3N2alF2dzQ5U3ZuZmw?oc=5</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Investing.com</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr"/>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>supply chain</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>5a710fd68e484d17ba3fabb3a4aa70a7</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>1a7bf279996dd39eba2e70c7</t>
+        </is>
+      </c>
+      <c r="AD18" s="2" t="inlineStr">
+        <is>
+          <t>40915b7abd936cc448ca631c</t>
+        </is>
+      </c>
+      <c r="AE18" s="2" t="inlineStr"/>
+      <c r="AF18" s="2" t="inlineStr"/>
+      <c r="AG18" s="2" t="inlineStr"/>
+      <c r="AH18" s="2" t="inlineStr"/>
+      <c r="AI18" s="2" t="inlineStr"/>
+      <c r="AJ18" s="2" t="inlineStr"/>
+      <c r="AK18" s="2" t="inlineStr"/>
+      <c r="AL18" s="2" t="inlineStr"/>
+      <c r="AM18" s="2" t="inlineStr"/>
+      <c r="AN18" s="2" t="inlineStr"/>
+      <c r="AO18" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N18" s="5" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O18" s="5" t="inlineStr">
-        <is>
-          <t>'-0.769</t>
-        </is>
-      </c>
-      <c r="P18" s="5" t="inlineStr"/>
-      <c r="Q18" s="5" t="inlineStr"/>
-      <c r="R18" s="5" t="inlineStr"/>
-      <c r="S18" s="5" t="inlineStr"/>
-      <c r="T18" s="5" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U18" s="5" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPaXBDb0R1SWRKampnWV9NTUx3Y0lYZUlDUmpfbmx1TWtIeGUyeWVXelpaZ1hoZHRTT0xUSGhfbUpncmR3dEppakZPUVdJeGZhZ2pCa1NGTk9DNDc1emlzN3ZiemVLZVB3U3BJWUtrSWdXVWxTZVJQdVV1cXNjM19oSHNCMlMxaUY5dU1COWg1VFhoeWhMbmlLRnl3RjJnTzRSWEdUb0pTbVFwRklXaTZSb1N3dGJodWNhdXEzeU1TTmZMYlRFUTlMbFY1c3N2alF2dzQ5U3ZuZmw?oc=5</t>
-        </is>
-      </c>
-      <c r="V18" s="5" t="inlineStr">
-        <is>
-          <t>Investing.com</t>
-        </is>
-      </c>
-      <c r="W18" s="5" t="inlineStr"/>
-      <c r="X18" s="5" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y18" s="5" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z18" s="5" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA18" s="5" t="inlineStr"/>
-      <c r="AB18" s="5" t="inlineStr"/>
-      <c r="AC18" s="5" t="inlineStr">
-        <is>
-          <t>1a7bf279996dd39eba2e70c7</t>
-        </is>
-      </c>
-      <c r="AD18" s="5" t="inlineStr">
-        <is>
-          <t>40915b7abd936cc448ca631c</t>
-        </is>
-      </c>
-      <c r="AE18" s="5" t="inlineStr"/>
-      <c r="AF18" s="5" t="inlineStr"/>
-      <c r="AG18" s="5" t="inlineStr"/>
-      <c r="AH18" s="5" t="inlineStr"/>
-      <c r="AI18" s="5" t="inlineStr"/>
-      <c r="AJ18" s="5" t="inlineStr"/>
-      <c r="AK18" s="5" t="inlineStr"/>
-      <c r="AL18" s="5" t="inlineStr"/>
-      <c r="AM18" s="5" t="inlineStr"/>
-      <c r="AN18" s="5" t="inlineStr"/>
-      <c r="AO18" s="5" t="inlineStr"/>
-      <c r="AP18" s="5" t="inlineStr"/>
-      <c r="AQ18" s="5" t="inlineStr"/>
-      <c r="AR18" s="5" t="inlineStr"/>
-      <c r="AS18" s="5" t="inlineStr"/>
-      <c r="AT18" s="5" t="inlineStr"/>
-      <c r="AU18" s="5" t="inlineStr"/>
-      <c r="AV18" s="5" t="inlineStr"/>
-      <c r="AW18" s="5" t="inlineStr">
+      <c r="AP18" s="2" t="inlineStr"/>
+      <c r="AQ18" s="2" t="inlineStr"/>
+      <c r="AR18" s="2" t="inlineStr"/>
+      <c r="AS18" s="2" t="inlineStr"/>
+      <c r="AT18" s="2" t="inlineStr"/>
+      <c r="AU18" s="2" t="inlineStr"/>
+      <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" s="2" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX18" s="5" t="inlineStr"/>
-      <c r="AY18" s="5" t="inlineStr"/>
-      <c r="AZ18" s="5" t="inlineStr"/>
-      <c r="BA18" s="5" t="inlineStr"/>
-      <c r="BB18" s="5" t="inlineStr">
+      <c r="AX18" s="2" t="inlineStr"/>
+      <c r="AY18" s="2" t="inlineStr"/>
+      <c r="AZ18" s="2" t="inlineStr"/>
+      <c r="BA18" s="2" t="inlineStr"/>
+      <c r="BB18" s="2" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="BC18" s="5" t="inlineStr">
+      <c r="BC18" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD18" s="5" t="inlineStr"/>
-      <c r="BE18" s="5" t="inlineStr">
+      <c r="BD18" s="2" t="inlineStr"/>
+      <c r="BE18" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF18" s="5" t="inlineStr">
+      <c r="BF18" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG18" s="5" t="inlineStr">
+      <c r="BG18" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH18" s="5" t="inlineStr"/>
-      <c r="BI18" s="5" t="inlineStr"/>
-      <c r="BJ18" s="5" t="inlineStr"/>
-      <c r="BK18" s="5" t="inlineStr"/>
-      <c r="BL18" s="5" t="inlineStr"/>
+      <c r="BH18" s="2" t="inlineStr"/>
+      <c r="BI18" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ18" s="2" t="inlineStr"/>
+      <c r="BK18" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -4059,7 +4083,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>TMUS</t>
+        </is>
+      </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
           <t>T-Mobile US</t>
@@ -4093,17 +4121,17 @@
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N19" s="5" t="inlineStr">
@@ -4148,7 +4176,11 @@
         </is>
       </c>
       <c r="AA19" s="5" t="inlineStr"/>
-      <c r="AB19" s="5" t="inlineStr"/>
+      <c r="AB19" s="5" t="inlineStr">
+        <is>
+          <t>aeb88a7795fd4139b8638392d1e8cbb1</t>
+        </is>
+      </c>
       <c r="AC19" s="5" t="inlineStr">
         <is>
           <t>a66028331c9d1c3dec9371f4</t>
@@ -4171,7 +4203,7 @@
       <c r="AN19" s="5" t="inlineStr"/>
       <c r="AO19" s="5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP19" s="5" t="inlineStr"/>
@@ -4201,10 +4233,22 @@
       <c r="BF19" s="5" t="inlineStr"/>
       <c r="BG19" s="5" t="inlineStr"/>
       <c r="BH19" s="5" t="inlineStr"/>
-      <c r="BI19" s="5" t="inlineStr"/>
+      <c r="BI19" s="5" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
       <c r="BJ19" s="5" t="inlineStr"/>
-      <c r="BK19" s="5" t="inlineStr"/>
-      <c r="BL19" s="5" t="inlineStr"/>
+      <c r="BK19" s="5" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL19" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -5352,32 +5396,32 @@
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -5413,7 +5457,7 @@
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -5422,7 +5466,11 @@
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr"/>
-      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>697ed8cf64654fb194e78433f353283a</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
           <t>7e6cff4c708cba0068778da2</t>
@@ -5445,7 +5493,7 @@
       <c r="AN26" s="2" t="inlineStr"/>
       <c r="AO26" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP26" s="2" t="inlineStr"/>
@@ -5475,184 +5523,220 @@
       <c r="BF26" s="2" t="inlineStr"/>
       <c r="BG26" s="2" t="inlineStr"/>
       <c r="BH26" s="2" t="inlineStr"/>
-      <c r="BI26" s="2" t="inlineStr"/>
+      <c r="BI26" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ26" s="2" t="inlineStr"/>
-      <c r="BK26" s="2" t="inlineStr"/>
-      <c r="BL26" s="2" t="inlineStr"/>
+      <c r="BK26" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>FDX</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>FedEx Corporation Common Stock</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>2026-08-27T03:48:16+08:00</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>FedEx Cup playoffs: What to watch over the next three weeks, including Ryder Cup spots</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr"/>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="inlineStr"/>
-      <c r="M27" s="5" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>'-0.004</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr"/>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE03cUtKcjNZX0F4OFBnVVlKbkdXVW5pZ2JJaEtlSVlpTmRzOVl2N3JWSFdXcUFxd2dOSDBBN2gtWHJWUjRVY3pMdVlQUDVSUzdpZEhmOW5TMWkxc0E?oc=5</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>ESPN</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr"/>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>layoff；layoffs</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr"/>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>36d63fb50c6d4c1cbb332609d51b22d4</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>4983f82dd60dacc31d2b65da</t>
+        </is>
+      </c>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>ce7b96e947cb336b8f02e89d</t>
+        </is>
+      </c>
+      <c r="AE27" s="2" t="inlineStr"/>
+      <c r="AF27" s="2" t="inlineStr"/>
+      <c r="AG27" s="2" t="inlineStr"/>
+      <c r="AH27" s="2" t="inlineStr"/>
+      <c r="AI27" s="2" t="inlineStr"/>
+      <c r="AJ27" s="2" t="inlineStr"/>
+      <c r="AK27" s="2" t="inlineStr"/>
+      <c r="AL27" s="2" t="inlineStr"/>
+      <c r="AM27" s="2" t="inlineStr"/>
+      <c r="AN27" s="2" t="inlineStr"/>
+      <c r="AO27" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N27" s="5" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O27" s="5" t="inlineStr">
-        <is>
-          <t>'-0.004</t>
-        </is>
-      </c>
-      <c r="P27" s="5" t="inlineStr"/>
-      <c r="Q27" s="5" t="inlineStr"/>
-      <c r="R27" s="5" t="inlineStr"/>
-      <c r="S27" s="5" t="inlineStr"/>
-      <c r="T27" s="5" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U27" s="5" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE03cUtKcjNZX0F4OFBnVVlKbkdXVW5pZ2JJaEtlSVlpTmRzOVl2N3JWSFdXcUFxd2dOSDBBN2gtWHJWUjRVY3pMdVlQUDVSUzdpZEhmOW5TMWkxc0E?oc=5</t>
-        </is>
-      </c>
-      <c r="V27" s="5" t="inlineStr">
-        <is>
-          <t>ESPN</t>
-        </is>
-      </c>
-      <c r="W27" s="5" t="inlineStr"/>
-      <c r="X27" s="5" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y27" s="5" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z27" s="5" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA27" s="5" t="inlineStr"/>
-      <c r="AB27" s="5" t="inlineStr"/>
-      <c r="AC27" s="5" t="inlineStr">
-        <is>
-          <t>4983f82dd60dacc31d2b65da</t>
-        </is>
-      </c>
-      <c r="AD27" s="5" t="inlineStr">
-        <is>
-          <t>ce7b96e947cb336b8f02e89d</t>
-        </is>
-      </c>
-      <c r="AE27" s="5" t="inlineStr"/>
-      <c r="AF27" s="5" t="inlineStr"/>
-      <c r="AG27" s="5" t="inlineStr"/>
-      <c r="AH27" s="5" t="inlineStr"/>
-      <c r="AI27" s="5" t="inlineStr"/>
-      <c r="AJ27" s="5" t="inlineStr"/>
-      <c r="AK27" s="5" t="inlineStr"/>
-      <c r="AL27" s="5" t="inlineStr"/>
-      <c r="AM27" s="5" t="inlineStr"/>
-      <c r="AN27" s="5" t="inlineStr"/>
-      <c r="AO27" s="5" t="inlineStr"/>
-      <c r="AP27" s="5" t="inlineStr"/>
-      <c r="AQ27" s="5" t="inlineStr"/>
-      <c r="AR27" s="5" t="inlineStr"/>
-      <c r="AS27" s="5" t="inlineStr"/>
-      <c r="AT27" s="5" t="inlineStr"/>
-      <c r="AU27" s="5" t="inlineStr"/>
-      <c r="AV27" s="5" t="inlineStr"/>
-      <c r="AW27" s="5" t="inlineStr">
+      <c r="AP27" s="2" t="inlineStr"/>
+      <c r="AQ27" s="2" t="inlineStr"/>
+      <c r="AR27" s="2" t="inlineStr"/>
+      <c r="AS27" s="2" t="inlineStr"/>
+      <c r="AT27" s="2" t="inlineStr"/>
+      <c r="AU27" s="2" t="inlineStr"/>
+      <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX27" s="5" t="inlineStr"/>
-      <c r="AY27" s="5" t="inlineStr"/>
-      <c r="AZ27" s="5" t="inlineStr"/>
-      <c r="BA27" s="5" t="inlineStr"/>
-      <c r="BB27" s="5" t="inlineStr">
+      <c r="AX27" s="2" t="inlineStr"/>
+      <c r="AY27" s="2" t="inlineStr"/>
+      <c r="AZ27" s="2" t="inlineStr"/>
+      <c r="BA27" s="2" t="inlineStr"/>
+      <c r="BB27" s="2" t="inlineStr">
         <is>
           <t>FDX</t>
         </is>
       </c>
-      <c r="BC27" s="5" t="inlineStr">
+      <c r="BC27" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD27" s="5" t="inlineStr"/>
-      <c r="BE27" s="5" t="inlineStr">
+      <c r="BD27" s="2" t="inlineStr"/>
+      <c r="BE27" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF27" s="5" t="inlineStr">
+      <c r="BF27" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG27" s="5" t="inlineStr">
+      <c r="BG27" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH27" s="5" t="inlineStr"/>
-      <c r="BI27" s="5" t="inlineStr"/>
-      <c r="BJ27" s="5" t="inlineStr"/>
-      <c r="BK27" s="5" t="inlineStr"/>
-      <c r="BL27" s="5" t="inlineStr"/>
+      <c r="BH27" s="2" t="inlineStr"/>
+      <c r="BI27" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ27" s="2" t="inlineStr"/>
+      <c r="BK27" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL27" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -6754,7 +6838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL18"/>
+  <dimension ref="A1:BL16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8904,22 +8988,22 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>T-Mobile US</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>2026-08-27T11:08:04+08:00</t>
+          <t>2026-08-27T10:36:59+08:00</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Nvidia blowout earnings spur mixed reaction in its Asian supply chain, here’s why:</t>
+          <t>T-Mobile計劃在華盛頓州裁員並關閉多個網點</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr"/>
@@ -8930,7 +9014,7 @@
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>供應鏈中斷</t>
+          <t>裁員或人力縮減</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
@@ -8940,13 +9024,17 @@
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N11" s="5" t="inlineStr">
@@ -8954,28 +9042,24 @@
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O11" s="5" t="inlineStr">
-        <is>
-          <t>'-0.769</t>
-        </is>
-      </c>
+      <c r="O11" s="5" t="inlineStr"/>
       <c r="P11" s="5" t="inlineStr"/>
       <c r="Q11" s="5" t="inlineStr"/>
       <c r="R11" s="5" t="inlineStr"/>
       <c r="S11" s="5" t="inlineStr"/>
       <c r="T11" s="5" t="inlineStr">
         <is>
-          <t>公司清單／別名核對</t>
+          <t>公司名稱／股票代號歧義</t>
         </is>
       </c>
       <c r="U11" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPaXBDb0R1SWRKampnWV9NTUx3Y0lYZUlDUmpfbmx1TWtIeGUyeWVXelpaZ1hoZHRTT0xUSGhfbUpncmR3dEppakZPUVdJeGZhZ2pCa1NGTk9DNDc1emlzN3ZiemVLZVB3U3BJWUtrSWdXVWxTZVJQdVV1cXNjM19oSHNCMlMxaUY5dU1COWg1VFhoeWhMbmlLRnl3RjJnTzRSWEdUb0pTbVFwRklXaTZSb1N3dGJodWNhdXEzeU1TTmZMYlRFUTlMbFY1c3N2alF2dzQ5U3ZuZmw?oc=5</t>
+          <t>https://www.gelonghui.com/live/2635509</t>
         </is>
       </c>
       <c r="V11" s="5" t="inlineStr">
         <is>
-          <t>Investing.com</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="W11" s="5" t="inlineStr"/>
@@ -8986,24 +9070,28 @@
       </c>
       <c r="Y11" s="5" t="inlineStr">
         <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
+          <t>WORKFORCE_REDUCTION</t>
         </is>
       </c>
       <c r="Z11" s="5" t="inlineStr">
         <is>
-          <t>supply chain</t>
+          <t>裁員</t>
         </is>
       </c>
       <c r="AA11" s="5" t="inlineStr"/>
-      <c r="AB11" s="5" t="inlineStr"/>
+      <c r="AB11" s="5" t="inlineStr">
+        <is>
+          <t>aeb88a7795fd4139b8638392d1e8cbb1</t>
+        </is>
+      </c>
       <c r="AC11" s="5" t="inlineStr">
         <is>
-          <t>1a7bf279996dd39eba2e70c7</t>
+          <t>a66028331c9d1c3dec9371f4</t>
         </is>
       </c>
       <c r="AD11" s="5" t="inlineStr">
         <is>
-          <t>40915b7abd936cc448ca631c</t>
+          <t>69306eed6362ccd5aad985fc</t>
         </is>
       </c>
       <c r="AE11" s="5" t="inlineStr"/>
@@ -9016,7 +9104,11 @@
       <c r="AL11" s="5" t="inlineStr"/>
       <c r="AM11" s="5" t="inlineStr"/>
       <c r="AN11" s="5" t="inlineStr"/>
-      <c r="AO11" s="5" t="inlineStr"/>
+      <c r="AO11" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP11" s="5" t="inlineStr"/>
       <c r="AQ11" s="5" t="inlineStr"/>
       <c r="AR11" s="5" t="inlineStr"/>
@@ -9024,204 +9116,236 @@
       <c r="AT11" s="5" t="inlineStr"/>
       <c r="AU11" s="5" t="inlineStr"/>
       <c r="AV11" s="5" t="inlineStr"/>
-      <c r="AW11" s="5" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
+      <c r="AW11" s="5" t="inlineStr"/>
       <c r="AX11" s="5" t="inlineStr"/>
       <c r="AY11" s="5" t="inlineStr"/>
       <c r="AZ11" s="5" t="inlineStr"/>
       <c r="BA11" s="5" t="inlineStr"/>
       <c r="BB11" s="5" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="BC11" s="5" t="inlineStr">
         <is>
-          <t>已核對</t>
+          <t>公司名稱／股票代號歧義</t>
         </is>
       </c>
       <c r="BD11" s="5" t="inlineStr"/>
-      <c r="BE11" s="5" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF11" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG11" s="5" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
+      <c r="BE11" s="5" t="inlineStr"/>
+      <c r="BF11" s="5" t="inlineStr"/>
+      <c r="BG11" s="5" t="inlineStr"/>
       <c r="BH11" s="5" t="inlineStr"/>
-      <c r="BI11" s="5" t="inlineStr"/>
+      <c r="BI11" s="5" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
       <c r="BJ11" s="5" t="inlineStr"/>
-      <c r="BK11" s="5" t="inlineStr"/>
-      <c r="BL11" s="5" t="inlineStr"/>
+      <c r="BK11" s="5" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>T-Mobile US</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-27T10:36:59+08:00</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>T-Mobile計劃在華盛頓州裁員並關閉多個網點</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="5" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M12" s="5" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27T09:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Landmark settlement agreement with META</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>監管裁罰</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>0.694</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr"/>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQVE5XWkRKckFwRk1HWmc0WlhxbzRZVlNCc3docC0tVF9EbGNnUVpmRk40RXBWUmt5YVZ1NjN1Qk1nTUlrSFFMYXdqYmwyeUN4RWZVektWMlJkSDFwa19OOHVDaEtvTzZrcHRpMDRQVUlrVU1pcHpsb21mejVXSU5RUlVyZTBYbEZ2bFFjNmR0YkNCUWlqbDFvT1V4aDNUMGpmSWJKUkJYNkozbnNyWUhtN0ZBOWI?oc=5</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>KXLY.com</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr"/>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr"/>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>832797d648cf412aadc3fea1aca57fb8</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>39e351ac93b9ef965a0173b9</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr">
+        <is>
+          <t>60fc635434635081cf5136dd</t>
+        </is>
+      </c>
+      <c r="AE12" s="3" t="inlineStr"/>
+      <c r="AF12" s="3" t="inlineStr"/>
+      <c r="AG12" s="3" t="inlineStr"/>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr"/>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr"/>
+      <c r="AM12" s="3" t="inlineStr"/>
+      <c r="AN12" s="3" t="inlineStr"/>
+      <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N12" s="5" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O12" s="5" t="inlineStr"/>
-      <c r="P12" s="5" t="inlineStr"/>
-      <c r="Q12" s="5" t="inlineStr"/>
-      <c r="R12" s="5" t="inlineStr"/>
-      <c r="S12" s="5" t="inlineStr"/>
-      <c r="T12" s="5" t="inlineStr">
-        <is>
-          <t>公司名稱／股票代號歧義</t>
-        </is>
-      </c>
-      <c r="U12" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/live/2635509</t>
-        </is>
-      </c>
-      <c r="V12" s="5" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W12" s="5" t="inlineStr"/>
-      <c r="X12" s="5" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y12" s="5" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z12" s="5" t="inlineStr">
-        <is>
-          <t>裁員</t>
-        </is>
-      </c>
-      <c r="AA12" s="5" t="inlineStr"/>
-      <c r="AB12" s="5" t="inlineStr"/>
-      <c r="AC12" s="5" t="inlineStr">
-        <is>
-          <t>a66028331c9d1c3dec9371f4</t>
-        </is>
-      </c>
-      <c r="AD12" s="5" t="inlineStr">
-        <is>
-          <t>69306eed6362ccd5aad985fc</t>
-        </is>
-      </c>
-      <c r="AE12" s="5" t="inlineStr"/>
-      <c r="AF12" s="5" t="inlineStr"/>
-      <c r="AG12" s="5" t="inlineStr"/>
-      <c r="AH12" s="5" t="inlineStr"/>
-      <c r="AI12" s="5" t="inlineStr"/>
-      <c r="AJ12" s="5" t="inlineStr"/>
-      <c r="AK12" s="5" t="inlineStr"/>
-      <c r="AL12" s="5" t="inlineStr"/>
-      <c r="AM12" s="5" t="inlineStr"/>
-      <c r="AN12" s="5" t="inlineStr"/>
-      <c r="AO12" s="5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP12" s="5" t="inlineStr"/>
-      <c r="AQ12" s="5" t="inlineStr"/>
-      <c r="AR12" s="5" t="inlineStr"/>
-      <c r="AS12" s="5" t="inlineStr"/>
-      <c r="AT12" s="5" t="inlineStr"/>
-      <c r="AU12" s="5" t="inlineStr"/>
-      <c r="AV12" s="5" t="inlineStr"/>
-      <c r="AW12" s="5" t="inlineStr"/>
-      <c r="AX12" s="5" t="inlineStr"/>
-      <c r="AY12" s="5" t="inlineStr"/>
-      <c r="AZ12" s="5" t="inlineStr"/>
-      <c r="BA12" s="5" t="inlineStr"/>
-      <c r="BB12" s="5" t="inlineStr">
-        <is>
-          <t>TMUS</t>
-        </is>
-      </c>
-      <c r="BC12" s="5" t="inlineStr">
-        <is>
-          <t>公司名稱／股票代號歧義</t>
-        </is>
-      </c>
-      <c r="BD12" s="5" t="inlineStr"/>
-      <c r="BE12" s="5" t="inlineStr"/>
-      <c r="BF12" s="5" t="inlineStr"/>
-      <c r="BG12" s="5" t="inlineStr"/>
-      <c r="BH12" s="5" t="inlineStr"/>
-      <c r="BI12" s="5" t="inlineStr"/>
-      <c r="BJ12" s="5" t="inlineStr"/>
-      <c r="BK12" s="5" t="inlineStr"/>
-      <c r="BL12" s="5" t="inlineStr"/>
+      <c r="AP12" s="3" t="inlineStr"/>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr"/>
+      <c r="AS12" s="3" t="inlineStr"/>
+      <c r="AT12" s="3" t="inlineStr"/>
+      <c r="AU12" s="3" t="inlineStr"/>
+      <c r="AV12" s="3" t="inlineStr"/>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="AX12" s="3" t="inlineStr"/>
+      <c r="AY12" s="3" t="inlineStr"/>
+      <c r="AZ12" s="3" t="inlineStr"/>
+      <c r="BA12" s="3" t="inlineStr"/>
+      <c r="BB12" s="3" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="BC12" s="3" t="inlineStr">
+        <is>
+          <t>已核對</t>
+        </is>
+      </c>
+      <c r="BD12" s="3" t="inlineStr"/>
+      <c r="BE12" s="3" t="inlineStr">
+        <is>
+          <t>https://investor.atmeta.com/stock-info/default.aspx</t>
+        </is>
+      </c>
+      <c r="BF12" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="BG12" s="3" t="inlineStr">
+        <is>
+          <t>上市公司</t>
+        </is>
+      </c>
+      <c r="BH12" s="3" t="inlineStr"/>
+      <c r="BI12" s="3" t="inlineStr"/>
+      <c r="BJ12" s="3" t="inlineStr"/>
+      <c r="BK12" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL12" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -9236,22 +9360,22 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>PNR</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>Pentair</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27T09:20:00+08:00</t>
+          <t>2026-08-27T07:55:00+08:00</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Landmark settlement agreement with META</t>
+          <t>PNR INVESTOR DEADLINE: Robbins Geller Rudman &amp; Dowd LLP Files Class Action Lawsuit Against Pentair plc and Announces Opportunity for Investors with Substantial Losses to Lead the Pentair Class Action Lawsuit</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -9262,7 +9386,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>重大訴訟</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -9292,7 +9416,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>0.694</t>
+          <t>0.003</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr"/>
@@ -9306,12 +9430,12 @@
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQVE5XWkRKckFwRk1HWmc0WlhxbzRZVlNCc3docC0tVF9EbGNnUVpmRk40RXBWUmt5YVZ1NjN1Qk1nTUlrSFFMYXdqYmwyeUN4RWZVektWMlJkSDFwa19OOHVDaEtvTzZrcHRpMDRQVUlrVU1pcHpsb21mejVXSU5RUlVyZTBYbEZ2bFFjNmR0YkNCUWlqbDFvT1V4aDNUMGpmSWJKUkJYNkozbnNyWUhtN0ZBOWI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AJBVV95cUxOdjZZemJ1VDJ0emtGZVd1ZzBOZVlaclFuMHpaNHZwTXIxVDVfZlZUVUZKQzIzX2x0Q3l3RUZaa1g0VDYwcW5EbmQ5czlEenVvdHhNLVVqbkowQjlCQ2s3X18yU0pvczU3eHFuYUZkaVJ3N2FxTlVFaUkxTzJQXzc0NGxSRUtTZkR4MzdDUVNhZlRzdFUtVmUxMm45bWp2WE9vTGRLSWk3Z1JXS2QxZGROaWRCWUpuUmpQRk5tWUhGaE95UWJNZzVvMW1reGhJOWVibGhkZnB3eEljd0ZGaEllNExzNUIxSGtZemVEdFBDZ184M3luMmRWS2theEQyQVVYT0JPNnVvdUVuc2VsUDg5blZwMTFZWGU2VHdTLWFsSm1fRGFBdGpLUFV0Mm5sYTZyMGh2WTRPM2RteHZNR3Y3STJyYUtOdExGUG9sZWlsTEpTaFJ5TXRNTU4yX2xlN2JKM1dVMVNVTlFBS3RDS0FVRDctV3loRzR0?oc=5</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t>KXLY.com</t>
+          <t>prnewswire.com</t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr"/>
@@ -9322,28 +9446,28 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>MAJOR_LITIGATION</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t>settlement</t>
+          <t>class action</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr"/>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>832797d648cf412aadc3fea1aca57fb8</t>
+          <t>844e78ec07bb4e12a544fa2235bc541e</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>39e351ac93b9ef965a0173b9</t>
+          <t>227a7f932a6bb9d768ff6fd1</t>
         </is>
       </c>
       <c r="AD13" s="3" t="inlineStr">
         <is>
-          <t>60fc635434635081cf5136dd</t>
+          <t>df17447d9bc471f1391300cd</t>
         </is>
       </c>
       <c r="AE13" s="3" t="inlineStr"/>
@@ -9368,18 +9492,14 @@
       <c r="AT13" s="3" t="inlineStr"/>
       <c r="AU13" s="3" t="inlineStr"/>
       <c r="AV13" s="3" t="inlineStr"/>
-      <c r="AW13" s="3" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
+      <c r="AW13" s="3" t="inlineStr"/>
       <c r="AX13" s="3" t="inlineStr"/>
       <c r="AY13" s="3" t="inlineStr"/>
       <c r="AZ13" s="3" t="inlineStr"/>
       <c r="BA13" s="3" t="inlineStr"/>
       <c r="BB13" s="3" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>PNR</t>
         </is>
       </c>
       <c r="BC13" s="3" t="inlineStr">
@@ -9390,17 +9510,13 @@
       <c r="BD13" s="3" t="inlineStr"/>
       <c r="BE13" s="3" t="inlineStr">
         <is>
-          <t>https://investor.atmeta.com/stock-info/default.aspx</t>
-        </is>
-      </c>
-      <c r="BF13" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF13" s="3" t="inlineStr"/>
       <c r="BG13" s="3" t="inlineStr">
         <is>
-          <t>上市公司</t>
+          <t>公司清單／交易所參照</t>
         </is>
       </c>
       <c r="BH13" s="3" t="inlineStr"/>
@@ -9430,22 +9546,22 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>PNR</t>
+          <t>KKR</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Pentair</t>
+          <t>KKR &amp; Co. Inc. Common Stock</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27T07:55:00+08:00</t>
+          <t>2026-08-27T07:25:13+08:00</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>PNR INVESTOR DEADLINE: Robbins Geller Rudman &amp; Dowd LLP Files Class Action Lawsuit Against Pentair plc and Announces Opportunity for Investors with Substantial Losses to Lead the Pentair Class Action Lawsuit</t>
+          <t>KKR將支付2.5億美元了結司法部併購申報訴訟</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -9456,7 +9572,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>重大訴訟</t>
+          <t>監管裁罰</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -9484,11 +9600,7 @@
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>0.003</t>
-        </is>
-      </c>
+      <c r="O14" s="3" t="inlineStr"/>
       <c r="P14" s="3" t="inlineStr"/>
       <c r="Q14" s="3" t="inlineStr"/>
       <c r="R14" s="3" t="inlineStr"/>
@@ -9500,12 +9612,12 @@
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AJBVV95cUxOdjZZemJ1VDJ0emtGZVd1ZzBOZVlaclFuMHpaNHZwTXIxVDVfZlZUVUZKQzIzX2x0Q3l3RUZaa1g0VDYwcW5EbmQ5czlEenVvdHhNLVVqbkowQjlCQ2s3X18yU0pvczU3eHFuYUZkaVJ3N2FxTlVFaUkxTzJQXzc0NGxSRUtTZkR4MzdDUVNhZlRzdFUtVmUxMm45bWp2WE9vTGRLSWk3Z1JXS2QxZGROaWRCWUpuUmpQRk5tWUhGaE95UWJNZzVvMW1reGhJOWVibGhkZnB3eEljd0ZGaEllNExzNUIxSGtZemVEdFBDZ184M3luMmRWS2theEQyQVVYT0JPNnVvdUVuc2VsUDg5blZwMTFZWGU2VHdTLWFsSm1fRGFBdGpLUFV0Mm5sYTZyMGh2WTRPM2RteHZNR3Y3STJyYUtOdExGUG9sZWlsTEpTaFJ5TXRNTU4yX2xlN2JKM1dVMVNVTlFBS3RDS0FVRDctV3loRzR0?oc=5</t>
+          <t>https://www.gelonghui.com/live/2635016</t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t>prnewswire.com</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr"/>
@@ -9516,28 +9628,28 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>MAJOR_LITIGATION</t>
+          <t>REGULATORY_PENALTY</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t>class action</t>
+          <t>訴訟</t>
         </is>
       </c>
       <c r="AA14" s="3" t="inlineStr"/>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>844e78ec07bb4e12a544fa2235bc541e</t>
+          <t>1aa3debf05bb46d1b5430dfa9909b986</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>227a7f932a6bb9d768ff6fd1</t>
+          <t>41638baa3e96be115a8cb4a0</t>
         </is>
       </c>
       <c r="AD14" s="3" t="inlineStr">
         <is>
-          <t>df17447d9bc471f1391300cd</t>
+          <t>da1b0f5d42dae22f74977dfa</t>
         </is>
       </c>
       <c r="AE14" s="3" t="inlineStr"/>
@@ -9562,14 +9674,18 @@
       <c r="AT14" s="3" t="inlineStr"/>
       <c r="AU14" s="3" t="inlineStr"/>
       <c r="AV14" s="3" t="inlineStr"/>
-      <c r="AW14" s="3" t="inlineStr"/>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
       <c r="AX14" s="3" t="inlineStr"/>
       <c r="AY14" s="3" t="inlineStr"/>
       <c r="AZ14" s="3" t="inlineStr"/>
       <c r="BA14" s="3" t="inlineStr"/>
       <c r="BB14" s="3" t="inlineStr">
         <is>
-          <t>PNR</t>
+          <t>KKR</t>
         </is>
       </c>
       <c r="BC14" s="3" t="inlineStr">
@@ -9580,17 +9696,25 @@
       <c r="BD14" s="3" t="inlineStr"/>
       <c r="BE14" s="3" t="inlineStr">
         <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF14" s="3" t="inlineStr"/>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF14" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
       <c r="BG14" s="3" t="inlineStr">
         <is>
-          <t>公司清單／交易所參照</t>
+          <t>交易所目前名單</t>
         </is>
       </c>
       <c r="BH14" s="3" t="inlineStr"/>
-      <c r="BI14" s="3" t="inlineStr"/>
+      <c r="BI14" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
       <c r="BJ14" s="3" t="inlineStr"/>
       <c r="BK14" s="3" t="inlineStr">
         <is>
@@ -9616,22 +9740,22 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>KKR</t>
+          <t>META</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>KKR &amp; Co. Inc. Common Stock</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27T07:25:13+08:00</t>
+          <t>2026-08-27T05:15:00+08:00</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>KKR將支付2.5億美元了結司法部併購申報訴訟</t>
+          <t>Meta reaches landmark $18 billion settlement with states in trial over teen social media addiction</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr"/>
@@ -9670,7 +9794,11 @@
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr"/>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>'-0.184</t>
+        </is>
+      </c>
       <c r="P15" s="3" t="inlineStr"/>
       <c r="Q15" s="3" t="inlineStr"/>
       <c r="R15" s="3" t="inlineStr"/>
@@ -9682,12 +9810,12 @@
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t>https://www.gelonghui.com/live/2635016</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNMlhBT1Zvb1ZRZFhDYmpQdzhKVlJ3LXFEb1VUby1ZR0xZQnp3LTdwY2E2UWFzVy1sbHRUWTJXM0VaeVRZRnJFdjZUS3c3Q3V4VzdXYW1KeXRIT0JGZmFLeE1iNklXQkdZdmxmVnB3bnpGZ1V0bUpGSGZiZjF1c01FcU5zd3NCblNzSU9RRnR4OGNNdGpSRmc?oc=5</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>AP News</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr"/>
@@ -9703,23 +9831,23 @@
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t>訴訟</t>
+          <t>settlement</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr"/>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>1aa3debf05bb46d1b5430dfa9909b986</t>
+          <t>c15c1b53295b47a7aa47af0c95dcdceb</t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>41638baa3e96be115a8cb4a0</t>
+          <t>4441b880142ef32d3285eafd</t>
         </is>
       </c>
       <c r="AD15" s="3" t="inlineStr">
         <is>
-          <t>da1b0f5d42dae22f74977dfa</t>
+          <t>2b0eb5bbbe871ecbf264a7df</t>
         </is>
       </c>
       <c r="AE15" s="3" t="inlineStr"/>
@@ -9746,7 +9874,7 @@
       <c r="AV15" s="3" t="inlineStr"/>
       <c r="AW15" s="3" t="inlineStr">
         <is>
-          <t>NYSE</t>
+          <t>NASDAQ</t>
         </is>
       </c>
       <c r="AX15" s="3" t="inlineStr"/>
@@ -9755,7 +9883,7 @@
       <c r="BA15" s="3" t="inlineStr"/>
       <c r="BB15" s="3" t="inlineStr">
         <is>
-          <t>KKR</t>
+          <t>META</t>
         </is>
       </c>
       <c r="BC15" s="3" t="inlineStr">
@@ -9766,25 +9894,21 @@
       <c r="BD15" s="3" t="inlineStr"/>
       <c r="BE15" s="3" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+          <t>https://investor.atmeta.com/stock-info/default.aspx</t>
         </is>
       </c>
       <c r="BF15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="BG15" s="3" t="inlineStr">
         <is>
-          <t>交易所目前名單</t>
+          <t>上市公司</t>
         </is>
       </c>
       <c r="BH15" s="3" t="inlineStr"/>
-      <c r="BI15" s="3" t="inlineStr">
-        <is>
-          <t>Event_Code|事件中文</t>
-        </is>
-      </c>
+      <c r="BI15" s="3" t="inlineStr"/>
       <c r="BJ15" s="3" t="inlineStr"/>
       <c r="BK15" s="3" t="inlineStr">
         <is>
@@ -9810,22 +9934,22 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>PNR</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>Pentair</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27T05:15:00+08:00</t>
+          <t>2026-08-27T03:11:00+08:00</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Meta reaches landmark $18 billion settlement with states in trial over teen social media addiction</t>
+          <t>Levi &amp; Korsinsky Reminds Pentair plc Investors of the Pending Class Action Lawsuit With a Lead Plaintiff Deadline of October 2, 2026 - PNR</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr"/>
@@ -9836,7 +9960,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>重大訴訟</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -9866,7 +9990,7 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>'-0.184</t>
+          <t>'-0.206</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr"/>
@@ -9880,12 +10004,12 @@
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNMlhBT1Zvb1ZRZFhDYmpQdzhKVlJ3LXFEb1VUby1ZR0xZQnp3LTdwY2E2UWFzVy1sbHRUWTJXM0VaeVRZRnJFdjZUS3c3Q3V4VzdXYW1KeXRIT0JGZmFLeE1iNklXQkdZdmxmVnB3bnpGZ1V0bUpGSGZiZjF1c01FcU5zd3NCblNzSU9RRnR4OGNNdGpSRmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwJBVV95cUxPX0N5b084TkpHLTByOE0wZUs1RmtmSnNFUkVPbnJGWUhWMkVYVFBZQm1fbkw3bFlkREZSSnRLNWNKMExMcVl0STJsb3pSWXFLRDBRMDBaY1dHYWJYdWxZbzF5ekZZaWR3WmI3ZWtON1ZGTVRBaHlkeFVibjY2R1JITy1sTUhPUlNlV3Nvd2NjVnUzaHpraGhMR1c2NHVFV3l3VllfNmpMeVlKalhCaUpudnMzUUliSVM0N2MxSGw1dzNVZ1MyZlZfVnBVdFJfMDhEWDc4bFFUN2R2TUVrY3JQMk5zNklSOFhDTzZXQzQxdFdqTUpvckRxdjNnRzgtOFdRemd1WS11d1VORFlSeWJGRUV2LUNTOVpBSjhPNGUzOA?oc=5</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t>AP News</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr"/>
@@ -9896,28 +10020,28 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>MAJOR_LITIGATION</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t>settlement</t>
+          <t>class action</t>
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr"/>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>c15c1b53295b47a7aa47af0c95dcdceb</t>
+          <t>cd5b2ac52af1476a96a9c3d822dd467e</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>4441b880142ef32d3285eafd</t>
+          <t>fc678d417cfd75c3ec6d960b</t>
         </is>
       </c>
       <c r="AD16" s="3" t="inlineStr">
         <is>
-          <t>2b0eb5bbbe871ecbf264a7df</t>
+          <t>466023413d68985d9685c100</t>
         </is>
       </c>
       <c r="AE16" s="3" t="inlineStr"/>
@@ -9942,18 +10066,14 @@
       <c r="AT16" s="3" t="inlineStr"/>
       <c r="AU16" s="3" t="inlineStr"/>
       <c r="AV16" s="3" t="inlineStr"/>
-      <c r="AW16" s="3" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
+      <c r="AW16" s="3" t="inlineStr"/>
       <c r="AX16" s="3" t="inlineStr"/>
       <c r="AY16" s="3" t="inlineStr"/>
       <c r="AZ16" s="3" t="inlineStr"/>
       <c r="BA16" s="3" t="inlineStr"/>
       <c r="BB16" s="3" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>PNR</t>
         </is>
       </c>
       <c r="BC16" s="3" t="inlineStr">
@@ -9964,17 +10084,13 @@
       <c r="BD16" s="3" t="inlineStr"/>
       <c r="BE16" s="3" t="inlineStr">
         <is>
-          <t>https://investor.atmeta.com/stock-info/default.aspx</t>
-        </is>
-      </c>
-      <c r="BF16" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF16" s="3" t="inlineStr"/>
       <c r="BG16" s="3" t="inlineStr">
         <is>
-          <t>上市公司</t>
+          <t>公司清單／交易所參照</t>
         </is>
       </c>
       <c r="BH16" s="3" t="inlineStr"/>
@@ -9991,368 +10107,8 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>FDX</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>FedEx Corporation Common Stock</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-27T03:48:16+08:00</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>FedEx Cup playoffs: What to watch over the next three weeks, including Ryder Cup spots</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L17" s="5" t="inlineStr"/>
-      <c r="M17" s="5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N17" s="5" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O17" s="5" t="inlineStr">
-        <is>
-          <t>'-0.004</t>
-        </is>
-      </c>
-      <c r="P17" s="5" t="inlineStr"/>
-      <c r="Q17" s="5" t="inlineStr"/>
-      <c r="R17" s="5" t="inlineStr"/>
-      <c r="S17" s="5" t="inlineStr"/>
-      <c r="T17" s="5" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U17" s="5" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE03cUtKcjNZX0F4OFBnVVlKbkdXVW5pZ2JJaEtlSVlpTmRzOVl2N3JWSFdXcUFxd2dOSDBBN2gtWHJWUjRVY3pMdVlQUDVSUzdpZEhmOW5TMWkxc0E?oc=5</t>
-        </is>
-      </c>
-      <c r="V17" s="5" t="inlineStr">
-        <is>
-          <t>ESPN</t>
-        </is>
-      </c>
-      <c r="W17" s="5" t="inlineStr"/>
-      <c r="X17" s="5" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y17" s="5" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z17" s="5" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA17" s="5" t="inlineStr"/>
-      <c r="AB17" s="5" t="inlineStr"/>
-      <c r="AC17" s="5" t="inlineStr">
-        <is>
-          <t>4983f82dd60dacc31d2b65da</t>
-        </is>
-      </c>
-      <c r="AD17" s="5" t="inlineStr">
-        <is>
-          <t>ce7b96e947cb336b8f02e89d</t>
-        </is>
-      </c>
-      <c r="AE17" s="5" t="inlineStr"/>
-      <c r="AF17" s="5" t="inlineStr"/>
-      <c r="AG17" s="5" t="inlineStr"/>
-      <c r="AH17" s="5" t="inlineStr"/>
-      <c r="AI17" s="5" t="inlineStr"/>
-      <c r="AJ17" s="5" t="inlineStr"/>
-      <c r="AK17" s="5" t="inlineStr"/>
-      <c r="AL17" s="5" t="inlineStr"/>
-      <c r="AM17" s="5" t="inlineStr"/>
-      <c r="AN17" s="5" t="inlineStr"/>
-      <c r="AO17" s="5" t="inlineStr"/>
-      <c r="AP17" s="5" t="inlineStr"/>
-      <c r="AQ17" s="5" t="inlineStr"/>
-      <c r="AR17" s="5" t="inlineStr"/>
-      <c r="AS17" s="5" t="inlineStr"/>
-      <c r="AT17" s="5" t="inlineStr"/>
-      <c r="AU17" s="5" t="inlineStr"/>
-      <c r="AV17" s="5" t="inlineStr"/>
-      <c r="AW17" s="5" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX17" s="5" t="inlineStr"/>
-      <c r="AY17" s="5" t="inlineStr"/>
-      <c r="AZ17" s="5" t="inlineStr"/>
-      <c r="BA17" s="5" t="inlineStr"/>
-      <c r="BB17" s="5" t="inlineStr">
-        <is>
-          <t>FDX</t>
-        </is>
-      </c>
-      <c r="BC17" s="5" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD17" s="5" t="inlineStr"/>
-      <c r="BE17" s="5" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF17" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG17" s="5" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH17" s="5" t="inlineStr"/>
-      <c r="BI17" s="5" t="inlineStr"/>
-      <c r="BJ17" s="5" t="inlineStr"/>
-      <c r="BK17" s="5" t="inlineStr"/>
-      <c r="BL17" s="5" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>PNR</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>Pentair</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27T03:11:00+08:00</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>Levi &amp; Korsinsky Reminds Pentair plc Investors of the Pending Class Action Lawsuit With a Lead Plaintiff Deadline of October 2, 2026 - PNR</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>'-0.206</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="inlineStr"/>
-      <c r="Q18" s="3" t="inlineStr"/>
-      <c r="R18" s="3" t="inlineStr"/>
-      <c r="S18" s="3" t="inlineStr"/>
-      <c r="T18" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U18" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMinwJBVV95cUxPX0N5b084TkpHLTByOE0wZUs1RmtmSnNFUkVPbnJGWUhWMkVYVFBZQm1fbkw3bFlkREZSSnRLNWNKMExMcVl0STJsb3pSWXFLRDBRMDBaY1dHYWJYdWxZbzF5ekZZaWR3WmI3ZWtON1ZGTVRBaHlkeFVibjY2R1JITy1sTUhPUlNlV3Nvd2NjVnUzaHpraGhMR1c2NHVFV3l3VllfNmpMeVlKalhCaUpudnMzUUliSVM0N2MxSGw1dzNVZ1MyZlZfVnBVdFJfMDhEWDc4bFFUN2R2TUVrY3JQMk5zNklSOFhDTzZXQzQxdFdqTUpvckRxdjNnRzgtOFdRemd1WS11d1VORFlSeWJGRUV2LUNTOVpBSjhPNGUzOA?oc=5</t>
-        </is>
-      </c>
-      <c r="V18" s="3" t="inlineStr">
-        <is>
-          <t>Morningstar</t>
-        </is>
-      </c>
-      <c r="W18" s="3" t="inlineStr"/>
-      <c r="X18" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y18" s="3" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z18" s="3" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA18" s="3" t="inlineStr"/>
-      <c r="AB18" s="3" t="inlineStr">
-        <is>
-          <t>cd5b2ac52af1476a96a9c3d822dd467e</t>
-        </is>
-      </c>
-      <c r="AC18" s="3" t="inlineStr">
-        <is>
-          <t>fc678d417cfd75c3ec6d960b</t>
-        </is>
-      </c>
-      <c r="AD18" s="3" t="inlineStr">
-        <is>
-          <t>466023413d68985d9685c100</t>
-        </is>
-      </c>
-      <c r="AE18" s="3" t="inlineStr"/>
-      <c r="AF18" s="3" t="inlineStr"/>
-      <c r="AG18" s="3" t="inlineStr"/>
-      <c r="AH18" s="3" t="inlineStr"/>
-      <c r="AI18" s="3" t="inlineStr"/>
-      <c r="AJ18" s="3" t="inlineStr"/>
-      <c r="AK18" s="3" t="inlineStr"/>
-      <c r="AL18" s="3" t="inlineStr"/>
-      <c r="AM18" s="3" t="inlineStr"/>
-      <c r="AN18" s="3" t="inlineStr"/>
-      <c r="AO18" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP18" s="3" t="inlineStr"/>
-      <c r="AQ18" s="3" t="inlineStr"/>
-      <c r="AR18" s="3" t="inlineStr"/>
-      <c r="AS18" s="3" t="inlineStr"/>
-      <c r="AT18" s="3" t="inlineStr"/>
-      <c r="AU18" s="3" t="inlineStr"/>
-      <c r="AV18" s="3" t="inlineStr"/>
-      <c r="AW18" s="3" t="inlineStr"/>
-      <c r="AX18" s="3" t="inlineStr"/>
-      <c r="AY18" s="3" t="inlineStr"/>
-      <c r="AZ18" s="3" t="inlineStr"/>
-      <c r="BA18" s="3" t="inlineStr"/>
-      <c r="BB18" s="3" t="inlineStr">
-        <is>
-          <t>PNR</t>
-        </is>
-      </c>
-      <c r="BC18" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD18" s="3" t="inlineStr"/>
-      <c r="BE18" s="3" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF18" s="3" t="inlineStr"/>
-      <c r="BG18" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH18" s="3" t="inlineStr"/>
-      <c r="BI18" s="3" t="inlineStr"/>
-      <c r="BJ18" s="3" t="inlineStr"/>
-      <c r="BK18" s="3" t="inlineStr">
-        <is>
-          <t>離線覆核</t>
-        </is>
-      </c>
-      <c r="BL18" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:BL18"/>
+  <autoFilter ref="A1:BL16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10363,7 +10119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL3"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10754,324 +10510,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr"/>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>T-Mobile US</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-27T10:36:59+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>T-Mobile計劃在華盛頓州裁員並關閉多個網點</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr"/>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I2" s="5" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J2" s="5" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="5" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M2" s="5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N2" s="5" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O2" s="5" t="inlineStr"/>
-      <c r="P2" s="5" t="inlineStr"/>
-      <c r="Q2" s="5" t="inlineStr"/>
-      <c r="R2" s="5" t="inlineStr"/>
-      <c r="S2" s="5" t="inlineStr"/>
-      <c r="T2" s="5" t="inlineStr">
-        <is>
-          <t>公司名稱／股票代號歧義</t>
-        </is>
-      </c>
-      <c r="U2" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/live/2635509</t>
-        </is>
-      </c>
-      <c r="V2" s="5" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W2" s="5" t="inlineStr"/>
-      <c r="X2" s="5" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y2" s="5" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z2" s="5" t="inlineStr">
-        <is>
-          <t>裁員</t>
-        </is>
-      </c>
-      <c r="AA2" s="5" t="inlineStr"/>
-      <c r="AB2" s="5" t="inlineStr"/>
-      <c r="AC2" s="5" t="inlineStr">
-        <is>
-          <t>a66028331c9d1c3dec9371f4</t>
-        </is>
-      </c>
-      <c r="AD2" s="5" t="inlineStr">
-        <is>
-          <t>69306eed6362ccd5aad985fc</t>
-        </is>
-      </c>
-      <c r="AE2" s="5" t="inlineStr"/>
-      <c r="AF2" s="5" t="inlineStr"/>
-      <c r="AG2" s="5" t="inlineStr"/>
-      <c r="AH2" s="5" t="inlineStr"/>
-      <c r="AI2" s="5" t="inlineStr"/>
-      <c r="AJ2" s="5" t="inlineStr"/>
-      <c r="AK2" s="5" t="inlineStr"/>
-      <c r="AL2" s="5" t="inlineStr"/>
-      <c r="AM2" s="5" t="inlineStr"/>
-      <c r="AN2" s="5" t="inlineStr"/>
-      <c r="AO2" s="5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP2" s="5" t="inlineStr"/>
-      <c r="AQ2" s="5" t="inlineStr"/>
-      <c r="AR2" s="5" t="inlineStr"/>
-      <c r="AS2" s="5" t="inlineStr"/>
-      <c r="AT2" s="5" t="inlineStr"/>
-      <c r="AU2" s="5" t="inlineStr"/>
-      <c r="AV2" s="5" t="inlineStr"/>
-      <c r="AW2" s="5" t="inlineStr"/>
-      <c r="AX2" s="5" t="inlineStr"/>
-      <c r="AY2" s="5" t="inlineStr"/>
-      <c r="AZ2" s="5" t="inlineStr"/>
-      <c r="BA2" s="5" t="inlineStr"/>
-      <c r="BB2" s="5" t="inlineStr">
-        <is>
-          <t>TMUS</t>
-        </is>
-      </c>
-      <c r="BC2" s="5" t="inlineStr">
-        <is>
-          <t>公司名稱／股票代號歧義</t>
-        </is>
-      </c>
-      <c r="BD2" s="5" t="inlineStr"/>
-      <c r="BE2" s="5" t="inlineStr"/>
-      <c r="BF2" s="5" t="inlineStr"/>
-      <c r="BG2" s="5" t="inlineStr"/>
-      <c r="BH2" s="5" t="inlineStr"/>
-      <c r="BI2" s="5" t="inlineStr"/>
-      <c r="BJ2" s="5" t="inlineStr"/>
-      <c r="BK2" s="5" t="inlineStr"/>
-      <c r="BL2" s="5" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>HP Inc.</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27T04:16:03+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>惠普預計，得益於提價和美國關稅退稅，第四季度利潤將表現強勁</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>關稅</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
-      <c r="S3" s="2" t="inlineStr"/>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t>公司名稱／股票代號歧義</t>
-        </is>
-      </c>
-      <c r="U3" s="2" t="inlineStr">
-        <is>
-          <t>https://tw.tradingview.com/symbols/NYSE-HPQ/news/</t>
-        </is>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W3" s="2" t="inlineStr"/>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>GEOPOLITICAL</t>
-        </is>
-      </c>
-      <c r="Y3" s="2" t="inlineStr">
-        <is>
-          <t>TARIFF</t>
-        </is>
-      </c>
-      <c r="Z3" s="2" t="inlineStr">
-        <is>
-          <t>關稅</t>
-        </is>
-      </c>
-      <c r="AA3" s="2" t="inlineStr"/>
-      <c r="AB3" s="2" t="inlineStr"/>
-      <c r="AC3" s="2" t="inlineStr">
-        <is>
-          <t>7e6cff4c708cba0068778da2</t>
-        </is>
-      </c>
-      <c r="AD3" s="2" t="inlineStr">
-        <is>
-          <t>b44e753a259cedc98127ae6d</t>
-        </is>
-      </c>
-      <c r="AE3" s="2" t="inlineStr"/>
-      <c r="AF3" s="2" t="inlineStr"/>
-      <c r="AG3" s="2" t="inlineStr"/>
-      <c r="AH3" s="2" t="inlineStr"/>
-      <c r="AI3" s="2" t="inlineStr"/>
-      <c r="AJ3" s="2" t="inlineStr"/>
-      <c r="AK3" s="2" t="inlineStr"/>
-      <c r="AL3" s="2" t="inlineStr"/>
-      <c r="AM3" s="2" t="inlineStr"/>
-      <c r="AN3" s="2" t="inlineStr"/>
-      <c r="AO3" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP3" s="2" t="inlineStr"/>
-      <c r="AQ3" s="2" t="inlineStr"/>
-      <c r="AR3" s="2" t="inlineStr"/>
-      <c r="AS3" s="2" t="inlineStr"/>
-      <c r="AT3" s="2" t="inlineStr"/>
-      <c r="AU3" s="2" t="inlineStr"/>
-      <c r="AV3" s="2" t="inlineStr"/>
-      <c r="AW3" s="2" t="inlineStr"/>
-      <c r="AX3" s="2" t="inlineStr"/>
-      <c r="AY3" s="2" t="inlineStr"/>
-      <c r="AZ3" s="2" t="inlineStr"/>
-      <c r="BA3" s="2" t="inlineStr"/>
-      <c r="BB3" s="2" t="inlineStr">
-        <is>
-          <t>HPQ</t>
-        </is>
-      </c>
-      <c r="BC3" s="2" t="inlineStr">
-        <is>
-          <t>公司名稱／股票代號歧義</t>
-        </is>
-      </c>
-      <c r="BD3" s="2" t="inlineStr"/>
-      <c r="BE3" s="2" t="inlineStr"/>
-      <c r="BF3" s="2" t="inlineStr"/>
-      <c r="BG3" s="2" t="inlineStr"/>
-      <c r="BH3" s="2" t="inlineStr"/>
-      <c r="BI3" s="2" t="inlineStr"/>
-      <c r="BJ3" s="2" t="inlineStr"/>
-      <c r="BK3" s="2" t="inlineStr"/>
-      <c r="BL3" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:BL3"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/news_daily/2026-08-27.xlsx
+++ b/news_daily/2026-08-27.xlsx
@@ -896,28 +896,32 @@
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -957,7 +961,7 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -966,7 +970,11 @@
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>0da033f6754941d5a0fc60d8506c07f7</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>1eb7827b5b5253467b5b317b</t>
@@ -987,7 +995,11 @@
       <c r="AL2" s="2" t="inlineStr"/>
       <c r="AM2" s="2" t="inlineStr"/>
       <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="2" t="inlineStr"/>
       <c r="AQ2" s="2" t="inlineStr"/>
       <c r="AR2" s="2" t="inlineStr"/>
@@ -1031,10 +1043,22 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
-      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1462,28 +1486,32 @@
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1523,7 +1551,7 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1532,7 +1560,11 @@
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr"/>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>d849cd807f3e4affa88e59b9916cee22</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
           <t>aef9837bd9e77e59a3d3d665</t>
@@ -1553,7 +1585,11 @@
       <c r="AL5" s="2" t="inlineStr"/>
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="inlineStr"/>
-      <c r="AO5" s="2" t="inlineStr"/>
+      <c r="AO5" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP5" s="2" t="inlineStr"/>
       <c r="AQ5" s="2" t="inlineStr"/>
       <c r="AR5" s="2" t="inlineStr"/>
@@ -1597,10 +1633,22 @@
         </is>
       </c>
       <c r="BH5" s="2" t="inlineStr"/>
-      <c r="BI5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ5" s="2" t="inlineStr"/>
-      <c r="BK5" s="2" t="inlineStr"/>
-      <c r="BL5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -2416,28 +2464,32 @@
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -2477,7 +2529,7 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
@@ -2486,7 +2538,11 @@
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr"/>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>b8a70f44bf6c4c3ca326022b0a57812d</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
           <t>47ee87fbc0be259e9e7b691f</t>
@@ -2507,7 +2563,11 @@
       <c r="AL10" s="2" t="inlineStr"/>
       <c r="AM10" s="2" t="inlineStr"/>
       <c r="AN10" s="2" t="inlineStr"/>
-      <c r="AO10" s="2" t="inlineStr"/>
+      <c r="AO10" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP10" s="2" t="inlineStr"/>
       <c r="AQ10" s="2" t="inlineStr"/>
       <c r="AR10" s="2" t="inlineStr"/>
@@ -2551,10 +2611,22 @@
         </is>
       </c>
       <c r="BH10" s="2" t="inlineStr"/>
-      <c r="BI10" s="2" t="inlineStr"/>
+      <c r="BI10" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ10" s="2" t="inlineStr"/>
-      <c r="BK10" s="2" t="inlineStr"/>
-      <c r="BL10" s="2" t="inlineStr"/>
+      <c r="BK10" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2590,28 +2662,32 @@
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -2651,7 +2727,7 @@
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -2660,7 +2736,11 @@
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr"/>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>3e7b393531ea428d9ca88d88acfeb042</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
           <t>b8dafd412ab007aa0c8d0b6a</t>
@@ -2681,7 +2761,11 @@
       <c r="AL11" s="2" t="inlineStr"/>
       <c r="AM11" s="2" t="inlineStr"/>
       <c r="AN11" s="2" t="inlineStr"/>
-      <c r="AO11" s="2" t="inlineStr"/>
+      <c r="AO11" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP11" s="2" t="inlineStr"/>
       <c r="AQ11" s="2" t="inlineStr"/>
       <c r="AR11" s="2" t="inlineStr"/>
@@ -2725,10 +2809,22 @@
         </is>
       </c>
       <c r="BH11" s="2" t="inlineStr"/>
-      <c r="BI11" s="2" t="inlineStr"/>
+      <c r="BI11" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ11" s="2" t="inlineStr"/>
-      <c r="BK11" s="2" t="inlineStr"/>
-      <c r="BL11" s="2" t="inlineStr"/>
+      <c r="BK11" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -3346,28 +3442,32 @@
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3407,7 +3507,7 @@
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
@@ -3416,7 +3516,11 @@
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr"/>
-      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>00d3be2e88144fad95e99433885e0a66</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
           <t>a5a8db1640b334ed3f2409c0</t>
@@ -3437,7 +3541,11 @@
       <c r="AL15" s="2" t="inlineStr"/>
       <c r="AM15" s="2" t="inlineStr"/>
       <c r="AN15" s="2" t="inlineStr"/>
-      <c r="AO15" s="2" t="inlineStr"/>
+      <c r="AO15" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP15" s="2" t="inlineStr"/>
       <c r="AQ15" s="2" t="inlineStr"/>
       <c r="AR15" s="2" t="inlineStr"/>
@@ -3481,10 +3589,22 @@
         </is>
       </c>
       <c r="BH15" s="2" t="inlineStr"/>
-      <c r="BI15" s="2" t="inlineStr"/>
+      <c r="BI15" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ15" s="2" t="inlineStr"/>
-      <c r="BK15" s="2" t="inlineStr"/>
-      <c r="BL15" s="2" t="inlineStr"/>
+      <c r="BK15" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -4858,28 +4978,32 @@
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -4919,7 +5043,7 @@
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -4928,7 +5052,11 @@
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr"/>
-      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>5f22d8a21e43445a9aeefee766a2f59f</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
           <t>1e0941df4a11efcfb48f8ff6</t>
@@ -4949,7 +5077,11 @@
       <c r="AL23" s="2" t="inlineStr"/>
       <c r="AM23" s="2" t="inlineStr"/>
       <c r="AN23" s="2" t="inlineStr"/>
-      <c r="AO23" s="2" t="inlineStr"/>
+      <c r="AO23" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP23" s="2" t="inlineStr"/>
       <c r="AQ23" s="2" t="inlineStr"/>
       <c r="AR23" s="2" t="inlineStr"/>
@@ -4993,10 +5125,22 @@
         </is>
       </c>
       <c r="BH23" s="2" t="inlineStr"/>
-      <c r="BI23" s="2" t="inlineStr"/>
+      <c r="BI23" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ23" s="2" t="inlineStr"/>
-      <c r="BK23" s="2" t="inlineStr"/>
-      <c r="BL23" s="2" t="inlineStr"/>
+      <c r="BK23" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -5226,28 +5370,32 @@
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -5287,7 +5435,7 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -5296,7 +5444,11 @@
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr"/>
-      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>c07be8f372874a99bb1704e132ec2809</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
           <t>64b4c6abd35c4085b7cb9afc</t>
@@ -5317,7 +5469,11 @@
       <c r="AL25" s="2" t="inlineStr"/>
       <c r="AM25" s="2" t="inlineStr"/>
       <c r="AN25" s="2" t="inlineStr"/>
-      <c r="AO25" s="2" t="inlineStr"/>
+      <c r="AO25" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP25" s="2" t="inlineStr"/>
       <c r="AQ25" s="2" t="inlineStr"/>
       <c r="AR25" s="2" t="inlineStr"/>
@@ -5361,10 +5517,22 @@
         </is>
       </c>
       <c r="BH25" s="2" t="inlineStr"/>
-      <c r="BI25" s="2" t="inlineStr"/>
+      <c r="BI25" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ25" s="2" t="inlineStr"/>
-      <c r="BK25" s="2" t="inlineStr"/>
-      <c r="BL25" s="2" t="inlineStr"/>
+      <c r="BK25" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5772,28 +5940,32 @@
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -5833,7 +6005,7 @@
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -5842,7 +6014,11 @@
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr"/>
-      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>e84cd9d244b84b6286903978b740e2cf</t>
+        </is>
+      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
           <t>4525384846879e77baa39a0a</t>
@@ -5863,7 +6039,11 @@
       <c r="AL28" s="2" t="inlineStr"/>
       <c r="AM28" s="2" t="inlineStr"/>
       <c r="AN28" s="2" t="inlineStr"/>
-      <c r="AO28" s="2" t="inlineStr"/>
+      <c r="AO28" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP28" s="2" t="inlineStr"/>
       <c r="AQ28" s="2" t="inlineStr"/>
       <c r="AR28" s="2" t="inlineStr"/>
@@ -5907,10 +6087,22 @@
         </is>
       </c>
       <c r="BH28" s="2" t="inlineStr"/>
-      <c r="BI28" s="2" t="inlineStr"/>
+      <c r="BI28" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ28" s="2" t="inlineStr"/>
-      <c r="BK28" s="2" t="inlineStr"/>
-      <c r="BL28" s="2" t="inlineStr"/>
+      <c r="BK28" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -6147,13 +6339,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -6202,7 +6398,11 @@
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr"/>
-      <c r="AB30" s="2" t="inlineStr"/>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>1499b167cf374973a746cfe90b4ddb8a</t>
+        </is>
+      </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
           <t>dd9f4fd42f4c3277a958f408</t>
@@ -6223,7 +6423,11 @@
       <c r="AL30" s="2" t="inlineStr"/>
       <c r="AM30" s="2" t="inlineStr"/>
       <c r="AN30" s="2" t="inlineStr"/>
-      <c r="AO30" s="2" t="inlineStr"/>
+      <c r="AO30" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP30" s="2" t="inlineStr"/>
       <c r="AQ30" s="2" t="inlineStr"/>
       <c r="AR30" s="2" t="inlineStr"/>
@@ -6269,8 +6473,16 @@
       <c r="BH30" s="2" t="inlineStr"/>
       <c r="BI30" s="2" t="inlineStr"/>
       <c r="BJ30" s="2" t="inlineStr"/>
-      <c r="BK30" s="2" t="inlineStr"/>
-      <c r="BL30" s="2" t="inlineStr"/>
+      <c r="BK30" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6511,13 +6723,17 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -6566,7 +6782,11 @@
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr"/>
-      <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>e72cd892ba104b7ca1c486f08e74ac98</t>
+        </is>
+      </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
           <t>39975b497d1456ef4a593336</t>
@@ -6587,7 +6807,11 @@
       <c r="AL32" s="2" t="inlineStr"/>
       <c r="AM32" s="2" t="inlineStr"/>
       <c r="AN32" s="2" t="inlineStr"/>
-      <c r="AO32" s="2" t="inlineStr"/>
+      <c r="AO32" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP32" s="2" t="inlineStr"/>
       <c r="AQ32" s="2" t="inlineStr"/>
       <c r="AR32" s="2" t="inlineStr"/>
@@ -6633,8 +6857,16 @@
       <c r="BH32" s="2" t="inlineStr"/>
       <c r="BI32" s="2" t="inlineStr"/>
       <c r="BJ32" s="2" t="inlineStr"/>
-      <c r="BK32" s="2" t="inlineStr"/>
-      <c r="BL32" s="2" t="inlineStr"/>
+      <c r="BK32" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
